--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,42 +425,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>10 лет</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>5 лет</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3 года</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>1 год</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Средняя</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Прошла фильтр</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Причина</t>
         </is>
@@ -1517,92 +1505,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, ₽</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, ₽</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, ₽</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, ₽</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), ₽</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -2967,92 +2955,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, ₽</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, ₽</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, ₽</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, ₽</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), ₽</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -4673,92 +4661,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, ₽</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, ₽</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, ₽</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, ₽</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), ₽</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -6507,92 +6495,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, ₽</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, ₽</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, ₽</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, ₽</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), ₽</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -7445,47 +7433,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -8444,31 +8432,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TATN/PLZL_2025</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>772.7</v>
+        <v>237.21</v>
       </c>
       <c r="E29" t="n">
-        <v>693.9</v>
+        <v>284.91</v>
       </c>
       <c r="F29" t="n">
-        <v>772.7</v>
+        <v>237.21</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-10.2</v>
+        <v>20.11</v>
       </c>
       <c r="I29" t="n">
-        <v>-10.2</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="30">
@@ -8514,19 +8502,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/PLZL_2025</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>772.7</v>
       </c>
       <c r="E31" t="n">
-        <v>632.2</v>
+        <v>693.9</v>
       </c>
       <c r="F31" t="n">
         <v>772.7</v>
@@ -8535,10 +8523,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-18.18</v>
+        <v>-10.2</v>
       </c>
       <c r="I31" t="n">
-        <v>-18.18</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="32">
@@ -8549,12 +8537,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -8584,31 +8572,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>237.21</v>
+        <v>772.7</v>
       </c>
       <c r="E33" t="n">
-        <v>284.91</v>
+        <v>632.2</v>
       </c>
       <c r="F33" t="n">
-        <v>237.21</v>
+        <v>772.7</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>20.11</v>
+        <v>-18.18</v>
       </c>
       <c r="I33" t="n">
-        <v>20.11</v>
+        <v>-18.18</v>
       </c>
     </row>
   </sheetData>
@@ -8626,47 +8614,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -9807,47 +9795,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -10988,47 +10976,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Под-пара</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -11532,31 +11520,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>600.6</v>
+        <v>304.69</v>
       </c>
       <c r="E16" t="n">
-        <v>606.2</v>
+        <v>285.3</v>
       </c>
       <c r="F16" t="n">
-        <v>600.6</v>
+        <v>304.69</v>
       </c>
       <c r="G16" t="n">
         <v>5.61</v>
       </c>
       <c r="H16" t="n">
-        <v>0.93</v>
+        <v>-6.36</v>
       </c>
       <c r="I16" t="n">
-        <v>4.42</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="17">
@@ -11567,31 +11555,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>304.69</v>
+        <v>600.6</v>
       </c>
       <c r="E17" t="n">
-        <v>285.3</v>
+        <v>606.2</v>
       </c>
       <c r="F17" t="n">
-        <v>304.69</v>
+        <v>600.6</v>
       </c>
       <c r="G17" t="n">
         <v>5.61</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.36</v>
+        <v>0.93</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.25</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="18">
@@ -11672,31 +11660,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>ROSN/SBERP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>ROSN/SBERP</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2309.6</v>
+        <v>304.69</v>
       </c>
       <c r="E20" t="n">
-        <v>990.2</v>
+        <v>285.3</v>
       </c>
       <c r="F20" t="n">
-        <v>2309.6</v>
+        <v>304.69</v>
       </c>
       <c r="G20" t="n">
         <v>3.81</v>
       </c>
       <c r="H20" t="n">
-        <v>-57.13</v>
+        <v>-6.36</v>
       </c>
       <c r="I20" t="n">
-        <v>-58.46</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="21">
@@ -11707,31 +11695,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ROSN/SBERP</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ROSN/SBERP</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>304.69</v>
+        <v>2309.6</v>
       </c>
       <c r="E21" t="n">
-        <v>285.3</v>
+        <v>990.2</v>
       </c>
       <c r="F21" t="n">
-        <v>304.69</v>
+        <v>2309.6</v>
       </c>
       <c r="G21" t="n">
         <v>3.81</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.36</v>
+        <v>-57.13</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.84</v>
+        <v>-58.46</v>
       </c>
     </row>
     <row r="22">
@@ -11847,31 +11835,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>629.3</v>
+        <v>441</v>
       </c>
       <c r="E25" t="n">
-        <v>632.2</v>
+        <v>372.65</v>
       </c>
       <c r="F25" t="n">
-        <v>629.3</v>
+        <v>441</v>
       </c>
       <c r="G25" t="n">
         <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>0.46</v>
+        <v>-15.5</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.68</v>
+        <v>-18.57</v>
       </c>
     </row>
     <row r="26">
@@ -11882,31 +11870,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>441</v>
+        <v>629.3</v>
       </c>
       <c r="E26" t="n">
-        <v>372.65</v>
+        <v>632.2</v>
       </c>
       <c r="F26" t="n">
-        <v>441</v>
+        <v>629.3</v>
       </c>
       <c r="G26" t="n">
         <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.5</v>
+        <v>0.46</v>
       </c>
       <c r="I26" t="n">
-        <v>-18.57</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="27">
@@ -11952,31 +11940,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2309.6</v>
+        <v>170.92</v>
       </c>
       <c r="E28" t="n">
-        <v>990.2</v>
+        <v>152.19</v>
       </c>
       <c r="F28" t="n">
-        <v>2309.6</v>
+        <v>170.92</v>
       </c>
       <c r="G28" t="n">
         <v>2.19</v>
       </c>
       <c r="H28" t="n">
-        <v>-57.13</v>
+        <v>-10.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-56.13</v>
+        <v>-10.76</v>
       </c>
     </row>
     <row r="29">
@@ -11987,31 +11975,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>170.92</v>
+        <v>2309.6</v>
       </c>
       <c r="E29" t="n">
-        <v>152.19</v>
+        <v>990.2</v>
       </c>
       <c r="F29" t="n">
-        <v>170.92</v>
+        <v>2309.6</v>
       </c>
       <c r="G29" t="n">
         <v>2.19</v>
       </c>
       <c r="H29" t="n">
-        <v>-10.96</v>
+        <v>-57.13</v>
       </c>
       <c r="I29" t="n">
-        <v>-10.76</v>
+        <v>-56.13</v>
       </c>
     </row>
     <row r="30">
@@ -12057,31 +12045,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22.84</v>
+        <v>304.5</v>
       </c>
       <c r="E31" t="n">
-        <v>16.58</v>
+        <v>284.91</v>
       </c>
       <c r="F31" t="n">
-        <v>22.84</v>
+        <v>304.5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-27.39</v>
+        <v>-6.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-27.39</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="32">
@@ -12092,31 +12080,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>304.5</v>
+        <v>6380</v>
       </c>
       <c r="E32" t="n">
-        <v>284.91</v>
+        <v>5484.5</v>
       </c>
       <c r="F32" t="n">
-        <v>304.5</v>
+        <v>6380</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-6.43</v>
+        <v>-14.04</v>
       </c>
       <c r="I32" t="n">
-        <v>-6.43</v>
+        <v>-14.04</v>
       </c>
     </row>
     <row r="33">
@@ -12127,31 +12115,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6380</v>
+        <v>22.84</v>
       </c>
       <c r="E33" t="n">
-        <v>5484.5</v>
+        <v>16.58</v>
       </c>
       <c r="F33" t="n">
-        <v>6380</v>
+        <v>22.84</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-14.04</v>
+        <v>-27.39</v>
       </c>
       <c r="I33" t="n">
-        <v>-14.04</v>
+        <v>-27.39</v>
       </c>
     </row>
   </sheetData>

--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.5</v>
+        <v>67.33</v>
       </c>
       <c r="C2" t="n">
         <v>43.7</v>
       </c>
       <c r="D2" t="n">
-        <v>57.63</v>
+        <v>56.34</v>
       </c>
       <c r="E2" t="n">
-        <v>12.27</v>
+        <v>12.77</v>
       </c>
       <c r="F2" t="n">
-        <v>45.03</v>
+        <v>45.04</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>107.8</v>
+        <v>107.59</v>
       </c>
       <c r="C3" t="n">
         <v>9.94</v>
       </c>
       <c r="D3" t="n">
-        <v>38.57</v>
+        <v>36.85</v>
       </c>
       <c r="E3" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="F3" t="n">
-        <v>39.54</v>
+        <v>39.16</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>103.49</v>
+        <v>103.45</v>
       </c>
       <c r="C4" t="n">
         <v>12.52</v>
@@ -546,10 +546,10 @@
         <v>17.42</v>
       </c>
       <c r="E4" t="n">
-        <v>14.59</v>
+        <v>20.3</v>
       </c>
       <c r="F4" t="n">
-        <v>37.01</v>
+        <v>38.42</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84.29000000000001</v>
+        <v>85</v>
       </c>
       <c r="C5" t="n">
         <v>9.06</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6</v>
+        <v>31.81</v>
       </c>
       <c r="E5" t="n">
-        <v>6.18</v>
+        <v>7.19</v>
       </c>
       <c r="F5" t="n">
-        <v>33.03</v>
+        <v>33.27</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -601,19 +601,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.41</v>
+        <v>49.68</v>
       </c>
       <c r="C6" t="n">
         <v>19.23</v>
       </c>
       <c r="D6" t="n">
-        <v>42.17</v>
+        <v>40.74</v>
       </c>
       <c r="E6" t="n">
-        <v>5.45</v>
+        <v>5.84</v>
       </c>
       <c r="F6" t="n">
-        <v>31.32</v>
+        <v>28.87</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -629,23 +629,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>SBER/PLZL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.15000000000001</v>
+        <v>40.61</v>
       </c>
       <c r="C7" t="n">
-        <v>4.81</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>53.54</v>
       </c>
       <c r="E7" t="n">
-        <v>19.01</v>
+        <v>1.61</v>
       </c>
       <c r="F7" t="n">
-        <v>25.99</v>
+        <v>25.95</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -661,23 +661,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBER/PLZL</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.61</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>8.039999999999999</v>
+        <v>37.97</v>
       </c>
       <c r="D8" t="n">
-        <v>55.49</v>
+        <v>30.72</v>
       </c>
       <c r="E8" t="n">
-        <v>3.26</v>
+        <v>16.43</v>
       </c>
       <c r="F8" t="n">
-        <v>24.35</v>
+        <v>23.37</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="C9" t="n">
-        <v>48.44</v>
+        <v>45.68</v>
       </c>
       <c r="D9" t="n">
-        <v>39.87</v>
+        <v>38.97</v>
       </c>
       <c r="E9" t="n">
-        <v>5.61</v>
+        <v>3.06</v>
       </c>
       <c r="F9" t="n">
-        <v>23.48</v>
+        <v>22.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -725,23 +725,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>45.68</v>
+        <v>48.44</v>
       </c>
       <c r="D10" t="n">
-        <v>40.7</v>
+        <v>40.33</v>
       </c>
       <c r="E10" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="F10" t="n">
-        <v>23.18</v>
+        <v>22.71</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41.46</v>
+        <v>41.99</v>
       </c>
       <c r="C11" t="n">
         <v>8.98</v>
       </c>
       <c r="D11" t="n">
-        <v>33.61</v>
+        <v>32.83</v>
       </c>
       <c r="E11" t="n">
-        <v>3.81</v>
+        <v>4.78</v>
       </c>
       <c r="F11" t="n">
-        <v>21.96</v>
+        <v>22.14</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>GMKN/PLZL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>80.11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.53</v>
+        <v>4.81</v>
       </c>
       <c r="D12" t="n">
-        <v>36.31</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="F12" t="n">
-        <v>21.76</v>
+        <v>22</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -821,23 +821,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>32.95</v>
+        <v>48.53</v>
       </c>
       <c r="D13" t="n">
-        <v>44.1</v>
+        <v>36.76</v>
       </c>
       <c r="E13" t="n">
-        <v>5.61</v>
+        <v>2.5</v>
       </c>
       <c r="F13" t="n">
-        <v>20.67</v>
+        <v>21.95</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -853,23 +853,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLZL/SBERP</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.42</v>
+        <v>28.1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>13.41</v>
       </c>
       <c r="D14" t="n">
-        <v>40.1</v>
+        <v>19.9</v>
       </c>
       <c r="E14" t="n">
-        <v>9.779999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="F14" t="n">
-        <v>20.08</v>
+        <v>21.08</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -885,23 +885,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBER/TATNP</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.61</v>
+        <v>10.89</v>
       </c>
       <c r="C15" t="n">
-        <v>37.97</v>
+        <v>30.96</v>
       </c>
       <c r="D15" t="n">
-        <v>32.34</v>
+        <v>26.33</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>14.87</v>
       </c>
       <c r="F15" t="n">
-        <v>20.07</v>
+        <v>20.76</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -917,23 +917,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ROSN/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>43.22</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.04</v>
+        <v>32.95</v>
       </c>
       <c r="D16" t="n">
-        <v>18.21</v>
+        <v>42.82</v>
       </c>
       <c r="E16" t="n">
-        <v>3.81</v>
+        <v>6.75</v>
       </c>
       <c r="F16" t="n">
-        <v>19.82</v>
+        <v>20.63</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -949,23 +949,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>ROSN/SBERP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12.34</v>
+        <v>43.14</v>
       </c>
       <c r="C17" t="n">
-        <v>30.96</v>
+        <v>14.04</v>
       </c>
       <c r="D17" t="n">
-        <v>27.24</v>
+        <v>19.74</v>
       </c>
       <c r="E17" t="n">
-        <v>2.32</v>
+        <v>4.78</v>
       </c>
       <c r="F17" t="n">
-        <v>18.21</v>
+        <v>20.43</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -981,23 +981,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>PLZL/SBERP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.01</v>
+        <v>27.03</v>
       </c>
       <c r="C18" t="n">
-        <v>19.76</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>24.83</v>
+        <v>38.98</v>
       </c>
       <c r="E18" t="n">
-        <v>7.34</v>
+        <v>9.98</v>
       </c>
       <c r="F18" t="n">
-        <v>17.98</v>
+        <v>20</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1013,23 +1013,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GAZP/VTBR</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.73</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>13.41</v>
+        <v>20.92</v>
       </c>
       <c r="D19" t="n">
-        <v>19.9</v>
+        <v>44.17</v>
       </c>
       <c r="E19" t="n">
-        <v>9.77</v>
+        <v>8.69</v>
       </c>
       <c r="F19" t="n">
-        <v>17.45</v>
+        <v>18.45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1045,23 +1045,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>27.54</v>
       </c>
       <c r="C20" t="n">
-        <v>20.92</v>
+        <v>6.88</v>
       </c>
       <c r="D20" t="n">
-        <v>43.69</v>
+        <v>16.07</v>
       </c>
       <c r="E20" t="n">
-        <v>2.19</v>
+        <v>13.09</v>
       </c>
       <c r="F20" t="n">
-        <v>16.7</v>
+        <v>15.89</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1077,23 +1077,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.529999999999999</v>
+        <v>34.48</v>
       </c>
       <c r="C21" t="n">
-        <v>9.619999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="D21" t="n">
-        <v>39.38</v>
+        <v>17.42</v>
       </c>
       <c r="E21" t="n">
-        <v>7.86</v>
+        <v>3.06</v>
       </c>
       <c r="F21" t="n">
-        <v>16.6</v>
+        <v>15.69</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1109,23 +1109,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>ROSN/TATN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34.61</v>
+        <v>3.12</v>
       </c>
       <c r="C22" t="n">
-        <v>7.79</v>
+        <v>18.72</v>
       </c>
       <c r="D22" t="n">
-        <v>20.63</v>
+        <v>26.05</v>
       </c>
       <c r="E22" t="n">
-        <v>2.34</v>
+        <v>13.17</v>
       </c>
       <c r="F22" t="n">
-        <v>16.34</v>
+        <v>15.27</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1141,23 +1141,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.57</v>
+        <v>33.72</v>
       </c>
       <c r="C23" t="n">
-        <v>6.88</v>
+        <v>4.27</v>
       </c>
       <c r="D23" t="n">
-        <v>16.07</v>
+        <v>22.63</v>
       </c>
       <c r="E23" t="n">
-        <v>10.75</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>15.32</v>
+        <v>15.15</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1173,23 +1173,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ROSN/TATN</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.75</v>
+        <v>21.46</v>
       </c>
       <c r="C24" t="n">
-        <v>18.72</v>
+        <v>24.53</v>
       </c>
       <c r="D24" t="n">
-        <v>26.81</v>
+        <v>7.55</v>
       </c>
       <c r="E24" t="n">
-        <v>12.1</v>
+        <v>2.69</v>
       </c>
       <c r="F24" t="n">
-        <v>15.1</v>
+        <v>14.06</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1205,23 +1205,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>36.72</v>
+        <v>14.03</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>27.22</v>
       </c>
       <c r="D25" t="n">
-        <v>6.89</v>
+        <v>7.51</v>
       </c>
       <c r="E25" t="n">
-        <v>10.81</v>
+        <v>6.66</v>
       </c>
       <c r="F25" t="n">
-        <v>13.61</v>
+        <v>13.86</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1237,23 +1237,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.72</v>
+        <v>7.48</v>
       </c>
       <c r="C26" t="n">
-        <v>17.38</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>23.67</v>
+        <v>30.2</v>
       </c>
       <c r="E26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.89</v>
       </c>
       <c r="F26" t="n">
-        <v>12.89</v>
+        <v>13.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1269,23 +1269,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GAZP/SNGS</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.22</v>
+        <v>36.7</v>
       </c>
       <c r="C27" t="n">
-        <v>24.53</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7.9</v>
+        <v>6.89</v>
       </c>
       <c r="E27" t="n">
-        <v>6.09</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>12.43</v>
+        <v>13.08</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1301,23 +1301,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.79</v>
+        <v>2.08</v>
       </c>
       <c r="C28" t="n">
-        <v>27.22</v>
+        <v>17.38</v>
       </c>
       <c r="D28" t="n">
-        <v>7.51</v>
+        <v>22.94</v>
       </c>
       <c r="E28" t="n">
-        <v>4.48</v>
+        <v>9.83</v>
       </c>
       <c r="F28" t="n">
-        <v>11.5</v>
+        <v>13.06</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1333,23 +1333,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>PLZL/TATNP</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30.27</v>
+        <v>2.34</v>
       </c>
       <c r="C29" t="n">
-        <v>4.27</v>
+        <v>19.76</v>
       </c>
       <c r="D29" t="n">
-        <v>11.36</v>
+        <v>21.75</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="F29" t="n">
-        <v>11.47</v>
+        <v>11.92</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11.43</v>
+        <v>12.31</v>
       </c>
       <c r="C30" t="n">
         <v>21.49</v>
@@ -1378,10 +1378,10 @@
         <v>8.33</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="F30" t="n">
-        <v>10.31</v>
+        <v>11.54</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.27</v>
+        <v>20.16</v>
       </c>
       <c r="C31" t="n">
         <v>6.42</v>
@@ -1410,10 +1410,10 @@
         <v>10.33</v>
       </c>
       <c r="E31" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="F31" t="n">
-        <v>10.02</v>
+        <v>10.17</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.04</v>
+        <v>9.07</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1442,10 +1442,10 @@
         <v>7.41</v>
       </c>
       <c r="E32" t="n">
-        <v>9.5</v>
+        <v>11.8</v>
       </c>
       <c r="F32" t="n">
-        <v>4.74</v>
+        <v>7.07</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>средняя = 4.74</t>
+          <t>средняя = 7.07</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,42 +1619,42 @@
         <v>185</v>
       </c>
       <c r="F2" t="n">
-        <v>14.0115</v>
+        <v>14.0984</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>980.3519</v>
+        <v>985.7044</v>
       </c>
       <c r="I2" t="n">
-        <v>785.5391</v>
+        <v>789.8278</v>
       </c>
       <c r="J2" t="n">
         <v>100000</v>
       </c>
       <c r="K2" t="n">
-        <v>167390.52</v>
+        <v>168304.42</v>
       </c>
       <c r="L2" t="n">
-        <v>12740.54</v>
+        <v>12891.72</v>
       </c>
       <c r="M2" t="n">
-        <v>3010.72</v>
+        <v>3027.4</v>
       </c>
       <c r="N2" t="n">
-        <v>151639.25</v>
+        <v>152385.29</v>
       </c>
       <c r="O2" t="n">
-        <v>51.64</v>
+        <v>52.39</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>785.5391 MOEX</t>
+          <t>789.8278 MOEX</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>100.26</v>
+        <v>99.94</v>
       </c>
       <c r="R2" t="n">
         <v>213.09</v>
@@ -1683,13 +1683,13 @@
         <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>421.5674</v>
+        <v>421.0526</v>
       </c>
       <c r="G3" t="n">
-        <v>629.2284</v>
+        <v>628.5551</v>
       </c>
       <c r="H3" t="n">
-        <v>981.7675</v>
+        <v>980.7169</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1698,30 +1698,30 @@
         <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>179273.46</v>
+        <v>175957.71</v>
       </c>
       <c r="L3" t="n">
-        <v>21792.11</v>
+        <v>21752.8</v>
       </c>
       <c r="M3" t="n">
-        <v>8123.34</v>
+        <v>8114.6</v>
       </c>
       <c r="N3" t="n">
-        <v>149358.01</v>
+        <v>146090.31</v>
       </c>
       <c r="O3" t="n">
-        <v>49.36</v>
+        <v>46.09</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>629.2284 SBER</t>
+          <t>628.5551 SBER</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>237.21</v>
+        <v>237.5</v>
       </c>
       <c r="R3" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="4">
@@ -1732,60 +1732,60 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>SBER/PLZL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GMKN_2024/PLZL_2025</t>
+          <t>SBER/PLZL_2025</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7399</v>
+        <v>421.0526</v>
       </c>
       <c r="G4" t="n">
+        <v>479.2078</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14.7832</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15.7309</v>
-      </c>
-      <c r="I4" t="n">
-        <v>13.0434</v>
       </c>
       <c r="J4" t="n">
         <v>100000</v>
       </c>
       <c r="K4" t="n">
-        <v>162390.41</v>
+        <v>154908.71</v>
       </c>
       <c r="L4" t="n">
-        <v>15793.36</v>
+        <v>8213.66</v>
       </c>
       <c r="M4" t="n">
-        <v>4877.75</v>
+        <v>3073.87</v>
       </c>
       <c r="N4" t="n">
-        <v>141719.3</v>
+        <v>143621.18</v>
       </c>
       <c r="O4" t="n">
-        <v>41.72</v>
+        <v>43.62</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>13.0434 PLZL_2025</t>
+          <t>479.2078 SBER</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>7137</v>
+        <v>237.5</v>
       </c>
       <c r="R4" t="n">
-        <v>12450</v>
+        <v>323.26</v>
       </c>
     </row>
     <row r="5">
@@ -1796,60 +1796,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SBER/PLZL</t>
+          <t>GMKN/PLZL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SBER/PLZL_2025</t>
+          <t>GMKN_2024/PLZL_2025</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F5" t="n">
-        <v>421.5674</v>
+        <v>5.7386</v>
       </c>
       <c r="G5" t="n">
-        <v>438.3511</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2116</v>
+        <v>15.7277</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>13.0408</v>
       </c>
       <c r="J5" t="n">
         <v>100000</v>
       </c>
       <c r="K5" t="n">
-        <v>141701.39</v>
+        <v>162357.55</v>
       </c>
       <c r="L5" t="n">
-        <v>6146.32</v>
+        <v>15787.14</v>
       </c>
       <c r="M5" t="n">
-        <v>2188.88</v>
+        <v>4876.75</v>
       </c>
       <c r="N5" t="n">
-        <v>133366.19</v>
+        <v>141693.65</v>
       </c>
       <c r="O5" t="n">
-        <v>33.37</v>
+        <v>41.69</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>438.3511 SBER</t>
+          <t>13.0408 PLZL_2025</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>237.21</v>
+        <v>7093</v>
       </c>
       <c r="R5" t="n">
-        <v>323.26</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="6">
@@ -1875,13 +1875,13 @@
         <v>170</v>
       </c>
       <c r="F6" t="n">
-        <v>217.6279</v>
+        <v>218.6748</v>
       </c>
       <c r="G6" t="n">
-        <v>262.3388</v>
+        <v>263.4406</v>
       </c>
       <c r="H6" t="n">
-        <v>14.1747</v>
+        <v>14.2343</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1890,27 +1890,27 @@
         <v>100000</v>
       </c>
       <c r="K6" t="n">
-        <v>140246.33</v>
+        <v>140835.33</v>
       </c>
       <c r="L6" t="n">
-        <v>8361.549999999999</v>
+        <v>8459.450000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>3067.02</v>
+        <v>3080.09</v>
       </c>
       <c r="N6" t="n">
-        <v>128817.76</v>
+        <v>129295.79</v>
       </c>
       <c r="O6" t="n">
-        <v>28.82</v>
+        <v>29.3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>262.3388 ROSN</t>
+          <t>263.4406 ROSN</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459.5</v>
+        <v>457.3</v>
       </c>
       <c r="R6" t="n">
         <v>534.6</v>
@@ -1924,60 +1924,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>PLZL/SBERP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>PLZL_2025/SBERP</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="F7" t="n">
-        <v>997.4067</v>
+        <v>14.0984</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>492.7378</v>
+        <v>459.0191</v>
       </c>
       <c r="I7" t="n">
-        <v>501.2501</v>
+        <v>407.3089</v>
       </c>
       <c r="J7" t="n">
         <v>100000</v>
       </c>
       <c r="K7" t="n">
-        <v>143006.65</v>
+        <v>130314.41</v>
       </c>
       <c r="L7" t="n">
-        <v>11578.1</v>
+        <v>5883.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3745.91</v>
+        <v>3233.55</v>
       </c>
       <c r="N7" t="n">
-        <v>127682.64</v>
+        <v>121197.01</v>
       </c>
       <c r="O7" t="n">
-        <v>27.68</v>
+        <v>21.2</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>501.2501 SBERP</t>
+          <t>407.3089 SBERP</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="R7" t="n">
-        <v>285.3</v>
+        <v>319.94</v>
       </c>
     </row>
     <row r="8">
@@ -1988,60 +1988,60 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLZL/SBERP</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PLZL_2025/SBERP</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>14.0115</v>
+        <v>1000.6004</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>456.5439</v>
+        <v>482.3425</v>
       </c>
       <c r="I8" t="n">
-        <v>405.1126</v>
+        <v>468.2323</v>
       </c>
       <c r="J8" t="n">
         <v>100000</v>
       </c>
       <c r="K8" t="n">
-        <v>129611.71</v>
+        <v>131348.52</v>
       </c>
       <c r="L8" t="n">
-        <v>5771.51</v>
+        <v>9737.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3215.87</v>
+        <v>2872.88</v>
       </c>
       <c r="N8" t="n">
-        <v>120624.33</v>
+        <v>118738.06</v>
       </c>
       <c r="O8" t="n">
-        <v>20.62</v>
+        <v>18.74</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>405.1126 SBERP</t>
+          <t>468.2323 SBERP</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="R8" t="n">
-        <v>319.94</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="9">
@@ -2067,45 +2067,45 @@
         <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>217.6279</v>
+        <v>218.6748</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>459.0362</v>
+        <v>458.3818</v>
       </c>
       <c r="I9" t="n">
-        <v>459.3615</v>
+        <v>459.0901</v>
       </c>
       <c r="J9" t="n">
         <v>100000</v>
       </c>
       <c r="K9" t="n">
-        <v>131055.82</v>
+        <v>128783.96</v>
       </c>
       <c r="L9" t="n">
-        <v>8811.110000000001</v>
+        <v>8797.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3468.22</v>
+        <v>3467.95</v>
       </c>
       <c r="N9" t="n">
-        <v>118776.5</v>
+        <v>116518.66</v>
       </c>
       <c r="O9" t="n">
-        <v>18.78</v>
+        <v>16.52</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>459.3615 SBERP</t>
+          <t>459.0901 SBERP</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="R9" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="10">
@@ -2131,13 +2131,13 @@
         <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7399</v>
+        <v>5.7386</v>
       </c>
       <c r="G10" t="n">
-        <v>9.5708</v>
+        <v>9.568899999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>986.9544</v>
+        <v>986.756</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2146,27 +2146,27 @@
         <v>100000</v>
       </c>
       <c r="K10" t="n">
-        <v>144078.47</v>
+        <v>144049.51</v>
       </c>
       <c r="L10" t="n">
-        <v>20631.34</v>
+        <v>20624.18</v>
       </c>
       <c r="M10" t="n">
-        <v>6975.28</v>
+        <v>6973.87</v>
       </c>
       <c r="N10" t="n">
-        <v>116471.85</v>
+        <v>116451.45</v>
       </c>
       <c r="O10" t="n">
-        <v>16.47</v>
+        <v>16.45</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9.5708 GMKN_2024</t>
+          <t>9.5689 GMKN_2024</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>17422</v>
+        <v>17426</v>
       </c>
       <c r="R10" t="n">
         <v>15054</v>
@@ -2195,13 +2195,13 @@
         <v>150</v>
       </c>
       <c r="F11" t="n">
-        <v>217.6279</v>
+        <v>218.6748</v>
       </c>
       <c r="G11" t="n">
-        <v>358.7162</v>
+        <v>360.2244</v>
       </c>
       <c r="H11" t="n">
-        <v>926.6310999999999</v>
+        <v>930.527</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2210,30 +2210,30 @@
         <v>100000</v>
       </c>
       <c r="K11" t="n">
-        <v>133675.58</v>
+        <v>128474.02</v>
       </c>
       <c r="L11" t="n">
-        <v>17089.87</v>
+        <v>17224.58</v>
       </c>
       <c r="M11" t="n">
-        <v>6494.67</v>
+        <v>6522.17</v>
       </c>
       <c r="N11" t="n">
-        <v>110091.03</v>
+        <v>104727.27</v>
       </c>
       <c r="O11" t="n">
-        <v>10.09</v>
+        <v>4.73</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>358.7162 ROSN</t>
+          <t>360.2244 ROSN</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459.5</v>
+        <v>457.3</v>
       </c>
       <c r="R11" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="12">
@@ -2244,60 +2244,60 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PLZL_2025/TATNP</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>14.0115</v>
+        <v>463.4135</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>140.1006</v>
+        <v>146.4755</v>
       </c>
       <c r="I12" t="n">
-        <v>173.3439</v>
+        <v>159.5335</v>
       </c>
       <c r="J12" t="n">
         <v>100000</v>
       </c>
       <c r="K12" t="n">
-        <v>113384.27</v>
+        <v>95241.47</v>
       </c>
       <c r="L12" t="n">
-        <v>4118.98</v>
+        <v>2262.44</v>
       </c>
       <c r="M12" t="n">
-        <v>1717.8</v>
+        <v>994.77</v>
       </c>
       <c r="N12" t="n">
-        <v>107547.48</v>
+        <v>91984.25</v>
       </c>
       <c r="O12" t="n">
-        <v>7.55</v>
+        <v>-8.02</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>173.3439 TATNP</t>
+          <t>159.5335 TATNP</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="R12" t="n">
-        <v>654.1</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13">
@@ -2308,28 +2308,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GMKN_2024/TATNP</t>
+          <t>GMKN_2024/ROSN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7399</v>
+        <v>5.7386</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2482</v>
+        <v>6.3844</v>
       </c>
       <c r="H13" t="n">
-        <v>147.8718</v>
+        <v>243.6033</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2338,27 +2338,27 @@
         <v>100000</v>
       </c>
       <c r="K13" t="n">
-        <v>109113.9</v>
+        <v>96110.63</v>
       </c>
       <c r="L13" t="n">
-        <v>1418.67</v>
+        <v>7567.31</v>
       </c>
       <c r="M13" t="n">
-        <v>641.1799999999999</v>
+        <v>3188.85</v>
       </c>
       <c r="N13" t="n">
-        <v>107054.05</v>
+        <v>85354.47</v>
       </c>
       <c r="O13" t="n">
-        <v>7.05</v>
+        <v>-14.65</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7.2482 GMKN_2024</t>
+          <t>6.3844 GMKN_2024</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>17422</v>
+        <v>17426</v>
       </c>
       <c r="R13" t="n">
         <v>15054</v>
@@ -2372,60 +2372,60 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>GMKN_2024/SBERP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="F14" t="n">
-        <v>465.0298</v>
+        <v>5.7386</v>
       </c>
       <c r="G14" t="n">
+        <v>5.5402</v>
+      </c>
+      <c r="H14" t="n">
+        <v>485.5938</v>
+      </c>
+      <c r="I14" t="n">
         <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>148.8913</v>
-      </c>
-      <c r="I14" t="n">
-        <v>161.948</v>
       </c>
       <c r="J14" t="n">
         <v>100000</v>
       </c>
       <c r="K14" t="n">
-        <v>98172.89999999999</v>
+        <v>83402.85000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2522.5</v>
+        <v>5604.18</v>
       </c>
       <c r="M14" t="n">
-        <v>1007.54</v>
+        <v>2178.89</v>
       </c>
       <c r="N14" t="n">
-        <v>94642.86</v>
+        <v>75619.77</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.36</v>
+        <v>-24.38</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>161.9480 TATNP</t>
+          <t>5.5402 GMKN_2024</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665</v>
+        <v>17426</v>
       </c>
       <c r="R14" t="n">
-        <v>606.2</v>
+        <v>15054</v>
       </c>
     </row>
     <row r="15">
@@ -2436,57 +2436,57 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>SBER/GMKN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GMKN_2024/ROSN</t>
+          <t>SBER/GMKN_2024</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7399</v>
+        <v>421.0526</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3857</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>243.6526</v>
+        <v>4.5181</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5.0131</v>
       </c>
       <c r="J15" t="n">
         <v>100000</v>
       </c>
       <c r="K15" t="n">
-        <v>96130.08</v>
+        <v>75466.98</v>
       </c>
       <c r="L15" t="n">
-        <v>7571.87</v>
+        <v>3925.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3189.51</v>
+        <v>1091.56</v>
       </c>
       <c r="N15" t="n">
-        <v>85368.71000000001</v>
+        <v>70450.28</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.63</v>
+        <v>-29.55</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>6.3857 GMKN_2024</t>
+          <t>5.0131 GMKN_2024</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>17422</v>
+        <v>17426</v>
       </c>
       <c r="R15" t="n">
         <v>15054</v>
@@ -2500,60 +2500,60 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GMKN_2024/SBERP</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>5.7399</v>
+        <v>421.0526</v>
       </c>
       <c r="G16" t="n">
-        <v>5.5414</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>485.6915</v>
+        <v>230.2109</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>222.9528</v>
       </c>
       <c r="J16" t="n">
         <v>100000</v>
       </c>
       <c r="K16" t="n">
-        <v>83419.62</v>
+        <v>79516.11</v>
       </c>
       <c r="L16" t="n">
-        <v>5608.32</v>
+        <v>6964.66</v>
       </c>
       <c r="M16" t="n">
-        <v>2179.34</v>
+        <v>2582.17</v>
       </c>
       <c r="N16" t="n">
-        <v>75631.96000000001</v>
+        <v>69969.28</v>
       </c>
       <c r="O16" t="n">
-        <v>-24.37</v>
+        <v>-30.03</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>5.5414 GMKN_2024</t>
+          <t>222.9528 ROSN</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>17422</v>
+        <v>457.3</v>
       </c>
       <c r="R16" t="n">
-        <v>15054</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="17">
@@ -2564,60 +2564,60 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>421.5674</v>
+        <v>16.4352</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>230.4571</v>
+        <v>84.1245</v>
       </c>
       <c r="I17" t="n">
-        <v>223.1912</v>
+        <v>73.8737</v>
       </c>
       <c r="J17" t="n">
         <v>100000</v>
       </c>
       <c r="K17" t="n">
-        <v>83172.21000000001</v>
+        <v>75964.33</v>
       </c>
       <c r="L17" t="n">
-        <v>6988.1</v>
+        <v>6585.98</v>
       </c>
       <c r="M17" t="n">
-        <v>2584.98</v>
+        <v>1883.27</v>
       </c>
       <c r="N17" t="n">
-        <v>73599.13</v>
+        <v>67495.09</v>
       </c>
       <c r="O17" t="n">
-        <v>-26.4</v>
+        <v>-32.5</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>223.1912 ROSN</t>
+          <t>73.8737 NVTK</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459.5</v>
+        <v>1331.6</v>
       </c>
       <c r="R17" t="n">
-        <v>372.65</v>
+        <v>1028.3</v>
       </c>
     </row>
     <row r="18">
@@ -2628,60 +2628,60 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SBER/GMKN</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SBER/GMKN_2024</t>
+          <t>SNGS/VTBR_2024</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F18" t="n">
-        <v>421.5674</v>
+        <v>2114.1649</v>
       </c>
       <c r="G18" t="n">
+        <v>2217.3241</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2344802.735</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.523</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5.0185</v>
       </c>
       <c r="J18" t="n">
         <v>100000</v>
       </c>
       <c r="K18" t="n">
-        <v>75548.56</v>
+        <v>62772.45</v>
       </c>
       <c r="L18" t="n">
-        <v>3945.55</v>
+        <v>2401.42</v>
       </c>
       <c r="M18" t="n">
-        <v>1092.78</v>
+        <v>681.46</v>
       </c>
       <c r="N18" t="n">
-        <v>70510.23</v>
+        <v>59689.57</v>
       </c>
       <c r="O18" t="n">
-        <v>-29.49</v>
+        <v>-40.31</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>5.0185 GMKN_2024</t>
+          <t>2217.3241 SNGS</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>17422</v>
+        <v>47.3</v>
       </c>
       <c r="R18" t="n">
-        <v>15054</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="19">
@@ -2692,60 +2692,60 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>GAZP/VTBR_2024</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="F19" t="n">
-        <v>16.5289</v>
+        <v>402.6738</v>
       </c>
       <c r="G19" t="n">
+        <v>368.6612</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2319733.5762</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>81.6429</v>
-      </c>
-      <c r="I19" t="n">
-        <v>71.72880000000001</v>
       </c>
       <c r="J19" t="n">
         <v>100000</v>
       </c>
       <c r="K19" t="n">
-        <v>75458.73</v>
+        <v>47092.78</v>
       </c>
       <c r="L19" t="n">
-        <v>5960.88</v>
+        <v>5445.57</v>
       </c>
       <c r="M19" t="n">
-        <v>1828.36</v>
+        <v>1450.78</v>
       </c>
       <c r="N19" t="n">
-        <v>67669.49000000001</v>
+        <v>40196.43</v>
       </c>
       <c r="O19" t="n">
-        <v>-32.33</v>
+        <v>-59.8</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>71.7288 NVTK</t>
+          <t>368.6612 GAZP</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>1351</v>
+        <v>248.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1052</v>
+        <v>127.74</v>
       </c>
     </row>
     <row r="20">
@@ -2756,28 +2756,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SNGS/VTBR_2024</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="F20" t="n">
-        <v>2092.488</v>
+        <v>402.6738</v>
       </c>
       <c r="G20" t="n">
-        <v>2197.3089</v>
+        <v>365.8279</v>
       </c>
       <c r="H20" t="n">
-        <v>2323636.7847</v>
+        <v>2333.6029</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2786,158 +2786,30 @@
         <v>100000</v>
       </c>
       <c r="K20" t="n">
-        <v>62205.82</v>
+        <v>34234.18</v>
       </c>
       <c r="L20" t="n">
-        <v>2244.8</v>
+        <v>4257.54</v>
       </c>
       <c r="M20" t="n">
-        <v>674.9</v>
+        <v>1389.5</v>
       </c>
       <c r="N20" t="n">
-        <v>59286.12</v>
+        <v>28587.13</v>
       </c>
       <c r="O20" t="n">
-        <v>-40.71</v>
+        <v>-71.41</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2197.3089 SNGS</t>
+          <t>365.8279 GAZP</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>47.79</v>
+        <v>248.34</v>
       </c>
       <c r="R20" t="n">
-        <v>28.31</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>10 лет</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GAZP/VTBR</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GAZP/VTBR_2024</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="n">
-        <v>97</v>
-      </c>
-      <c r="F21" t="n">
-        <v>397.1406</v>
-      </c>
-      <c r="G21" t="n">
-        <v>364.217</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2291769.3722</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>46525.08</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5199.71</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1432.75</v>
-      </c>
-      <c r="N21" t="n">
-        <v>39892.62</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-60.11</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>364.2170 GAZP</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>251.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>127.74</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10 лет</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>GAZP/SNGS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GAZP/SNGS</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>152</v>
-      </c>
-      <c r="F22" t="n">
-        <v>397.1406</v>
-      </c>
-      <c r="G22" t="n">
-        <v>328.3611</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2878.9742</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>31749.24</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2204.12</v>
-      </c>
-      <c r="M22" t="n">
-        <v>664.86</v>
-      </c>
-      <c r="N22" t="n">
-        <v>28880.26</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-71.12</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>328.3611 GAZP</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>251.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
     </row>
   </sheetData>
@@ -3118,60 +2990,60 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>PLZL/MOEX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>PLZL_2025/MOEX</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>205.1282</v>
+        <v>7.764</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>342.9832</v>
+        <v>579.5334</v>
       </c>
       <c r="I3" t="n">
-        <v>510.4026</v>
+        <v>668.5507</v>
       </c>
       <c r="J3" t="n">
         <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>145617.87</v>
+        <v>142461.46</v>
       </c>
       <c r="L3" t="n">
-        <v>9511.34</v>
+        <v>8647.32</v>
       </c>
       <c r="M3" t="n">
-        <v>2850.43</v>
+        <v>2760.07</v>
       </c>
       <c r="N3" t="n">
-        <v>133256.1</v>
+        <v>131054.07</v>
       </c>
       <c r="O3" t="n">
-        <v>33.26</v>
+        <v>31.05</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>510.4026 SBERP</t>
+          <t>668.5507 MOEX</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>308.3</v>
+        <v>180.77</v>
       </c>
       <c r="R3" t="n">
-        <v>285.3</v>
+        <v>213.09</v>
       </c>
     </row>
     <row r="4">
@@ -3182,60 +3054,60 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLZL/MOEX</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PLZL_2025/MOEX</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
-        <v>7.764</v>
+        <v>205.1282</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>579.5334</v>
+        <v>342.9832</v>
       </c>
       <c r="I4" t="n">
-        <v>668.5507</v>
+        <v>510.4026</v>
       </c>
       <c r="J4" t="n">
         <v>100000</v>
       </c>
       <c r="K4" t="n">
-        <v>142461.46</v>
+        <v>143178.15</v>
       </c>
       <c r="L4" t="n">
-        <v>8647.32</v>
+        <v>9511.34</v>
       </c>
       <c r="M4" t="n">
-        <v>2760.07</v>
+        <v>2850.43</v>
       </c>
       <c r="N4" t="n">
-        <v>131054.07</v>
+        <v>130816.38</v>
       </c>
       <c r="O4" t="n">
-        <v>31.05</v>
+        <v>30.82</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>668.5507 MOEX</t>
+          <t>510.4026 SBERP</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>180.77</v>
+        <v>308.3</v>
       </c>
       <c r="R4" t="n">
-        <v>213.09</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3148,7 @@
         <v>100000</v>
       </c>
       <c r="K5" t="n">
-        <v>140734.22</v>
+        <v>138279.24</v>
       </c>
       <c r="L5" t="n">
         <v>8898.290000000001</v>
@@ -3285,10 +3157,10 @@
         <v>2485.55</v>
       </c>
       <c r="N5" t="n">
-        <v>129350.38</v>
+        <v>126895.4</v>
       </c>
       <c r="O5" t="n">
-        <v>29.35</v>
+        <v>26.9</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -3299,7 +3171,7 @@
         <v>326.92</v>
       </c>
       <c r="R5" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="6">
@@ -3340,7 +3212,7 @@
         <v>100000</v>
       </c>
       <c r="K6" t="n">
-        <v>125698.3</v>
+        <v>123790.63</v>
       </c>
       <c r="L6" t="n">
         <v>7637.75</v>
@@ -3349,10 +3221,10 @@
         <v>2752</v>
       </c>
       <c r="N6" t="n">
-        <v>115308.55</v>
+        <v>113400.89</v>
       </c>
       <c r="O6" t="n">
-        <v>15.31</v>
+        <v>13.4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -3363,7 +3235,7 @@
         <v>456.5</v>
       </c>
       <c r="R6" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="7">
@@ -3468,7 +3340,7 @@
         <v>100000</v>
       </c>
       <c r="K8" t="n">
-        <v>117739.61</v>
+        <v>115952.73</v>
       </c>
       <c r="L8" t="n">
         <v>6106.98</v>
@@ -3477,10 +3349,10 @@
         <v>1901.31</v>
       </c>
       <c r="N8" t="n">
-        <v>109731.32</v>
+        <v>107944.44</v>
       </c>
       <c r="O8" t="n">
-        <v>9.73</v>
+        <v>7.94</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -3491,7 +3363,7 @@
         <v>456.5</v>
       </c>
       <c r="R8" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9">
@@ -3660,7 +3532,7 @@
         <v>100000</v>
       </c>
       <c r="K11" t="n">
-        <v>99472.13</v>
+        <v>97962.49000000001</v>
       </c>
       <c r="L11" t="n">
         <v>2037.76</v>
@@ -3669,10 +3541,10 @@
         <v>988.63</v>
       </c>
       <c r="N11" t="n">
-        <v>96445.74000000001</v>
+        <v>94936.11</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.55</v>
+        <v>-5.06</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -3683,7 +3555,7 @@
         <v>456.5</v>
       </c>
       <c r="R11" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12">
@@ -3694,60 +3566,60 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ROSN/SBERP</t>
+          <t>GMKN/MOEX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ROSN/SBERP</t>
+          <t>GMKN_2024/MOEX</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>180.9955</v>
+        <v>4.4425</v>
       </c>
       <c r="G12" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H12" t="n">
+        <v>577.342</v>
+      </c>
+      <c r="I12" t="n">
         <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>338.5598</v>
-      </c>
-      <c r="I12" t="n">
-        <v>348.2632</v>
       </c>
       <c r="J12" t="n">
         <v>100000</v>
       </c>
       <c r="K12" t="n">
-        <v>99359.48</v>
+        <v>97248.86</v>
       </c>
       <c r="L12" t="n">
-        <v>2826.23</v>
+        <v>2434.11</v>
       </c>
       <c r="M12" t="n">
-        <v>1023.45</v>
+        <v>668.7</v>
       </c>
       <c r="N12" t="n">
-        <v>95509.81</v>
+        <v>94146.05</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.49</v>
+        <v>-5.85</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>348.2632 SBERP</t>
+          <t>6.4600 GMKN_2024</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>308.3</v>
+        <v>22510</v>
       </c>
       <c r="R12" t="n">
-        <v>285.3</v>
+        <v>15054</v>
       </c>
     </row>
     <row r="13">
@@ -3758,60 +3630,60 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GMKN/MOEX</t>
+          <t>ROSN/SBERP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GMKN_2024/MOEX</t>
+          <t>ROSN/SBERP</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4425</v>
+        <v>180.9955</v>
       </c>
       <c r="G13" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>577.342</v>
+        <v>338.5598</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>348.2632</v>
       </c>
       <c r="J13" t="n">
         <v>100000</v>
       </c>
       <c r="K13" t="n">
-        <v>97248.86</v>
+        <v>97694.78999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>2434.11</v>
+        <v>2826.23</v>
       </c>
       <c r="M13" t="n">
-        <v>668.7</v>
+        <v>1023.45</v>
       </c>
       <c r="N13" t="n">
-        <v>94146.05</v>
+        <v>93845.11</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.85</v>
+        <v>-6.15</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6.4600 GMKN_2024</t>
+          <t>348.2632 SBERP</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>22510</v>
+        <v>308.3</v>
       </c>
       <c r="R13" t="n">
-        <v>15054</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="14">
@@ -4044,7 +3916,7 @@
         <v>100000</v>
       </c>
       <c r="K17" t="n">
-        <v>84897.86</v>
+        <v>83416.89</v>
       </c>
       <c r="L17" t="n">
         <v>1977.52</v>
@@ -4053,10 +3925,10 @@
         <v>659.8</v>
       </c>
       <c r="N17" t="n">
-        <v>82260.53999999999</v>
+        <v>80779.58</v>
       </c>
       <c r="O17" t="n">
-        <v>-17.74</v>
+        <v>-19.22</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -4067,7 +3939,7 @@
         <v>326.92</v>
       </c>
       <c r="R17" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="18">
@@ -4108,7 +3980,7 @@
         <v>100000</v>
       </c>
       <c r="K18" t="n">
-        <v>82559.81</v>
+        <v>81735.24000000001</v>
       </c>
       <c r="L18" t="n">
         <v>4297.13</v>
@@ -4117,10 +3989,10 @@
         <v>1768.92</v>
       </c>
       <c r="N18" t="n">
-        <v>76493.75999999999</v>
+        <v>75669.2</v>
       </c>
       <c r="O18" t="n">
-        <v>-23.51</v>
+        <v>-24.33</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -4131,7 +4003,7 @@
         <v>180.77</v>
       </c>
       <c r="R18" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="19">
@@ -4142,28 +4014,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>GMKN/PLZL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>GMKN_2024/PLZL_2025</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>553.1891000000001</v>
+        <v>4.4425</v>
       </c>
       <c r="G19" t="n">
-        <v>528.7183</v>
+        <v>5.0751</v>
       </c>
       <c r="H19" t="n">
-        <v>404.8684</v>
+        <v>7.9481</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -4172,30 +4044,30 @@
         <v>100000</v>
       </c>
       <c r="K19" t="n">
-        <v>80465.64</v>
+        <v>76401.17</v>
       </c>
       <c r="L19" t="n">
-        <v>3873.13</v>
+        <v>1066.99</v>
       </c>
       <c r="M19" t="n">
-        <v>1407</v>
+        <v>633.75</v>
       </c>
       <c r="N19" t="n">
-        <v>75185.50999999999</v>
+        <v>74700.42</v>
       </c>
       <c r="O19" t="n">
-        <v>-24.81</v>
+        <v>-25.3</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>528.7183 MOEX</t>
+          <t>5.0751 GMKN_2024</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>180.77</v>
+        <v>22510</v>
       </c>
       <c r="R19" t="n">
-        <v>152.19</v>
+        <v>15054</v>
       </c>
     </row>
     <row r="20">
@@ -4206,28 +4078,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GMKN_2024/PLZL_2025</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F20" t="n">
-        <v>4.4425</v>
+        <v>553.1891000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>5.0751</v>
+        <v>528.7183</v>
       </c>
       <c r="H20" t="n">
-        <v>7.9481</v>
+        <v>404.8684</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4236,30 +4108,30 @@
         <v>100000</v>
       </c>
       <c r="K20" t="n">
-        <v>76401.17</v>
+        <v>79661.99000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1066.99</v>
+        <v>3873.13</v>
       </c>
       <c r="M20" t="n">
-        <v>633.75</v>
+        <v>1407</v>
       </c>
       <c r="N20" t="n">
-        <v>74700.42</v>
+        <v>74381.86</v>
       </c>
       <c r="O20" t="n">
-        <v>-25.3</v>
+        <v>-25.62</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.0751 GMKN_2024</t>
+          <t>528.7183 MOEX</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>22510</v>
+        <v>180.77</v>
       </c>
       <c r="R20" t="n">
-        <v>15054</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="21">
@@ -4300,7 +4172,7 @@
         <v>100000</v>
       </c>
       <c r="K21" t="n">
-        <v>71722.25999999999</v>
+        <v>68642.81</v>
       </c>
       <c r="L21" t="n">
         <v>1821.59</v>
@@ -4309,10 +4181,10 @@
         <v>656.91</v>
       </c>
       <c r="N21" t="n">
-        <v>69243.75999999999</v>
+        <v>66164.31</v>
       </c>
       <c r="O21" t="n">
-        <v>-30.76</v>
+        <v>-33.84</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -4323,7 +4195,7 @@
         <v>552.5</v>
       </c>
       <c r="R21" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="22">
@@ -4364,7 +4236,7 @@
         <v>100000</v>
       </c>
       <c r="K22" t="n">
-        <v>69934.74000000001</v>
+        <v>66932.05</v>
       </c>
       <c r="L22" t="n">
         <v>3538.34</v>
@@ -4373,10 +4245,10 @@
         <v>709.71</v>
       </c>
       <c r="N22" t="n">
-        <v>65686.7</v>
+        <v>62684</v>
       </c>
       <c r="O22" t="n">
-        <v>-34.31</v>
+        <v>-37.32</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -4387,7 +4259,7 @@
         <v>552.5</v>
       </c>
       <c r="R22" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="23">
@@ -4428,7 +4300,7 @@
         <v>100000</v>
       </c>
       <c r="K23" t="n">
-        <v>69032.07000000001</v>
+        <v>66068.12</v>
       </c>
       <c r="L23" t="n">
         <v>3300.34</v>
@@ -4437,10 +4309,10 @@
         <v>704.21</v>
       </c>
       <c r="N23" t="n">
-        <v>65027.51</v>
+        <v>62063.57</v>
       </c>
       <c r="O23" t="n">
-        <v>-34.97</v>
+        <v>-37.94</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -4451,7 +4323,7 @@
         <v>552.5</v>
       </c>
       <c r="R23" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="24">
@@ -4620,7 +4492,7 @@
         <v>100000</v>
       </c>
       <c r="K26" t="n">
-        <v>36398.33</v>
+        <v>35227.59</v>
       </c>
       <c r="L26" t="n">
         <v>4816.56</v>
@@ -4629,10 +4501,10 @@
         <v>1442.37</v>
       </c>
       <c r="N26" t="n">
-        <v>30139.4</v>
+        <v>28968.66</v>
       </c>
       <c r="O26" t="n">
-        <v>-69.86</v>
+        <v>-71.03</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -4643,7 +4515,7 @@
         <v>325.7</v>
       </c>
       <c r="R26" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
     </row>
   </sheetData>
@@ -4775,42 +4647,42 @@
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>9.821300000000001</v>
+        <v>9.720499999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>445.1387</v>
+        <v>441.131</v>
       </c>
       <c r="I2" t="n">
-        <v>554.9099</v>
+        <v>549.9139</v>
       </c>
       <c r="J2" t="n">
         <v>100000</v>
       </c>
       <c r="K2" t="n">
-        <v>177537.88</v>
+        <v>175939.46</v>
       </c>
       <c r="L2" t="n">
-        <v>8015.42</v>
+        <v>7808.67</v>
       </c>
       <c r="M2" t="n">
-        <v>2761.67</v>
+        <v>2736.4</v>
       </c>
       <c r="N2" t="n">
-        <v>166760.79</v>
+        <v>165394.39</v>
       </c>
       <c r="O2" t="n">
-        <v>66.76000000000001</v>
+        <v>65.39</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>554.9099 SBERP</t>
+          <t>549.9139 SBERP</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>236.37</v>
+        <v>238.58</v>
       </c>
       <c r="R2" t="n">
         <v>319.94</v>
@@ -4839,13 +4711,13 @@
         <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>421.7274</v>
+        <v>415.0928</v>
       </c>
       <c r="G3" t="n">
-        <v>535.3885</v>
+        <v>527.9825</v>
       </c>
       <c r="H3" t="n">
-        <v>9.6318</v>
+        <v>9.4985</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -4854,27 +4726,27 @@
         <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>173069.68</v>
+        <v>170675.61</v>
       </c>
       <c r="L3" t="n">
-        <v>10909.21</v>
+        <v>10551.51</v>
       </c>
       <c r="M3" t="n">
-        <v>3305.73</v>
+        <v>3259.38</v>
       </c>
       <c r="N3" t="n">
-        <v>158854.73</v>
+        <v>156864.71</v>
       </c>
       <c r="O3" t="n">
-        <v>58.85</v>
+        <v>56.86</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>535.3885 SBER</t>
+          <t>527.9825 SBER</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>237.12</v>
+        <v>240.91</v>
       </c>
       <c r="R3" t="n">
         <v>323.26</v>
@@ -4903,42 +4775,42 @@
         <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>9.821300000000001</v>
+        <v>9.720499999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>875.7021999999999</v>
+        <v>867.7929</v>
       </c>
       <c r="I4" t="n">
-        <v>740.7394</v>
+        <v>734.0491</v>
       </c>
       <c r="J4" t="n">
         <v>100000</v>
       </c>
       <c r="K4" t="n">
-        <v>157844.16</v>
+        <v>156418.52</v>
       </c>
       <c r="L4" t="n">
-        <v>11191.32</v>
+        <v>10955.22</v>
       </c>
       <c r="M4" t="n">
-        <v>3036.79</v>
+        <v>3008.95</v>
       </c>
       <c r="N4" t="n">
-        <v>143616.05</v>
+        <v>142454.35</v>
       </c>
       <c r="O4" t="n">
-        <v>43.62</v>
+        <v>42.45</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>740.7394 MOEX</t>
+          <t>734.0491 MOEX</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>119.98</v>
+        <v>121.53</v>
       </c>
       <c r="R4" t="n">
         <v>213.09</v>
@@ -4967,13 +4839,13 @@
         <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>210.5263</v>
+        <v>211.4165</v>
       </c>
       <c r="G5" t="n">
-        <v>197.7436</v>
+        <v>198.4782</v>
       </c>
       <c r="H5" t="n">
-        <v>10.2393</v>
+        <v>10.2774</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4982,27 +4854,27 @@
         <v>100000</v>
       </c>
       <c r="K5" t="n">
-        <v>137214.29</v>
+        <v>137723.99</v>
       </c>
       <c r="L5" t="n">
-        <v>7186.48</v>
+        <v>7268.71</v>
       </c>
       <c r="M5" t="n">
-        <v>2297.79</v>
+        <v>2306.49</v>
       </c>
       <c r="N5" t="n">
-        <v>127730.02</v>
+        <v>128148.79</v>
       </c>
       <c r="O5" t="n">
-        <v>27.73</v>
+        <v>28.15</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>197.7436 TATN</t>
+          <t>198.4782 TATN</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="R5" t="n">
         <v>693.9</v>
@@ -5031,45 +4903,45 @@
         <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>210.5263</v>
+        <v>211.4165</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>440.5148</v>
+        <v>442.1512</v>
       </c>
       <c r="I6" t="n">
-        <v>477.7582</v>
+        <v>479.5329</v>
       </c>
       <c r="J6" t="n">
         <v>100000</v>
       </c>
       <c r="K6" t="n">
-        <v>136304.41</v>
+        <v>134518.56</v>
       </c>
       <c r="L6" t="n">
-        <v>7951.65</v>
+        <v>8036.72</v>
       </c>
       <c r="M6" t="n">
-        <v>2697.17</v>
+        <v>2707.35</v>
       </c>
       <c r="N6" t="n">
-        <v>125655.6</v>
+        <v>123774.49</v>
       </c>
       <c r="O6" t="n">
-        <v>25.66</v>
+        <v>23.77</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>477.7582 SBERP</t>
+          <t>479.5329 SBERP</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>236.37</v>
+        <v>238.58</v>
       </c>
       <c r="R6" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="7">
@@ -5080,28 +4952,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>ROSN/PLZL_2025</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>421.7274</v>
+        <v>216.4034</v>
       </c>
       <c r="G7" t="n">
-        <v>477.9723</v>
+        <v>246.3916</v>
       </c>
       <c r="H7" t="n">
-        <v>213.5479</v>
+        <v>9.6624</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5110,30 +4982,30 @@
         <v>100000</v>
       </c>
       <c r="K7" t="n">
-        <v>136179.08</v>
+        <v>131720.95</v>
       </c>
       <c r="L7" t="n">
-        <v>8223.76</v>
+        <v>6555.27</v>
       </c>
       <c r="M7" t="n">
-        <v>3055.08</v>
+        <v>2243.95</v>
       </c>
       <c r="N7" t="n">
-        <v>124900.25</v>
+        <v>122921.74</v>
       </c>
       <c r="O7" t="n">
-        <v>24.9</v>
+        <v>22.92</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>477.9723 SBER</t>
+          <t>246.3916 ROSN</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>237.12</v>
+        <v>462.1</v>
       </c>
       <c r="R7" t="n">
-        <v>284.91</v>
+        <v>534.6</v>
       </c>
     </row>
     <row r="8">
@@ -5144,28 +5016,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ROSN/PLZL_2025</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>218.0549</v>
+        <v>415.0928</v>
       </c>
       <c r="G8" t="n">
-        <v>248.0359</v>
+        <v>471.391</v>
       </c>
       <c r="H8" t="n">
-        <v>9.726900000000001</v>
+        <v>210.6076</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -5174,30 +5046,30 @@
         <v>100000</v>
       </c>
       <c r="K8" t="n">
-        <v>132599.98</v>
+        <v>131961.2</v>
       </c>
       <c r="L8" t="n">
-        <v>6698.77</v>
+        <v>7904.69</v>
       </c>
       <c r="M8" t="n">
-        <v>2259.23</v>
+        <v>3012.39</v>
       </c>
       <c r="N8" t="n">
-        <v>123641.98</v>
+        <v>121044.13</v>
       </c>
       <c r="O8" t="n">
-        <v>23.64</v>
+        <v>21.04</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>248.0359 ROSN</t>
+          <t>471.3910 SBER</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458.6</v>
+        <v>240.91</v>
       </c>
       <c r="R8" t="n">
-        <v>534.6</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="9">
@@ -5217,51 +5089,51 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>833.4722</v>
+        <v>822.8421</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>220.3314</v>
+        <v>209.118</v>
       </c>
       <c r="I9" t="n">
-        <v>216.9121</v>
+        <v>199.7079</v>
       </c>
       <c r="J9" t="n">
         <v>100000</v>
       </c>
       <c r="K9" t="n">
-        <v>131492.12</v>
+        <v>119225.63</v>
       </c>
       <c r="L9" t="n">
-        <v>7597.41</v>
+        <v>5720.11</v>
       </c>
       <c r="M9" t="n">
-        <v>1934.04</v>
+        <v>1181.25</v>
       </c>
       <c r="N9" t="n">
-        <v>121960.67</v>
+        <v>112324.27</v>
       </c>
       <c r="O9" t="n">
-        <v>21.96</v>
+        <v>12.32</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>216.9121 TATNP</t>
+          <t>199.7079 TATNP</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="R9" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10">
@@ -5281,48 +5153,48 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>9.821300000000001</v>
+        <v>9.720499999999999</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>219.2963</v>
+        <v>210.567</v>
       </c>
       <c r="I10" t="n">
-        <v>179.8244</v>
+        <v>178.3034</v>
       </c>
       <c r="J10" t="n">
         <v>100000</v>
       </c>
       <c r="K10" t="n">
-        <v>117623.13</v>
+        <v>116628.28</v>
       </c>
       <c r="L10" t="n">
-        <v>5005.11</v>
+        <v>4189.51</v>
       </c>
       <c r="M10" t="n">
-        <v>1828.35</v>
+        <v>1049.76</v>
       </c>
       <c r="N10" t="n">
-        <v>110789.66</v>
+        <v>111389.01</v>
       </c>
       <c r="O10" t="n">
-        <v>10.79</v>
+        <v>11.39</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>179.8244 TATNP</t>
+          <t>178.3034 TATNP</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="R10" t="n">
         <v>654.1</v>
@@ -5351,45 +5223,45 @@
         <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>421.7274</v>
+        <v>415.0928</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>215.0021</v>
+        <v>212.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>197.8178</v>
+        <v>195.094</v>
       </c>
       <c r="J11" t="n">
         <v>100000</v>
       </c>
       <c r="K11" t="n">
-        <v>119917.15</v>
+        <v>116471.13</v>
       </c>
       <c r="L11" t="n">
-        <v>6596.1</v>
+        <v>6299.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2604.46</v>
+        <v>2567.98</v>
       </c>
       <c r="N11" t="n">
-        <v>110716.59</v>
+        <v>107603.72</v>
       </c>
       <c r="O11" t="n">
-        <v>10.72</v>
+        <v>7.6</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>197.8178 TATNP</t>
+          <t>195.0940 TATNP</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="R11" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12">
@@ -5415,45 +5287,45 @@
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>423.0655</v>
+        <v>419.1466</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>213.0257</v>
+        <v>211.3009</v>
       </c>
       <c r="I12" t="n">
-        <v>187.9596</v>
+        <v>186.4378</v>
       </c>
       <c r="J12" t="n">
         <v>100000</v>
       </c>
       <c r="K12" t="n">
-        <v>113941.12</v>
+        <v>111303.35</v>
       </c>
       <c r="L12" t="n">
-        <v>5424.86</v>
+        <v>5259.9</v>
       </c>
       <c r="M12" t="n">
-        <v>1819.75</v>
+        <v>1804.65</v>
       </c>
       <c r="N12" t="n">
-        <v>106696.5</v>
+        <v>104238.79</v>
       </c>
       <c r="O12" t="n">
-        <v>6.7</v>
+        <v>4.24</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>187.9596 TATNP</t>
+          <t>186.4378 TATNP</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="R12" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13">
@@ -5494,7 +5366,7 @@
         <v>100000</v>
       </c>
       <c r="K13" t="n">
-        <v>101912.96</v>
+        <v>101003.3</v>
       </c>
       <c r="L13" t="n">
         <v>3305.38</v>
@@ -5503,10 +5375,10 @@
         <v>1371.45</v>
       </c>
       <c r="N13" t="n">
-        <v>97236.14</v>
+        <v>96326.48</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.76</v>
+        <v>-3.67</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -5517,7 +5389,7 @@
         <v>152.96</v>
       </c>
       <c r="R13" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="14">
@@ -5558,7 +5430,7 @@
         <v>100000</v>
       </c>
       <c r="K14" t="n">
-        <v>98085.98</v>
+        <v>97210.48</v>
       </c>
       <c r="L14" t="n">
         <v>3540.35</v>
@@ -5567,10 +5439,10 @@
         <v>1364.9</v>
       </c>
       <c r="N14" t="n">
-        <v>93180.73</v>
+        <v>92305.23</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.82</v>
+        <v>-7.69</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -5581,7 +5453,7 @@
         <v>152.96</v>
       </c>
       <c r="R14" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="15">
@@ -5622,7 +5494,7 @@
         <v>100000</v>
       </c>
       <c r="K15" t="n">
-        <v>95773.10000000001</v>
+        <v>94918.24000000001</v>
       </c>
       <c r="L15" t="n">
         <v>2160.94</v>
@@ -5631,10 +5503,10 @@
         <v>987.22</v>
       </c>
       <c r="N15" t="n">
-        <v>92624.94</v>
+        <v>91770.08</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.38</v>
+        <v>-8.23</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -5645,7 +5517,7 @@
         <v>152.96</v>
       </c>
       <c r="R15" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="16">
@@ -5668,48 +5540,48 @@
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>210.5263</v>
+        <v>211.4165</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>861.1061999999999</v>
+        <v>864.3048</v>
       </c>
       <c r="I16" t="n">
-        <v>663.1543</v>
+        <v>665.6176</v>
       </c>
       <c r="J16" t="n">
         <v>100000</v>
       </c>
       <c r="K16" t="n">
-        <v>100925.45</v>
+        <v>100288.61</v>
       </c>
       <c r="L16" t="n">
-        <v>8682.18</v>
+        <v>8769.959999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>2866.05</v>
+        <v>2876.86</v>
       </c>
       <c r="N16" t="n">
-        <v>89377.22</v>
+        <v>88641.78999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.62</v>
+        <v>-11.36</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>663.1543 MOEX</t>
+          <t>665.6176 MOEX</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>119.98</v>
+        <v>121.53</v>
       </c>
       <c r="R16" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="17">
@@ -5720,28 +5592,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>833.4722</v>
+        <v>653.7657</v>
       </c>
       <c r="G17" t="n">
-        <v>653.0774</v>
+        <v>685.7873</v>
       </c>
       <c r="H17" t="n">
-        <v>439.9801</v>
+        <v>186.4139</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5750,30 +5622,30 @@
         <v>100000</v>
       </c>
       <c r="K17" t="n">
-        <v>99391.85000000001</v>
+        <v>88329.39999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>8505.950000000001</v>
+        <v>1439.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3124.69</v>
+        <v>651.1</v>
       </c>
       <c r="N17" t="n">
-        <v>87761.21000000001</v>
+        <v>86238.38</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.24</v>
+        <v>-13.76</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>653.0774 MOEX</t>
+          <t>685.7873 GMKN</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>119.98</v>
+        <v>152.96</v>
       </c>
       <c r="R17" t="n">
-        <v>152.19</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="18">
@@ -5784,28 +5656,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>653.7657</v>
+        <v>822.8421</v>
       </c>
       <c r="G18" t="n">
-        <v>685.7873</v>
+        <v>645.7491</v>
       </c>
       <c r="H18" t="n">
-        <v>186.4139</v>
+        <v>435.043</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -5814,30 +5686,30 @@
         <v>100000</v>
       </c>
       <c r="K18" t="n">
-        <v>89124.91</v>
+        <v>97295.00999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1439.92</v>
+        <v>8242.75</v>
       </c>
       <c r="M18" t="n">
-        <v>651.1</v>
+        <v>3089.12</v>
       </c>
       <c r="N18" t="n">
-        <v>87033.89</v>
+        <v>85963.14</v>
       </c>
       <c r="O18" t="n">
-        <v>-12.97</v>
+        <v>-14.04</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>685.7873 GMKN</t>
+          <t>645.7491 MOEX</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>152.96</v>
+        <v>121.53</v>
       </c>
       <c r="R18" t="n">
-        <v>129.96</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="19">
@@ -5848,60 +5720,60 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>421.7274</v>
+        <v>653.7657</v>
       </c>
       <c r="G19" t="n">
+        <v>675.7841</v>
+      </c>
+      <c r="H19" t="n">
+        <v>149.8694</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>826.653</v>
-      </c>
-      <c r="I19" t="n">
-        <v>632.6605</v>
       </c>
       <c r="J19" t="n">
         <v>100000</v>
       </c>
       <c r="K19" t="n">
-        <v>96284.60000000001</v>
+        <v>87040.99000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>7724.08</v>
+        <v>1548.1</v>
       </c>
       <c r="M19" t="n">
-        <v>2700.36</v>
+        <v>653.6</v>
       </c>
       <c r="N19" t="n">
-        <v>85860.16</v>
+        <v>84839.28</v>
       </c>
       <c r="O19" t="n">
-        <v>-14.14</v>
+        <v>-15.16</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>632.6605 MOEX</t>
+          <t>675.7841 GMKN</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>119.98</v>
+        <v>152.96</v>
       </c>
       <c r="R19" t="n">
-        <v>152.19</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="20">
@@ -5912,60 +5784,60 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
-        <v>653.7657</v>
+        <v>415.0928</v>
       </c>
       <c r="G20" t="n">
-        <v>675.7841</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>149.8694</v>
+        <v>815.1744</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>623.8755</v>
       </c>
       <c r="J20" t="n">
         <v>100000</v>
       </c>
       <c r="K20" t="n">
-        <v>87824.89999999999</v>
+        <v>93999.33</v>
       </c>
       <c r="L20" t="n">
-        <v>1548.1</v>
+        <v>7409.24</v>
       </c>
       <c r="M20" t="n">
-        <v>653.6</v>
+        <v>2662.24</v>
       </c>
       <c r="N20" t="n">
-        <v>85623.19</v>
+        <v>83927.84</v>
       </c>
       <c r="O20" t="n">
-        <v>-14.38</v>
+        <v>-16.07</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>675.7841 GMKN</t>
+          <t>623.8755 MOEX</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>152.96</v>
+        <v>121.53</v>
       </c>
       <c r="R20" t="n">
-        <v>129.96</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="21">
@@ -5991,13 +5863,13 @@
         <v>66</v>
       </c>
       <c r="F21" t="n">
-        <v>218.0549</v>
+        <v>216.4034</v>
       </c>
       <c r="G21" t="n">
-        <v>241.4342</v>
+        <v>239.8175</v>
       </c>
       <c r="H21" t="n">
-        <v>859.7957</v>
+        <v>854.0382</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -6006,30 +5878,30 @@
         <v>100000</v>
       </c>
       <c r="K21" t="n">
-        <v>89970.47</v>
+        <v>85530.91</v>
       </c>
       <c r="L21" t="n">
-        <v>6264.94</v>
+        <v>6122.88</v>
       </c>
       <c r="M21" t="n">
-        <v>1532.9</v>
+        <v>1522.33</v>
       </c>
       <c r="N21" t="n">
-        <v>82172.63</v>
+        <v>77885.7</v>
       </c>
       <c r="O21" t="n">
-        <v>-17.83</v>
+        <v>-22.11</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>241.4342 ROSN</t>
+          <t>239.8175 ROSN</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="R21" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="22">
@@ -6055,13 +5927,13 @@
         <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>218.0549</v>
+        <v>216.4034</v>
       </c>
       <c r="G22" t="n">
-        <v>230.6615</v>
+        <v>229.1017</v>
       </c>
       <c r="H22" t="n">
-        <v>193.0584</v>
+        <v>191.7528</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -6070,30 +5942,30 @@
         <v>100000</v>
       </c>
       <c r="K22" t="n">
-        <v>85956.03</v>
+        <v>81709.11</v>
       </c>
       <c r="L22" t="n">
-        <v>4983.59</v>
+        <v>4848.8</v>
       </c>
       <c r="M22" t="n">
-        <v>779.02</v>
+        <v>773.45</v>
       </c>
       <c r="N22" t="n">
-        <v>80193.41</v>
+        <v>76086.87</v>
       </c>
       <c r="O22" t="n">
-        <v>-19.81</v>
+        <v>-23.91</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>230.6615 ROSN</t>
+          <t>229.1017 ROSN</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="R22" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="23">
@@ -6104,60 +5976,60 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>421.7274</v>
+        <v>216.4034</v>
       </c>
       <c r="G23" t="n">
+        <v>219.0022</v>
+      </c>
+      <c r="H23" t="n">
+        <v>191.6004</v>
+      </c>
+      <c r="I23" t="n">
         <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>199.8448</v>
-      </c>
-      <c r="I23" t="n">
-        <v>225.282</v>
       </c>
       <c r="J23" t="n">
         <v>100000</v>
       </c>
       <c r="K23" t="n">
-        <v>83951.33</v>
+        <v>78107.13</v>
       </c>
       <c r="L23" t="n">
-        <v>4256.42</v>
+        <v>4296.95</v>
       </c>
       <c r="M23" t="n">
-        <v>1797.94</v>
+        <v>760.71</v>
       </c>
       <c r="N23" t="n">
-        <v>77896.97</v>
+        <v>73049.47</v>
       </c>
       <c r="O23" t="n">
-        <v>-22.1</v>
+        <v>-26.95</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>225.2820 ROSN</t>
+          <t>219.0022 ROSN</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="R23" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="24">
@@ -6168,28 +6040,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F24" t="n">
-        <v>218.0549</v>
+        <v>3660.9921</v>
       </c>
       <c r="G24" t="n">
-        <v>220.4933</v>
+        <v>4602.2693</v>
       </c>
       <c r="H24" t="n">
-        <v>192.9049</v>
+        <v>1134.9651</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -6198,30 +6070,30 @@
         <v>100000</v>
       </c>
       <c r="K24" t="n">
-        <v>82166.83</v>
+        <v>74096.53</v>
       </c>
       <c r="L24" t="n">
-        <v>4428</v>
+        <v>1694.49</v>
       </c>
       <c r="M24" t="n">
-        <v>766.2</v>
+        <v>655.49</v>
       </c>
       <c r="N24" t="n">
-        <v>76972.64</v>
+        <v>71746.56</v>
       </c>
       <c r="O24" t="n">
-        <v>-23.03</v>
+        <v>-28.25</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>220.4933 ROSN</t>
+          <t>4602.2693 SNGS</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458.6</v>
+        <v>27.32</v>
       </c>
       <c r="R24" t="n">
-        <v>372.65</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="25">
@@ -6232,28 +6104,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F25" t="n">
-        <v>3660.9921</v>
+        <v>838.3635</v>
       </c>
       <c r="G25" t="n">
-        <v>4602.2693</v>
+        <v>817.4186</v>
       </c>
       <c r="H25" t="n">
-        <v>1134.9651</v>
+        <v>1119.5521</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -6262,30 +6134,30 @@
         <v>100000</v>
       </c>
       <c r="K25" t="n">
-        <v>76305.62</v>
+        <v>76494.03</v>
       </c>
       <c r="L25" t="n">
-        <v>1694.49</v>
+        <v>3987.86</v>
       </c>
       <c r="M25" t="n">
-        <v>655.49</v>
+        <v>1402.26</v>
       </c>
       <c r="N25" t="n">
-        <v>73955.64999999999</v>
+        <v>71103.89999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-26.04</v>
+        <v>-28.9</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4602.2693 SNGS</t>
+          <t>817.4186 GAZP</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>27.32</v>
+        <v>119.28</v>
       </c>
       <c r="R25" t="n">
-        <v>16.58</v>
+        <v>93.58</v>
       </c>
     </row>
     <row r="26">
@@ -6305,19 +6177,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>46</v>
       </c>
       <c r="F26" t="n">
-        <v>218.0549</v>
+        <v>216.4034</v>
       </c>
       <c r="G26" t="n">
-        <v>209.2189</v>
+        <v>213.8388</v>
       </c>
       <c r="H26" t="n">
-        <v>439.293</v>
+        <v>436.7798</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -6326,30 +6198,30 @@
         <v>100000</v>
       </c>
       <c r="K26" t="n">
-        <v>77965.41</v>
+        <v>76265.60000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>3455.18</v>
+        <v>3958.91</v>
       </c>
       <c r="M26" t="n">
-        <v>730.11</v>
+        <v>1398.57</v>
       </c>
       <c r="N26" t="n">
-        <v>73780.12</v>
+        <v>70908.11</v>
       </c>
       <c r="O26" t="n">
-        <v>-26.22</v>
+        <v>-29.09</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>209.2189 ROSN</t>
+          <t>213.8388 ROSN</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="R26" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="27">
@@ -6360,60 +6232,60 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GAZP/VTBR</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GAZP/VTBR</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>46</v>
       </c>
       <c r="F27" t="n">
-        <v>838.3635</v>
+        <v>415.0928</v>
       </c>
       <c r="G27" t="n">
-        <v>817.4186</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1119.5521</v>
+        <v>202.8129</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>208.3445</v>
       </c>
       <c r="J27" t="n">
         <v>100000</v>
       </c>
       <c r="K27" t="n">
-        <v>79036.2</v>
+        <v>74306.07000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>3987.86</v>
+        <v>3424.74</v>
       </c>
       <c r="M27" t="n">
-        <v>1402.26</v>
+        <v>1037.85</v>
       </c>
       <c r="N27" t="n">
-        <v>73646.07000000001</v>
+        <v>69843.49000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-26.35</v>
+        <v>-30.16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>817.4186 GAZP</t>
+          <t>208.3445 ROSN</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>119.28</v>
+        <v>462.1</v>
       </c>
       <c r="R27" t="n">
-        <v>96.69</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="28">
@@ -6436,16 +6308,16 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>615.4982</v>
+        <v>612.8953</v>
       </c>
       <c r="G28" t="n">
-        <v>659.3444</v>
+        <v>656.8973999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>3525.1241</v>
+        <v>3512.0413</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -6454,30 +6326,30 @@
         <v>100000</v>
       </c>
       <c r="K28" t="n">
-        <v>63752.01</v>
+        <v>61472.46</v>
       </c>
       <c r="L28" t="n">
-        <v>1617.64</v>
+        <v>1556.16</v>
       </c>
       <c r="M28" t="n">
-        <v>655.91</v>
+        <v>653.3099999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>61478.45</v>
+        <v>59262.99</v>
       </c>
       <c r="O28" t="n">
-        <v>-38.52</v>
+        <v>-40.74</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>659.3444 GAZP</t>
+          <t>656.8974 GAZP</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>162.47</v>
+        <v>163.16</v>
       </c>
       <c r="R28" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
     </row>
   </sheetData>
@@ -6491,7 +6363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6594,28 +6466,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>791.7655999999999</v>
+        <v>331.4771</v>
       </c>
       <c r="G2" t="n">
-        <v>805.5644</v>
+        <v>376.287</v>
       </c>
       <c r="H2" t="n">
-        <v>48.6718</v>
+        <v>199.2137</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -6624,30 +6496,30 @@
         <v>100000</v>
       </c>
       <c r="K2" t="n">
-        <v>104691.15</v>
+        <v>105337.79</v>
       </c>
       <c r="L2" t="n">
-        <v>3582.89</v>
+        <v>3366.42</v>
       </c>
       <c r="M2" t="n">
-        <v>694.22</v>
+        <v>1368.44</v>
       </c>
       <c r="N2" t="n">
-        <v>100414.04</v>
+        <v>100602.93</v>
       </c>
       <c r="O2" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>805.5644 GMKN</t>
+          <t>376.2870 SBER</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>126.3</v>
+        <v>301.68</v>
       </c>
       <c r="R2" t="n">
-        <v>129.96</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="3">
@@ -6658,28 +6530,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>791.7655999999999</v>
+        <v>331.829</v>
       </c>
       <c r="G3" t="n">
-        <v>737.4212</v>
+        <v>370.4084</v>
       </c>
       <c r="H3" t="n">
-        <v>359.1429</v>
+        <v>196.1408</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -6688,30 +6560,30 @@
         <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>95835.25999999999</v>
+        <v>103906.97</v>
       </c>
       <c r="L3" t="n">
-        <v>2125.19</v>
+        <v>3087.56</v>
       </c>
       <c r="M3" t="n">
-        <v>674.3</v>
+        <v>1350.64</v>
       </c>
       <c r="N3" t="n">
-        <v>93035.78</v>
+        <v>99468.77</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.96</v>
+        <v>-0.53</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>737.4212 GMKN</t>
+          <t>370.4084 SBERP</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>126.3</v>
+        <v>301.36</v>
       </c>
       <c r="R3" t="n">
-        <v>129.96</v>
+        <v>280.52</v>
       </c>
     </row>
     <row r="4">
@@ -6722,28 +6594,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>GMKN/MOEX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>GMKN/MOEX</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>585.069</v>
+        <v>813.8021</v>
       </c>
       <c r="G4" t="n">
-        <v>624.5898999999999</v>
+        <v>775.8812</v>
       </c>
       <c r="H4" t="n">
-        <v>185.8861</v>
+        <v>653.6861</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -6752,30 +6624,30 @@
         <v>100000</v>
       </c>
       <c r="K4" t="n">
-        <v>95056.34</v>
+        <v>99933.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1608.5</v>
+        <v>4057.1</v>
       </c>
       <c r="M4" t="n">
-        <v>649.35</v>
+        <v>1396.53</v>
       </c>
       <c r="N4" t="n">
-        <v>92798.49000000001</v>
+        <v>94479.87</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.2</v>
+        <v>-5.52</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>624.5899 MOEX</t>
+          <t>775.8812 GMKN</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>170.92</v>
+        <v>122.88</v>
       </c>
       <c r="R4" t="n">
-        <v>152.19</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="5">
@@ -6786,28 +6658,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GMKN/MOEX</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GMKN/MOEX</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>791.7655999999999</v>
+        <v>813.8021</v>
       </c>
       <c r="G5" t="n">
-        <v>728.6724</v>
+        <v>755.4842</v>
       </c>
       <c r="H5" t="n">
-        <v>637.4161</v>
+        <v>367.94</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6816,30 +6688,30 @@
         <v>100000</v>
       </c>
       <c r="K5" t="n">
-        <v>94698.25999999999</v>
+        <v>97306.37</v>
       </c>
       <c r="L5" t="n">
-        <v>2809.56</v>
+        <v>2543.42</v>
       </c>
       <c r="M5" t="n">
-        <v>699.1900000000001</v>
+        <v>691.92</v>
       </c>
       <c r="N5" t="n">
-        <v>91189.50999999999</v>
+        <v>94071.03</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.81</v>
+        <v>-5.93</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>728.6724 GMKN</t>
+          <t>755.4842 GMKN</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="R5" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="6">
@@ -6850,60 +6722,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MOEX/SBERP</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>585.069</v>
+        <v>161.1863</v>
       </c>
       <c r="G6" t="n">
-        <v>607.0957</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>343.458</v>
+        <v>611.6786</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>631.2326</v>
       </c>
       <c r="J6" t="n">
         <v>100000</v>
       </c>
       <c r="K6" t="n">
-        <v>92393.89</v>
+        <v>95107.82000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1182.59</v>
+        <v>1869.89</v>
       </c>
       <c r="M6" t="n">
-        <v>640.42</v>
+        <v>975.1</v>
       </c>
       <c r="N6" t="n">
-        <v>90570.88</v>
+        <v>92262.82000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.43</v>
+        <v>-7.74</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>607.0957 MOEX</t>
+          <t>631.2326 MOEX</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>170.92</v>
+        <v>170.85</v>
       </c>
       <c r="R6" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="7">
@@ -6914,28 +6786,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>791.7655999999999</v>
+        <v>585.3088</v>
       </c>
       <c r="G7" t="n">
-        <v>704.3735</v>
+        <v>624.8139</v>
       </c>
       <c r="H7" t="n">
-        <v>263.6792</v>
+        <v>185.9527</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -6944,30 +6816,30 @@
         <v>100000</v>
       </c>
       <c r="K7" t="n">
-        <v>91540.38</v>
+        <v>94140.71000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>2134.91</v>
+        <v>1614.43</v>
       </c>
       <c r="M7" t="n">
-        <v>672.05</v>
+        <v>649.6</v>
       </c>
       <c r="N7" t="n">
-        <v>88733.41</v>
+        <v>91876.67</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.27</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>704.3735 GMKN</t>
+          <t>624.8139 MOEX</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>126.3</v>
+        <v>170.85</v>
       </c>
       <c r="R7" t="n">
-        <v>129.96</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="8">
@@ -6978,28 +6850,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>MOEX/SBERP</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>791.7655999999999</v>
+        <v>585.3088</v>
       </c>
       <c r="G8" t="n">
-        <v>657.9118</v>
+        <v>609.6644</v>
       </c>
       <c r="H8" t="n">
-        <v>186.9085</v>
+        <v>345.1425</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -7008,30 +6880,30 @@
         <v>100000</v>
       </c>
       <c r="K8" t="n">
-        <v>85502.21000000001</v>
+        <v>91858.14</v>
       </c>
       <c r="L8" t="n">
-        <v>1009.22</v>
+        <v>1250.62</v>
       </c>
       <c r="M8" t="n">
-        <v>632.8099999999999</v>
+        <v>641.86</v>
       </c>
       <c r="N8" t="n">
-        <v>83860.19</v>
+        <v>89965.64999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-16.14</v>
+        <v>-10.03</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>657.9118 GMKN</t>
+          <t>609.6644 MOEX</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>126.3</v>
+        <v>170.85</v>
       </c>
       <c r="R8" t="n">
-        <v>129.96</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="9">
@@ -7042,28 +6914,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ROSN/TATN</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ROSN/TATN</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>226.7574</v>
+        <v>813.8021</v>
       </c>
       <c r="G9" t="n">
-        <v>232.3546</v>
+        <v>688.9311</v>
       </c>
       <c r="H9" t="n">
-        <v>170.7951</v>
+        <v>258.3076</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7072,30 +6944,30 @@
         <v>100000</v>
       </c>
       <c r="K9" t="n">
-        <v>86586.95</v>
+        <v>88734.33</v>
       </c>
       <c r="L9" t="n">
-        <v>2364.33</v>
+        <v>1759.83</v>
       </c>
       <c r="M9" t="n">
-        <v>679.46</v>
+        <v>652.75</v>
       </c>
       <c r="N9" t="n">
-        <v>83543.16</v>
+        <v>86321.74000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-16.46</v>
+        <v>-13.68</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>232.3546 ROSN</t>
+          <t>688.9311 GMKN</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441</v>
+        <v>122.88</v>
       </c>
       <c r="R9" t="n">
-        <v>372.65</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="10">
@@ -7106,28 +6978,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>226.7574</v>
+        <v>813.8021</v>
       </c>
       <c r="G10" t="n">
-        <v>224.8892</v>
+        <v>673.9156</v>
       </c>
       <c r="H10" t="n">
-        <v>182.8177</v>
+        <v>191.4551</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -7136,30 +7008,30 @@
         <v>100000</v>
       </c>
       <c r="K10" t="n">
-        <v>83804.96000000001</v>
+        <v>86800.33</v>
       </c>
       <c r="L10" t="n">
-        <v>1779.27</v>
+        <v>1397.41</v>
       </c>
       <c r="M10" t="n">
-        <v>665.96</v>
+        <v>649.3</v>
       </c>
       <c r="N10" t="n">
-        <v>81359.73</v>
+        <v>84753.62</v>
       </c>
       <c r="O10" t="n">
-        <v>-18.64</v>
+        <v>-15.25</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>224.8892 ROSN</t>
+          <t>673.9156 GMKN</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441</v>
+        <v>122.88</v>
       </c>
       <c r="R10" t="n">
-        <v>372.65</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="11">
@@ -7179,19 +7051,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>800</v>
+        <v>814.5312</v>
       </c>
       <c r="G11" t="n">
-        <v>844.8262999999999</v>
+        <v>968.7338</v>
       </c>
       <c r="H11" t="n">
-        <v>1240.4933</v>
+        <v>1450.0259</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -7200,30 +7072,30 @@
         <v>100000</v>
       </c>
       <c r="K11" t="n">
-        <v>81686.25999999999</v>
+        <v>90654.10000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1948.83</v>
+        <v>4526.68</v>
       </c>
       <c r="M11" t="n">
-        <v>663.38</v>
+        <v>1432.96</v>
       </c>
       <c r="N11" t="n">
-        <v>79074.03999999999</v>
+        <v>84694.46000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-20.93</v>
+        <v>-15.31</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>844.8263 GAZP</t>
+          <t>968.7338 GAZP</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>125</v>
+        <v>122.77</v>
       </c>
       <c r="R11" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
     </row>
     <row r="12">
@@ -7234,28 +7106,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLZL/SBERP</t>
+          <t>ROSN/TATN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PLZL/SBERP</t>
+          <t>ROSN/TATN</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>43.2975</v>
+        <v>229.5948</v>
       </c>
       <c r="G12" t="n">
-        <v>45.5247</v>
+        <v>234.9131</v>
       </c>
       <c r="H12" t="n">
-        <v>364.2123</v>
+        <v>172.6757</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -7264,30 +7136,30 @@
         <v>100000</v>
       </c>
       <c r="K12" t="n">
-        <v>45078.53</v>
+        <v>83781.74000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1953.19</v>
+        <v>2554.96</v>
       </c>
       <c r="M12" t="n">
-        <v>670.91</v>
+        <v>687.4400000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>42454.44</v>
+        <v>80539.33</v>
       </c>
       <c r="O12" t="n">
-        <v>-57.55</v>
+        <v>-19.46</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>45.5247 PLZL</t>
+          <t>234.9131 ROSN</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>2309.6</v>
+        <v>435.55</v>
       </c>
       <c r="R12" t="n">
-        <v>990.2</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="13">
@@ -7298,28 +7170,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>43.2975</v>
+        <v>229.5948</v>
       </c>
       <c r="G13" t="n">
-        <v>43.0595</v>
+        <v>227.3654</v>
       </c>
       <c r="H13" t="n">
-        <v>193.3605</v>
+        <v>184.8307</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7328,30 +7200,30 @@
         <v>100000</v>
       </c>
       <c r="K13" t="n">
-        <v>42637.55</v>
+        <v>81089.89</v>
       </c>
       <c r="L13" t="n">
-        <v>1516.52</v>
+        <v>1963.46</v>
       </c>
       <c r="M13" t="n">
-        <v>648.65</v>
+        <v>673.79</v>
       </c>
       <c r="N13" t="n">
-        <v>40472.38</v>
+        <v>78452.63</v>
       </c>
       <c r="O13" t="n">
-        <v>-59.53</v>
+        <v>-21.55</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>43.0595 PLZL</t>
+          <t>227.3654 ROSN</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>2309.6</v>
+        <v>435.55</v>
       </c>
       <c r="R13" t="n">
-        <v>990.2</v>
+        <v>356.65</v>
       </c>
     </row>
     <row r="14">
@@ -7362,28 +7234,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLZL/MOEX</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PLZL/MOEX</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>43.2975</v>
+        <v>4515.692</v>
       </c>
       <c r="G14" t="n">
-        <v>44.6771</v>
+        <v>4957.8341</v>
       </c>
       <c r="H14" t="n">
-        <v>618.3502999999999</v>
+        <v>1207.3077</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7392,30 +7264,222 @@
         <v>100000</v>
       </c>
       <c r="K14" t="n">
-        <v>44239.23</v>
+        <v>79821.13</v>
       </c>
       <c r="L14" t="n">
-        <v>2620.47</v>
+        <v>931.13</v>
       </c>
       <c r="M14" t="n">
-        <v>1323</v>
+        <v>629.51</v>
       </c>
       <c r="N14" t="n">
-        <v>40295.76</v>
+        <v>78260.49000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-59.7</v>
+        <v>-21.74</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>44.6771 PLZL</t>
+          <t>4957.8341 SNGS</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>2309.6</v>
+        <v>22.14</v>
       </c>
       <c r="R14" t="n">
-        <v>990.2</v>
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1 год</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PLZL/SBERP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PLZL/SBERP</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.554</v>
+      </c>
+      <c r="G15" t="n">
+        <v>46.8733</v>
+      </c>
+      <c r="H15" t="n">
+        <v>358.4455</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>44679.67</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2214.49</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1311.58</v>
+      </c>
+      <c r="N15" t="n">
+        <v>41153.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-58.85</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>46.8733 PLZL</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>2296</v>
+      </c>
+      <c r="R15" t="n">
+        <v>953.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1 год</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PLZL/TATNP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PLZL/TATNP</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>43</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.554</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.231</v>
+      </c>
+      <c r="H16" t="n">
+        <v>177.0857</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>41207.76</v>
+      </c>
+      <c r="L16" t="n">
+        <v>889.9400000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>627.8200000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>39690</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-60.31</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>43.2310 PLZL</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2296</v>
+      </c>
+      <c r="R16" t="n">
+        <v>953.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1 год</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PLZL/MOEX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PLZL/MOEX</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.554</v>
+      </c>
+      <c r="G17" t="n">
+        <v>44.9082</v>
+      </c>
+      <c r="H17" t="n">
+        <v>621.5489</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>42806.46</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2711.35</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1330.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>38765.03</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-61.23</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>44.9082 PLZL</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2296</v>
+      </c>
+      <c r="R17" t="n">
+        <v>953.2</v>
       </c>
     </row>
   </sheetData>
@@ -7496,22 +7560,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>237.21</v>
+        <v>237.5</v>
       </c>
       <c r="E2" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
       <c r="F2" t="n">
-        <v>237.21</v>
+        <v>237.5</v>
       </c>
       <c r="G2" t="n">
-        <v>107.8</v>
+        <v>107.59</v>
       </c>
       <c r="H2" t="n">
-        <v>20.11</v>
+        <v>17.87</v>
       </c>
       <c r="I2" t="n">
-        <v>49.36</v>
+        <v>46.09</v>
       </c>
     </row>
     <row r="3">
@@ -7531,22 +7595,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17422</v>
+        <v>17426</v>
       </c>
       <c r="E3" t="n">
         <v>15054</v>
       </c>
       <c r="F3" t="n">
-        <v>17422</v>
+        <v>17426</v>
       </c>
       <c r="G3" t="n">
-        <v>103.49</v>
+        <v>103.45</v>
       </c>
       <c r="H3" t="n">
-        <v>-13.59</v>
+        <v>-13.61</v>
       </c>
       <c r="I3" t="n">
-        <v>16.47</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="4">
@@ -7566,22 +7630,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>459.5</v>
+        <v>457.3</v>
       </c>
       <c r="E4" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F4" t="n">
-        <v>459.5</v>
+        <v>457.3</v>
       </c>
       <c r="G4" t="n">
-        <v>84.29000000000001</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>-18.9</v>
+        <v>-22.01</v>
       </c>
       <c r="I4" t="n">
-        <v>10.09</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="5">
@@ -7601,22 +7665,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7137</v>
+        <v>7093</v>
       </c>
       <c r="E5" t="n">
         <v>12450</v>
       </c>
       <c r="F5" t="n">
-        <v>7137</v>
+        <v>7093</v>
       </c>
       <c r="G5" t="n">
-        <v>80.15000000000001</v>
+        <v>80.11</v>
       </c>
       <c r="H5" t="n">
-        <v>74.44</v>
+        <v>75.53</v>
       </c>
       <c r="I5" t="n">
-        <v>41.72</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="6">
@@ -7636,22 +7700,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100.26</v>
+        <v>99.94</v>
       </c>
       <c r="E6" t="n">
         <v>213.09</v>
       </c>
       <c r="F6" t="n">
-        <v>100.26</v>
+        <v>99.94</v>
       </c>
       <c r="G6" t="n">
-        <v>66.5</v>
+        <v>67.33</v>
       </c>
       <c r="H6" t="n">
-        <v>112.54</v>
+        <v>113.22</v>
       </c>
       <c r="I6" t="n">
-        <v>51.64</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="7">
@@ -7671,22 +7735,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="E7" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
       <c r="F7" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="G7" t="n">
-        <v>58.41</v>
+        <v>49.68</v>
       </c>
       <c r="H7" t="n">
-        <v>32.67</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>27.68</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="8">
@@ -7706,22 +7770,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="E8" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
       <c r="F8" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="G8" t="n">
-        <v>43.22</v>
+        <v>43.14</v>
       </c>
       <c r="H8" t="n">
-        <v>32.67</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>18.78</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="9">
@@ -7741,22 +7805,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>459.5</v>
+        <v>457.3</v>
       </c>
       <c r="E9" t="n">
         <v>534.6</v>
       </c>
       <c r="F9" t="n">
-        <v>459.5</v>
+        <v>457.3</v>
       </c>
       <c r="G9" t="n">
-        <v>41.46</v>
+        <v>41.99</v>
       </c>
       <c r="H9" t="n">
-        <v>16.34</v>
+        <v>16.9</v>
       </c>
       <c r="I9" t="n">
-        <v>28.82</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="10">
@@ -7767,31 +7831,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>SBER/PLZL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GMKN_2024/ROSN</t>
+          <t>SBER/PLZL_2025</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17422</v>
+        <v>237.5</v>
       </c>
       <c r="E10" t="n">
-        <v>15054</v>
+        <v>323.26</v>
       </c>
       <c r="F10" t="n">
-        <v>17422</v>
+        <v>237.5</v>
       </c>
       <c r="G10" t="n">
-        <v>36.72</v>
+        <v>40.61</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.59</v>
+        <v>36.11</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.63</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="11">
@@ -7802,31 +7866,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>GMKN_2024/ROSN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>459.5</v>
+        <v>17426</v>
       </c>
       <c r="E11" t="n">
-        <v>372.65</v>
+        <v>15054</v>
       </c>
       <c r="F11" t="n">
-        <v>459.5</v>
+        <v>17426</v>
       </c>
       <c r="G11" t="n">
-        <v>34.61</v>
+        <v>36.7</v>
       </c>
       <c r="H11" t="n">
-        <v>-18.9</v>
+        <v>-13.61</v>
       </c>
       <c r="I11" t="n">
-        <v>-26.4</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="12">
@@ -7837,31 +7901,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SBER/PLZL</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SBER/PLZL_2025</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>237.21</v>
+        <v>457.3</v>
       </c>
       <c r="E12" t="n">
-        <v>323.26</v>
+        <v>356.65</v>
       </c>
       <c r="F12" t="n">
-        <v>237.21</v>
+        <v>457.3</v>
       </c>
       <c r="G12" t="n">
-        <v>30.61</v>
+        <v>34.48</v>
       </c>
       <c r="H12" t="n">
-        <v>36.28</v>
+        <v>-22.01</v>
       </c>
       <c r="I12" t="n">
-        <v>33.37</v>
+        <v>-30.03</v>
       </c>
     </row>
     <row r="13">
@@ -7881,22 +7945,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1351</v>
+        <v>1331.6</v>
       </c>
       <c r="E13" t="n">
-        <v>1052</v>
+        <v>1028.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1351</v>
+        <v>1331.6</v>
       </c>
       <c r="G13" t="n">
-        <v>30.27</v>
+        <v>33.72</v>
       </c>
       <c r="H13" t="n">
-        <v>-22.13</v>
+        <v>-22.78</v>
       </c>
       <c r="I13" t="n">
-        <v>-32.33</v>
+        <v>-32.5</v>
       </c>
     </row>
     <row r="14">
@@ -7907,31 +7971,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GMKN_2024/SBERP</t>
+          <t>GAZP/VTBR_2024</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17422</v>
+        <v>248.34</v>
       </c>
       <c r="E14" t="n">
-        <v>15054</v>
+        <v>127.74</v>
       </c>
       <c r="F14" t="n">
-        <v>17422</v>
+        <v>248.34</v>
       </c>
       <c r="G14" t="n">
-        <v>27.57</v>
+        <v>28.1</v>
       </c>
       <c r="H14" t="n">
-        <v>-13.59</v>
+        <v>-48.56</v>
       </c>
       <c r="I14" t="n">
-        <v>-24.37</v>
+        <v>-59.8</v>
       </c>
     </row>
     <row r="15">
@@ -7942,31 +8006,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GAZP/VTBR</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GAZP/VTBR_2024</t>
+          <t>GMKN_2024/SBERP</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>251.8</v>
+        <v>17426</v>
       </c>
       <c r="E15" t="n">
-        <v>127.74</v>
+        <v>15054</v>
       </c>
       <c r="F15" t="n">
-        <v>251.8</v>
+        <v>17426</v>
       </c>
       <c r="G15" t="n">
-        <v>26.73</v>
+        <v>27.54</v>
       </c>
       <c r="H15" t="n">
-        <v>-49.27</v>
+        <v>-13.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-60.11</v>
+        <v>-24.38</v>
       </c>
     </row>
     <row r="16">
@@ -7986,22 +8050,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="E16" t="n">
         <v>319.94</v>
       </c>
       <c r="F16" t="n">
-        <v>215.04</v>
+        <v>215.79</v>
       </c>
       <c r="G16" t="n">
-        <v>26.42</v>
+        <v>27.03</v>
       </c>
       <c r="H16" t="n">
-        <v>48.78</v>
+        <v>48.26</v>
       </c>
       <c r="I16" t="n">
-        <v>20.62</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="17">
@@ -8012,31 +8076,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SBER/GMKN</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SBER/GMKN_2024</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17422</v>
+        <v>248.34</v>
       </c>
       <c r="E17" t="n">
-        <v>15054</v>
+        <v>93.58</v>
       </c>
       <c r="F17" t="n">
-        <v>17422</v>
+        <v>248.34</v>
       </c>
       <c r="G17" t="n">
-        <v>20.27</v>
+        <v>21.46</v>
       </c>
       <c r="H17" t="n">
-        <v>-13.59</v>
+        <v>-62.32</v>
       </c>
       <c r="I17" t="n">
-        <v>-29.49</v>
+        <v>-71.41</v>
       </c>
     </row>
     <row r="18">
@@ -8047,31 +8111,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>SBER/GMKN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PLZL_2025/TATNP</t>
+          <t>SBER/GMKN_2024</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>665</v>
+        <v>17426</v>
       </c>
       <c r="E18" t="n">
-        <v>654.1</v>
+        <v>15054</v>
       </c>
       <c r="F18" t="n">
-        <v>665</v>
+        <v>17426</v>
       </c>
       <c r="G18" t="n">
-        <v>20.01</v>
+        <v>20.16</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.64</v>
+        <v>-13.61</v>
       </c>
       <c r="I18" t="n">
-        <v>7.55</v>
+        <v>-29.55</v>
       </c>
     </row>
     <row r="19">
@@ -8082,31 +8146,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>GMKN_2024/TATNP</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="E19" t="n">
-        <v>606.2</v>
+        <v>711.1</v>
       </c>
       <c r="F19" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="G19" t="n">
-        <v>12.34</v>
+        <v>14.03</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.84</v>
+        <v>5.82</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.36</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="20">
@@ -8126,22 +8190,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>47.79</v>
+        <v>47.3</v>
       </c>
       <c r="E20" t="n">
         <v>28.31</v>
       </c>
       <c r="F20" t="n">
-        <v>47.79</v>
+        <v>47.3</v>
       </c>
       <c r="G20" t="n">
-        <v>11.43</v>
+        <v>12.31</v>
       </c>
       <c r="H20" t="n">
-        <v>-40.76</v>
+        <v>-40.15</v>
       </c>
       <c r="I20" t="n">
-        <v>-40.71</v>
+        <v>-40.31</v>
       </c>
     </row>
     <row r="21">
@@ -8152,31 +8216,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GAZP/SNGS</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GAZP/SNGS</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>251.8</v>
+        <v>672</v>
       </c>
       <c r="E21" t="n">
-        <v>96.69</v>
+        <v>597</v>
       </c>
       <c r="F21" t="n">
-        <v>251.8</v>
+        <v>672</v>
       </c>
       <c r="G21" t="n">
-        <v>11.22</v>
+        <v>10.89</v>
       </c>
       <c r="H21" t="n">
-        <v>-61.6</v>
+        <v>-11.16</v>
       </c>
       <c r="I21" t="n">
-        <v>-71.12</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="22">
@@ -8187,31 +8251,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>GMKN/TATN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>GMKN_2024/TATN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>665</v>
+        <v>773.9</v>
       </c>
       <c r="E22" t="n">
-        <v>606.2</v>
+        <v>711.5</v>
       </c>
       <c r="F22" t="n">
-        <v>665</v>
+        <v>773.9</v>
       </c>
       <c r="G22" t="n">
-        <v>9.529999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.84</v>
+        <v>-8.06</v>
       </c>
       <c r="I22" t="n">
-        <v>-13.23</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="23">
@@ -8231,22 +8295,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="E23" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F23" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="G23" t="n">
-        <v>7.61</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.84</v>
+        <v>-11.16</v>
       </c>
       <c r="I23" t="n">
-        <v>-12.63</v>
+        <v>-15.09</v>
       </c>
     </row>
     <row r="24">
@@ -8257,31 +8321,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GMKN_2024/TATNP</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17422</v>
+        <v>672</v>
       </c>
       <c r="E24" t="n">
-        <v>15054</v>
+        <v>597</v>
       </c>
       <c r="F24" t="n">
-        <v>17422</v>
+        <v>672</v>
       </c>
       <c r="G24" t="n">
-        <v>6.79</v>
+        <v>7.48</v>
       </c>
       <c r="H24" t="n">
-        <v>-13.59</v>
+        <v>-11.16</v>
       </c>
       <c r="I24" t="n">
-        <v>7.05</v>
+        <v>-9.640000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -8301,22 +8365,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="E25" t="n">
-        <v>632.2</v>
+        <v>623.4</v>
       </c>
       <c r="F25" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
       <c r="I25" t="n">
-        <v>-14.82</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="26">
@@ -8336,22 +8400,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="E26" t="n">
-        <v>632.2</v>
+        <v>623.4</v>
       </c>
       <c r="F26" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="G26" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="H26" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
       <c r="I26" t="n">
-        <v>-14.79</v>
+        <v>-15.7</v>
       </c>
     </row>
     <row r="27">
@@ -8362,31 +8426,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GMKN/TATN</t>
+          <t>PLZL/TATNP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GMKN_2024/TATN</t>
+          <t>PLZL_2025/TATNP</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>772.7</v>
+        <v>672</v>
       </c>
       <c r="E27" t="n">
-        <v>711.5</v>
+        <v>654.1</v>
       </c>
       <c r="F27" t="n">
-        <v>772.7</v>
+        <v>672</v>
       </c>
       <c r="G27" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.92</v>
+        <v>-2.66</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.54</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="28">
@@ -8406,22 +8470,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="E28" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F28" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="H28" t="n">
-        <v>-8.84</v>
+        <v>-11.16</v>
       </c>
       <c r="I28" t="n">
-        <v>-16.18</v>
+        <v>-17.18</v>
       </c>
     </row>
     <row r="29">
@@ -8441,22 +8505,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>237.21</v>
+        <v>237.5</v>
       </c>
       <c r="E29" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
       <c r="F29" t="n">
-        <v>237.21</v>
+        <v>237.5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>20.11</v>
+        <v>17.87</v>
       </c>
       <c r="I29" t="n">
-        <v>20.11</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="30">
@@ -8476,22 +8540,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="E30" t="n">
-        <v>632.2</v>
+        <v>623.4</v>
       </c>
       <c r="F30" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
       <c r="I30" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="31">
@@ -8511,22 +8575,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="E31" t="n">
         <v>693.9</v>
       </c>
       <c r="F31" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-10.2</v>
+        <v>-10.34</v>
       </c>
       <c r="I31" t="n">
-        <v>-10.2</v>
+        <v>-10.34</v>
       </c>
     </row>
     <row r="32">
@@ -8546,22 +8610,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="E32" t="n">
-        <v>632.2</v>
+        <v>623.4</v>
       </c>
       <c r="F32" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
       <c r="I32" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="33">
@@ -8581,22 +8645,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="E33" t="n">
-        <v>632.2</v>
+        <v>623.4</v>
       </c>
       <c r="F33" t="n">
-        <v>772.7</v>
+        <v>773.9</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
       <c r="I33" t="n">
-        <v>-18.18</v>
+        <v>-19.45</v>
       </c>
     </row>
   </sheetData>
@@ -8715,7 +8779,7 @@
         <v>308.3</v>
       </c>
       <c r="E3" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
       <c r="F3" t="n">
         <v>308.3</v>
@@ -8724,10 +8788,10 @@
         <v>48.44</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.46</v>
+        <v>-9.01</v>
       </c>
       <c r="I3" t="n">
-        <v>33.26</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="4">
@@ -8750,7 +8814,7 @@
         <v>326.92</v>
       </c>
       <c r="E4" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
       <c r="F4" t="n">
         <v>326.92</v>
@@ -8759,10 +8823,10 @@
         <v>45.68</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.85</v>
+        <v>-14.37</v>
       </c>
       <c r="I4" t="n">
-        <v>29.35</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="5">
@@ -8820,7 +8884,7 @@
         <v>456.5</v>
       </c>
       <c r="E6" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F6" t="n">
         <v>456.5</v>
@@ -8829,10 +8893,10 @@
         <v>37.97</v>
       </c>
       <c r="H6" t="n">
-        <v>32.79</v>
+        <v>30.78</v>
       </c>
       <c r="I6" t="n">
-        <v>15.31</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -8855,7 +8919,7 @@
         <v>456.5</v>
       </c>
       <c r="E7" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F7" t="n">
         <v>456.5</v>
@@ -8864,10 +8928,10 @@
         <v>32.95</v>
       </c>
       <c r="H7" t="n">
-        <v>32.79</v>
+        <v>30.78</v>
       </c>
       <c r="I7" t="n">
-        <v>22.06</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="8">
@@ -8890,7 +8954,7 @@
         <v>456.5</v>
       </c>
       <c r="E8" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F8" t="n">
         <v>456.5</v>
@@ -8899,10 +8963,10 @@
         <v>30.96</v>
       </c>
       <c r="H8" t="n">
-        <v>32.79</v>
+        <v>30.78</v>
       </c>
       <c r="I8" t="n">
-        <v>9.73</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="9">
@@ -8960,7 +9024,7 @@
         <v>325.7</v>
       </c>
       <c r="E10" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
       <c r="F10" t="n">
         <v>325.7</v>
@@ -8969,10 +9033,10 @@
         <v>24.53</v>
       </c>
       <c r="H10" t="n">
-        <v>-70.31</v>
+        <v>-71.27</v>
       </c>
       <c r="I10" t="n">
-        <v>-69.86</v>
+        <v>-71.03</v>
       </c>
     </row>
     <row r="11">
@@ -9030,7 +9094,7 @@
         <v>180.77</v>
       </c>
       <c r="E12" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
       <c r="F12" t="n">
         <v>180.77</v>
@@ -9039,10 +9103,10 @@
         <v>20.92</v>
       </c>
       <c r="H12" t="n">
-        <v>-15.81</v>
+        <v>-16.65</v>
       </c>
       <c r="I12" t="n">
-        <v>-23.51</v>
+        <v>-24.33</v>
       </c>
     </row>
     <row r="13">
@@ -9100,7 +9164,7 @@
         <v>180.77</v>
       </c>
       <c r="E14" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
       <c r="F14" t="n">
         <v>180.77</v>
@@ -9109,10 +9173,10 @@
         <v>19.23</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.81</v>
+        <v>-16.65</v>
       </c>
       <c r="I14" t="n">
-        <v>-24.81</v>
+        <v>-25.62</v>
       </c>
     </row>
     <row r="15">
@@ -9135,7 +9199,7 @@
         <v>552.5</v>
       </c>
       <c r="E15" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F15" t="n">
         <v>552.5</v>
@@ -9144,10 +9208,10 @@
         <v>18.72</v>
       </c>
       <c r="H15" t="n">
-        <v>-32.55</v>
+        <v>-35.45</v>
       </c>
       <c r="I15" t="n">
-        <v>-34.31</v>
+        <v>-37.32</v>
       </c>
     </row>
     <row r="16">
@@ -9170,7 +9234,7 @@
         <v>552.5</v>
       </c>
       <c r="E16" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F16" t="n">
         <v>552.5</v>
@@ -9179,10 +9243,10 @@
         <v>17.38</v>
       </c>
       <c r="H16" t="n">
-        <v>-32.55</v>
+        <v>-35.45</v>
       </c>
       <c r="I16" t="n">
-        <v>-34.97</v>
+        <v>-37.94</v>
       </c>
     </row>
     <row r="17">
@@ -9205,7 +9269,7 @@
         <v>308.3</v>
       </c>
       <c r="E17" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
       <c r="F17" t="n">
         <v>308.3</v>
@@ -9214,10 +9278,10 @@
         <v>14.04</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.46</v>
+        <v>-9.01</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.49</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="18">
@@ -9310,7 +9374,7 @@
         <v>326.92</v>
       </c>
       <c r="E20" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
       <c r="F20" t="n">
         <v>326.92</v>
@@ -9319,10 +9383,10 @@
         <v>9.94</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.85</v>
+        <v>-14.37</v>
       </c>
       <c r="I20" t="n">
-        <v>-17.74</v>
+        <v>-19.22</v>
       </c>
     </row>
     <row r="21">
@@ -9345,7 +9409,7 @@
         <v>456.5</v>
       </c>
       <c r="E21" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F21" t="n">
         <v>456.5</v>
@@ -9354,10 +9418,10 @@
         <v>9.619999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>32.79</v>
+        <v>30.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.55</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="22">
@@ -9380,7 +9444,7 @@
         <v>308.3</v>
       </c>
       <c r="E22" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
       <c r="F22" t="n">
         <v>308.3</v>
@@ -9389,10 +9453,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.46</v>
+        <v>-9.01</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.66</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="23">
@@ -9415,7 +9479,7 @@
         <v>552.5</v>
       </c>
       <c r="E23" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F23" t="n">
         <v>552.5</v>
@@ -9424,10 +9488,10 @@
         <v>9.06</v>
       </c>
       <c r="H23" t="n">
-        <v>-32.55</v>
+        <v>-35.45</v>
       </c>
       <c r="I23" t="n">
-        <v>-30.76</v>
+        <v>-33.84</v>
       </c>
     </row>
     <row r="24">
@@ -9520,7 +9584,7 @@
         <v>552.5</v>
       </c>
       <c r="E26" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F26" t="n">
         <v>552.5</v>
@@ -9529,10 +9593,10 @@
         <v>7.79</v>
       </c>
       <c r="H26" t="n">
-        <v>-32.55</v>
+        <v>-35.45</v>
       </c>
       <c r="I26" t="n">
-        <v>-38.59</v>
+        <v>-41.31</v>
       </c>
     </row>
     <row r="27">
@@ -9660,7 +9724,7 @@
         <v>1840</v>
       </c>
       <c r="E30" t="n">
-        <v>1052</v>
+        <v>1028.3</v>
       </c>
       <c r="F30" t="n">
         <v>1840</v>
@@ -9669,10 +9733,10 @@
         <v>4.27</v>
       </c>
       <c r="H30" t="n">
-        <v>-42.83</v>
+        <v>-44.11</v>
       </c>
       <c r="I30" t="n">
-        <v>-41.76</v>
+        <v>-43.1</v>
       </c>
     </row>
     <row r="31">
@@ -9858,22 +9922,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>119.98</v>
+        <v>121.53</v>
       </c>
       <c r="E2" t="n">
         <v>213.09</v>
       </c>
       <c r="F2" t="n">
-        <v>119.98</v>
+        <v>121.53</v>
       </c>
       <c r="G2" t="n">
-        <v>57.63</v>
+        <v>56.34</v>
       </c>
       <c r="H2" t="n">
-        <v>77.59999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="I2" t="n">
-        <v>43.62</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="3">
@@ -9893,22 +9957,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>237.12</v>
+        <v>240.91</v>
       </c>
       <c r="E3" t="n">
         <v>323.26</v>
       </c>
       <c r="F3" t="n">
-        <v>237.12</v>
+        <v>240.91</v>
       </c>
       <c r="G3" t="n">
-        <v>55.49</v>
+        <v>53.54</v>
       </c>
       <c r="H3" t="n">
-        <v>36.33</v>
+        <v>34.18</v>
       </c>
       <c r="I3" t="n">
-        <v>58.85</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="4">
@@ -9919,31 +9983,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>472.5</v>
+        <v>121.53</v>
       </c>
       <c r="E4" t="n">
-        <v>606.2</v>
+        <v>150.67</v>
       </c>
       <c r="F4" t="n">
-        <v>472.5</v>
+        <v>121.53</v>
       </c>
       <c r="G4" t="n">
-        <v>44.1</v>
+        <v>44.17</v>
       </c>
       <c r="H4" t="n">
-        <v>28.3</v>
+        <v>23.98</v>
       </c>
       <c r="I4" t="n">
-        <v>20.88</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="5">
@@ -9954,31 +10018,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>119.98</v>
+        <v>474.1</v>
       </c>
       <c r="E5" t="n">
-        <v>152.19</v>
+        <v>597</v>
       </c>
       <c r="F5" t="n">
-        <v>119.98</v>
+        <v>474.1</v>
       </c>
       <c r="G5" t="n">
-        <v>43.69</v>
+        <v>42.82</v>
       </c>
       <c r="H5" t="n">
-        <v>26.85</v>
+        <v>25.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.62</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="6">
@@ -9998,22 +10062,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>119.98</v>
+        <v>121.53</v>
       </c>
       <c r="E6" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
       <c r="F6" t="n">
-        <v>119.98</v>
+        <v>121.53</v>
       </c>
       <c r="G6" t="n">
-        <v>42.17</v>
+        <v>40.74</v>
       </c>
       <c r="H6" t="n">
-        <v>26.85</v>
+        <v>23.98</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.24</v>
+        <v>-14.04</v>
       </c>
     </row>
     <row r="7">
@@ -10024,31 +10088,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>237.12</v>
+        <v>238.58</v>
       </c>
       <c r="E7" t="n">
-        <v>284.91</v>
+        <v>280.52</v>
       </c>
       <c r="F7" t="n">
-        <v>237.12</v>
+        <v>238.58</v>
       </c>
       <c r="G7" t="n">
-        <v>40.7</v>
+        <v>40.33</v>
       </c>
       <c r="H7" t="n">
-        <v>20.15</v>
+        <v>17.58</v>
       </c>
       <c r="I7" t="n">
-        <v>24.9</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="8">
@@ -10068,22 +10132,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>236.37</v>
+        <v>238.58</v>
       </c>
       <c r="E8" t="n">
         <v>319.94</v>
       </c>
       <c r="F8" t="n">
-        <v>236.37</v>
+        <v>238.58</v>
       </c>
       <c r="G8" t="n">
-        <v>40.1</v>
+        <v>38.98</v>
       </c>
       <c r="H8" t="n">
-        <v>35.36</v>
+        <v>34.1</v>
       </c>
       <c r="I8" t="n">
-        <v>66.76000000000001</v>
+        <v>65.39</v>
       </c>
     </row>
     <row r="9">
@@ -10094,31 +10158,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>236.37</v>
+        <v>240.91</v>
       </c>
       <c r="E9" t="n">
-        <v>285.3</v>
+        <v>279.94</v>
       </c>
       <c r="F9" t="n">
-        <v>236.37</v>
+        <v>240.91</v>
       </c>
       <c r="G9" t="n">
-        <v>39.87</v>
+        <v>38.97</v>
       </c>
       <c r="H9" t="n">
-        <v>20.7</v>
+        <v>16.2</v>
       </c>
       <c r="I9" t="n">
-        <v>25.66</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="10">
@@ -10129,31 +10193,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>472.5</v>
+        <v>121.53</v>
       </c>
       <c r="E10" t="n">
-        <v>606.2</v>
+        <v>150.67</v>
       </c>
       <c r="F10" t="n">
-        <v>472.5</v>
+        <v>121.53</v>
       </c>
       <c r="G10" t="n">
-        <v>39.38</v>
+        <v>36.85</v>
       </c>
       <c r="H10" t="n">
-        <v>28.3</v>
+        <v>23.98</v>
       </c>
       <c r="I10" t="n">
-        <v>21.96</v>
+        <v>-16.07</v>
       </c>
     </row>
     <row r="11">
@@ -10164,31 +10228,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>TATN/PLZL_2025</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>119.98</v>
+        <v>473</v>
       </c>
       <c r="E11" t="n">
-        <v>152.19</v>
+        <v>693.9</v>
       </c>
       <c r="F11" t="n">
-        <v>119.98</v>
+        <v>473</v>
       </c>
       <c r="G11" t="n">
-        <v>38.57</v>
+        <v>36.76</v>
       </c>
       <c r="H11" t="n">
-        <v>26.85</v>
+        <v>46.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-14.14</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="12">
@@ -10199,31 +10263,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TATN/PLZL_2025</t>
+          <t>ROSN/PLZL_2025</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>475</v>
+        <v>462.1</v>
       </c>
       <c r="E12" t="n">
-        <v>693.9</v>
+        <v>534.6</v>
       </c>
       <c r="F12" t="n">
-        <v>475</v>
+        <v>462.1</v>
       </c>
       <c r="G12" t="n">
-        <v>36.31</v>
+        <v>32.83</v>
       </c>
       <c r="H12" t="n">
-        <v>46.08</v>
+        <v>15.69</v>
       </c>
       <c r="I12" t="n">
-        <v>27.73</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="13">
@@ -10234,31 +10298,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>ROSN/MOEX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ROSN/PLZL_2025</t>
+          <t>ROSN/MOEX</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="E13" t="n">
-        <v>534.6</v>
+        <v>356.65</v>
       </c>
       <c r="F13" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="G13" t="n">
-        <v>33.61</v>
+        <v>31.81</v>
       </c>
       <c r="H13" t="n">
-        <v>16.57</v>
+        <v>-22.82</v>
       </c>
       <c r="I13" t="n">
-        <v>23.64</v>
+        <v>-22.11</v>
       </c>
     </row>
     <row r="14">
@@ -10269,31 +10333,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROSN/MOEX</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROSN/MOEX</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>458.6</v>
+        <v>474.1</v>
       </c>
       <c r="E14" t="n">
-        <v>372.65</v>
+        <v>597</v>
       </c>
       <c r="F14" t="n">
-        <v>458.6</v>
+        <v>474.1</v>
       </c>
       <c r="G14" t="n">
-        <v>32.6</v>
+        <v>30.72</v>
       </c>
       <c r="H14" t="n">
-        <v>-18.74</v>
+        <v>25.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-17.83</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="15">
@@ -10304,31 +10368,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SBER/TATNP</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SBER/TATNP</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="E15" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F15" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="G15" t="n">
-        <v>32.34</v>
+        <v>30.2</v>
       </c>
       <c r="H15" t="n">
-        <v>28.3</v>
+        <v>25.92</v>
       </c>
       <c r="I15" t="n">
-        <v>10.72</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="16">
@@ -10348,22 +10412,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="E16" t="n">
-        <v>606.2</v>
+        <v>597</v>
       </c>
       <c r="F16" t="n">
-        <v>472.5</v>
+        <v>474.1</v>
       </c>
       <c r="G16" t="n">
-        <v>27.24</v>
+        <v>26.33</v>
       </c>
       <c r="H16" t="n">
-        <v>28.3</v>
+        <v>25.92</v>
       </c>
       <c r="I16" t="n">
-        <v>6.7</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="17">
@@ -10383,22 +10447,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="E17" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F17" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="G17" t="n">
-        <v>26.81</v>
+        <v>26.05</v>
       </c>
       <c r="H17" t="n">
-        <v>-18.74</v>
+        <v>-22.82</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.81</v>
+        <v>-23.91</v>
       </c>
     </row>
     <row r="18">
@@ -10409,31 +10473,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PLZL_2025/TATNP</t>
+          <t>ROSN/TATNP</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>472.5</v>
+        <v>462.1</v>
       </c>
       <c r="E18" t="n">
-        <v>654.1</v>
+        <v>356.65</v>
       </c>
       <c r="F18" t="n">
-        <v>472.5</v>
+        <v>462.1</v>
       </c>
       <c r="G18" t="n">
-        <v>24.83</v>
+        <v>22.94</v>
       </c>
       <c r="H18" t="n">
-        <v>38.43</v>
+        <v>-22.82</v>
       </c>
       <c r="I18" t="n">
-        <v>10.79</v>
+        <v>-26.95</v>
       </c>
     </row>
     <row r="19">
@@ -10444,31 +10508,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ROSN/TATNP</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>458.6</v>
+        <v>1347.4</v>
       </c>
       <c r="E19" t="n">
-        <v>372.65</v>
+        <v>1028.3</v>
       </c>
       <c r="F19" t="n">
-        <v>458.6</v>
+        <v>1347.4</v>
       </c>
       <c r="G19" t="n">
-        <v>23.67</v>
+        <v>22.63</v>
       </c>
       <c r="H19" t="n">
-        <v>-18.74</v>
+        <v>-23.68</v>
       </c>
       <c r="I19" t="n">
-        <v>-23.03</v>
+        <v>-26.82</v>
       </c>
     </row>
     <row r="20">
@@ -10479,31 +10543,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>PLZL/TATNP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>PLZL_2025/TATNP</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>458.6</v>
+        <v>474.1</v>
       </c>
       <c r="E20" t="n">
-        <v>372.65</v>
+        <v>654.1</v>
       </c>
       <c r="F20" t="n">
-        <v>458.6</v>
+        <v>474.1</v>
       </c>
       <c r="G20" t="n">
-        <v>20.63</v>
+        <v>21.75</v>
       </c>
       <c r="H20" t="n">
-        <v>-18.74</v>
+        <v>37.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-22.1</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="21">
@@ -10526,7 +10590,7 @@
         <v>119.28</v>
       </c>
       <c r="E21" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
       <c r="F21" t="n">
         <v>119.28</v>
@@ -10535,10 +10599,10 @@
         <v>19.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-18.94</v>
+        <v>-21.55</v>
       </c>
       <c r="I21" t="n">
-        <v>-26.35</v>
+        <v>-28.9</v>
       </c>
     </row>
     <row r="22">
@@ -10558,22 +10622,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="E22" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F22" t="n">
-        <v>458.6</v>
+        <v>462.1</v>
       </c>
       <c r="G22" t="n">
-        <v>18.21</v>
+        <v>19.74</v>
       </c>
       <c r="H22" t="n">
-        <v>-18.74</v>
+        <v>-22.82</v>
       </c>
       <c r="I22" t="n">
-        <v>-26.22</v>
+        <v>-29.09</v>
       </c>
     </row>
     <row r="23">
@@ -10596,7 +10660,7 @@
         <v>152.96</v>
       </c>
       <c r="E23" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F23" t="n">
         <v>152.96</v>
@@ -10605,10 +10669,10 @@
         <v>17.42</v>
       </c>
       <c r="H23" t="n">
-        <v>-15.04</v>
+        <v>-15.79</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.82</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="24">
@@ -10619,31 +10683,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GMKN/SBERP</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>152.96</v>
+        <v>462.1</v>
       </c>
       <c r="E24" t="n">
-        <v>129.96</v>
+        <v>356.65</v>
       </c>
       <c r="F24" t="n">
-        <v>152.96</v>
+        <v>462.1</v>
       </c>
       <c r="G24" t="n">
-        <v>16.07</v>
+        <v>17.42</v>
       </c>
       <c r="H24" t="n">
-        <v>-15.04</v>
+        <v>-22.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.76</v>
+        <v>-30.16</v>
       </c>
     </row>
     <row r="25">
@@ -10654,31 +10718,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>GMKN/SBERP</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1309.6</v>
+        <v>152.96</v>
       </c>
       <c r="E25" t="n">
-        <v>1052</v>
+        <v>128.8</v>
       </c>
       <c r="F25" t="n">
-        <v>1309.6</v>
+        <v>152.96</v>
       </c>
       <c r="G25" t="n">
-        <v>11.36</v>
+        <v>16.07</v>
       </c>
       <c r="H25" t="n">
-        <v>-19.67</v>
+        <v>-15.79</v>
       </c>
       <c r="I25" t="n">
-        <v>-23.96</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="26">
@@ -10701,7 +10765,7 @@
         <v>152.96</v>
       </c>
       <c r="E26" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F26" t="n">
         <v>152.96</v>
@@ -10710,10 +10774,10 @@
         <v>10.33</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.04</v>
+        <v>-15.79</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.38</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="27">
@@ -10736,7 +10800,7 @@
         <v>27.32</v>
       </c>
       <c r="E27" t="n">
-        <v>16.58</v>
+        <v>16.1</v>
       </c>
       <c r="F27" t="n">
         <v>27.32</v>
@@ -10745,10 +10809,10 @@
         <v>8.33</v>
       </c>
       <c r="H27" t="n">
-        <v>-39.3</v>
+        <v>-41.06</v>
       </c>
       <c r="I27" t="n">
-        <v>-26.04</v>
+        <v>-28.25</v>
       </c>
     </row>
     <row r="28">
@@ -10768,22 +10832,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>162.47</v>
+        <v>163.16</v>
       </c>
       <c r="E28" t="n">
-        <v>96.69</v>
+        <v>93.58</v>
       </c>
       <c r="F28" t="n">
-        <v>162.47</v>
+        <v>163.16</v>
       </c>
       <c r="G28" t="n">
-        <v>7.9</v>
+        <v>7.55</v>
       </c>
       <c r="H28" t="n">
-        <v>-40.49</v>
+        <v>-42.65</v>
       </c>
       <c r="I28" t="n">
-        <v>-38.52</v>
+        <v>-40.74</v>
       </c>
     </row>
     <row r="29">
@@ -10806,7 +10870,7 @@
         <v>152.96</v>
       </c>
       <c r="E29" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F29" t="n">
         <v>152.96</v>
@@ -10815,10 +10879,10 @@
         <v>7.51</v>
       </c>
       <c r="H29" t="n">
-        <v>-15.04</v>
+        <v>-15.79</v>
       </c>
       <c r="I29" t="n">
-        <v>-14.38</v>
+        <v>-15.16</v>
       </c>
     </row>
     <row r="30">
@@ -10841,7 +10905,7 @@
         <v>152.96</v>
       </c>
       <c r="E30" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F30" t="n">
         <v>152.96</v>
@@ -10850,10 +10914,10 @@
         <v>7.41</v>
       </c>
       <c r="H30" t="n">
-        <v>-15.04</v>
+        <v>-15.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-14.45</v>
+        <v>-15.23</v>
       </c>
     </row>
     <row r="31">
@@ -10876,7 +10940,7 @@
         <v>152.96</v>
       </c>
       <c r="E31" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F31" t="n">
         <v>152.96</v>
@@ -10885,10 +10949,10 @@
         <v>6.89</v>
       </c>
       <c r="H31" t="n">
-        <v>-15.04</v>
+        <v>-15.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-12.97</v>
+        <v>-13.76</v>
       </c>
     </row>
     <row r="32">
@@ -10943,22 +11007,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>237.12</v>
+        <v>240.91</v>
       </c>
       <c r="E33" t="n">
-        <v>284.91</v>
+        <v>279.94</v>
       </c>
       <c r="F33" t="n">
-        <v>237.12</v>
+        <v>240.91</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>20.15</v>
+        <v>16.2</v>
       </c>
       <c r="I33" t="n">
-        <v>20.15</v>
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>
@@ -11030,31 +11094,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GMKN/PLZL</t>
+          <t>GAZP/VTBR</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>126.3</v>
+        <v>122.77</v>
       </c>
       <c r="E2" t="n">
-        <v>129.96</v>
+        <v>93.58</v>
       </c>
       <c r="F2" t="n">
-        <v>126.3</v>
+        <v>122.77</v>
       </c>
       <c r="G2" t="n">
-        <v>19.01</v>
+        <v>22.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>-23.78</v>
       </c>
       <c r="I2" t="n">
-        <v>0.41</v>
+        <v>-15.31</v>
       </c>
     </row>
     <row r="3">
@@ -11074,22 +11138,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="E3" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F3" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="G3" t="n">
-        <v>14.59</v>
+        <v>20.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="I3" t="n">
-        <v>-8.81</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="4">
@@ -11100,31 +11164,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLZL/MOEX</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PLZL/MOEX</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2309.6</v>
+        <v>301.68</v>
       </c>
       <c r="E4" t="n">
-        <v>990.2</v>
+        <v>279.94</v>
       </c>
       <c r="F4" t="n">
-        <v>2309.6</v>
+        <v>301.68</v>
       </c>
       <c r="G4" t="n">
-        <v>12.27</v>
+        <v>16.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-57.13</v>
+        <v>-7.21</v>
       </c>
       <c r="I4" t="n">
-        <v>-59.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -11135,31 +11199,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROSN/TATN</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ROSN/TATN</t>
+          <t>SBERP/TATNP</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>441</v>
+        <v>301.36</v>
       </c>
       <c r="E5" t="n">
-        <v>372.65</v>
+        <v>280.52</v>
       </c>
       <c r="F5" t="n">
-        <v>441</v>
+        <v>301.36</v>
       </c>
       <c r="G5" t="n">
-        <v>12.1</v>
+        <v>14.87</v>
       </c>
       <c r="H5" t="n">
-        <v>-15.5</v>
+        <v>-6.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.46</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="6">
@@ -11170,31 +11234,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>ROSN/TATN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GMKN/ROSN</t>
+          <t>ROSN/TATN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>126.3</v>
+        <v>435.55</v>
       </c>
       <c r="E6" t="n">
-        <v>129.96</v>
+        <v>356.65</v>
       </c>
       <c r="F6" t="n">
-        <v>126.3</v>
+        <v>435.55</v>
       </c>
       <c r="G6" t="n">
-        <v>10.81</v>
+        <v>13.17</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9</v>
+        <v>-18.12</v>
       </c>
       <c r="I6" t="n">
-        <v>-11.27</v>
+        <v>-19.46</v>
       </c>
     </row>
     <row r="7">
@@ -11214,22 +11278,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="E7" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F7" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="G7" t="n">
-        <v>10.75</v>
+        <v>13.09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.96</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="8">
@@ -11240,31 +11304,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLZL/SBERP</t>
+          <t>PLZL/MOEX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PLZL/SBERP</t>
+          <t>PLZL/MOEX</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2309.6</v>
+        <v>2296</v>
       </c>
       <c r="E8" t="n">
-        <v>990.2</v>
+        <v>953.2</v>
       </c>
       <c r="F8" t="n">
-        <v>2309.6</v>
+        <v>2296</v>
       </c>
       <c r="G8" t="n">
-        <v>9.779999999999999</v>
+        <v>12.77</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.13</v>
+        <v>-58.48</v>
       </c>
       <c r="I8" t="n">
-        <v>-57.55</v>
+        <v>-61.23</v>
       </c>
     </row>
     <row r="9">
@@ -11275,31 +11339,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GAZP/VTBR</t>
+          <t>GMKN/TATN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GAZP/VTBR</t>
+          <t>GMKN/TATN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>125</v>
+        <v>122.88</v>
       </c>
       <c r="E9" t="n">
-        <v>96.69</v>
+        <v>128.8</v>
       </c>
       <c r="F9" t="n">
-        <v>125</v>
+        <v>122.88</v>
       </c>
       <c r="G9" t="n">
-        <v>9.77</v>
+        <v>11.8</v>
       </c>
       <c r="H9" t="n">
-        <v>-22.65</v>
+        <v>4.82</v>
       </c>
       <c r="I9" t="n">
-        <v>-20.93</v>
+        <v>-10.17</v>
       </c>
     </row>
     <row r="10">
@@ -11310,31 +11374,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GMKN/TATN</t>
+          <t>PLZL/SBERP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GMKN/TATN</t>
+          <t>PLZL/SBERP</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>126.3</v>
+        <v>2296</v>
       </c>
       <c r="E10" t="n">
-        <v>129.96</v>
+        <v>953.2</v>
       </c>
       <c r="F10" t="n">
-        <v>126.3</v>
+        <v>2296</v>
       </c>
       <c r="G10" t="n">
-        <v>9.5</v>
+        <v>9.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>-58.48</v>
       </c>
       <c r="I10" t="n">
-        <v>-11.14</v>
+        <v>-58.85</v>
       </c>
     </row>
     <row r="11">
@@ -11354,22 +11418,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>441</v>
+        <v>435.55</v>
       </c>
       <c r="E11" t="n">
-        <v>372.65</v>
+        <v>356.65</v>
       </c>
       <c r="F11" t="n">
-        <v>441</v>
+        <v>435.55</v>
       </c>
       <c r="G11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="H11" t="n">
-        <v>-15.5</v>
+        <v>-18.12</v>
       </c>
       <c r="I11" t="n">
-        <v>-18.64</v>
+        <v>-21.55</v>
       </c>
     </row>
     <row r="12">
@@ -11380,31 +11444,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>GMKN/ROSN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>170.92</v>
+        <v>122.88</v>
       </c>
       <c r="E12" t="n">
-        <v>152.19</v>
+        <v>128.8</v>
       </c>
       <c r="F12" t="n">
-        <v>170.92</v>
+        <v>122.88</v>
       </c>
       <c r="G12" t="n">
-        <v>7.86</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.96</v>
+        <v>4.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.2</v>
+        <v>-13.68</v>
       </c>
     </row>
     <row r="13">
@@ -11415,31 +11479,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PLZL/TATNP</t>
+          <t>TATN/MOEX</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2309.6</v>
+        <v>170.85</v>
       </c>
       <c r="E13" t="n">
-        <v>990.2</v>
+        <v>150.67</v>
       </c>
       <c r="F13" t="n">
-        <v>2309.6</v>
+        <v>170.85</v>
       </c>
       <c r="G13" t="n">
-        <v>7.34</v>
+        <v>8.69</v>
       </c>
       <c r="H13" t="n">
-        <v>-57.13</v>
+        <v>-11.81</v>
       </c>
       <c r="I13" t="n">
-        <v>-59.53</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="14">
@@ -11450,31 +11514,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROSN/MOEX</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROSN/MOEX</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>170.92</v>
+        <v>170.85</v>
       </c>
       <c r="E14" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
       <c r="F14" t="n">
-        <v>170.92</v>
+        <v>170.85</v>
       </c>
       <c r="G14" t="n">
-        <v>6.18</v>
+        <v>7.89</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.96</v>
+        <v>-11.81</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.82</v>
+        <v>-8.119999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -11485,31 +11549,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GAZP/SNGS</t>
+          <t>ROSN/MOEX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GAZP/SNGS</t>
+          <t>ROSN/MOEX</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22.84</v>
+        <v>170.85</v>
       </c>
       <c r="E15" t="n">
-        <v>16.58</v>
+        <v>150.67</v>
       </c>
       <c r="F15" t="n">
-        <v>22.84</v>
+        <v>170.85</v>
       </c>
       <c r="G15" t="n">
-        <v>6.09</v>
+        <v>7.19</v>
       </c>
       <c r="H15" t="n">
-        <v>-27.39</v>
+        <v>-11.81</v>
       </c>
       <c r="I15" t="n">
-        <v>-21.06</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="16">
@@ -11520,31 +11584,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>304.69</v>
+        <v>590.6</v>
       </c>
       <c r="E16" t="n">
-        <v>285.3</v>
+        <v>597</v>
       </c>
       <c r="F16" t="n">
-        <v>304.69</v>
+        <v>590.6</v>
       </c>
       <c r="G16" t="n">
-        <v>5.61</v>
+        <v>6.75</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.36</v>
+        <v>1.08</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.25</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="17">
@@ -11555,31 +11619,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>GMKN/TATNP</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>600.6</v>
+        <v>122.88</v>
       </c>
       <c r="E17" t="n">
-        <v>606.2</v>
+        <v>128.8</v>
       </c>
       <c r="F17" t="n">
-        <v>600.6</v>
+        <v>122.88</v>
       </c>
       <c r="G17" t="n">
-        <v>5.61</v>
+        <v>6.66</v>
       </c>
       <c r="H17" t="n">
-        <v>0.93</v>
+        <v>4.82</v>
       </c>
       <c r="I17" t="n">
-        <v>4.42</v>
+        <v>-15.25</v>
       </c>
     </row>
     <row r="18">
@@ -11599,22 +11663,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>170.92</v>
+        <v>170.85</v>
       </c>
       <c r="E18" t="n">
-        <v>152.19</v>
+        <v>150.67</v>
       </c>
       <c r="F18" t="n">
-        <v>170.92</v>
+        <v>170.85</v>
       </c>
       <c r="G18" t="n">
-        <v>5.45</v>
+        <v>5.84</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.96</v>
+        <v>-11.81</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.43</v>
+        <v>-10.03</v>
       </c>
     </row>
     <row r="19">
@@ -11625,31 +11689,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GMKN/TATNP</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>126.3</v>
+        <v>2296</v>
       </c>
       <c r="E19" t="n">
-        <v>129.96</v>
+        <v>953.2</v>
       </c>
       <c r="F19" t="n">
-        <v>126.3</v>
+        <v>2296</v>
       </c>
       <c r="G19" t="n">
-        <v>4.48</v>
+        <v>4.78</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9</v>
+        <v>-58.48</v>
       </c>
       <c r="I19" t="n">
-        <v>-16.14</v>
+        <v>-59.78</v>
       </c>
     </row>
     <row r="20">
@@ -11669,22 +11733,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>304.69</v>
+        <v>301.36</v>
       </c>
       <c r="E20" t="n">
-        <v>285.3</v>
+        <v>280.52</v>
       </c>
       <c r="F20" t="n">
-        <v>304.69</v>
+        <v>301.36</v>
       </c>
       <c r="G20" t="n">
-        <v>3.81</v>
+        <v>4.78</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.36</v>
+        <v>-6.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.84</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="21">
@@ -11695,31 +11759,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2309.6</v>
+        <v>22.14</v>
       </c>
       <c r="E21" t="n">
-        <v>990.2</v>
+        <v>16.1</v>
       </c>
       <c r="F21" t="n">
-        <v>2309.6</v>
+        <v>22.14</v>
       </c>
       <c r="G21" t="n">
-        <v>3.81</v>
+        <v>4.04</v>
       </c>
       <c r="H21" t="n">
-        <v>-57.13</v>
+        <v>-27.3</v>
       </c>
       <c r="I21" t="n">
-        <v>-58.46</v>
+        <v>-21.74</v>
       </c>
     </row>
     <row r="22">
@@ -11730,31 +11794,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SBER/PLZL</t>
+          <t>PLZL/TATNP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SBER/PLZL</t>
+          <t>PLZL/TATNP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2309.6</v>
+        <v>2296</v>
       </c>
       <c r="E22" t="n">
-        <v>990.2</v>
+        <v>953.2</v>
       </c>
       <c r="F22" t="n">
-        <v>2309.6</v>
+        <v>2296</v>
       </c>
       <c r="G22" t="n">
-        <v>3.26</v>
+        <v>3.81</v>
       </c>
       <c r="H22" t="n">
-        <v>-57.13</v>
+        <v>-58.48</v>
       </c>
       <c r="I22" t="n">
-        <v>-56.55</v>
+        <v>-60.31</v>
       </c>
     </row>
     <row r="23">
@@ -11774,22 +11838,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="E23" t="n">
-        <v>129.96</v>
+        <v>128.8</v>
       </c>
       <c r="F23" t="n">
-        <v>126.3</v>
+        <v>122.88</v>
       </c>
       <c r="G23" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="I23" t="n">
-        <v>-13.17</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="24">
@@ -11800,31 +11864,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SBER/TATNP</t>
+          <t>GMKN/PLZL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SBER/TATNP</t>
+          <t>GMKN/PLZL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>600.6</v>
+        <v>2296</v>
       </c>
       <c r="E24" t="n">
-        <v>606.2</v>
+        <v>953.2</v>
       </c>
       <c r="F24" t="n">
-        <v>600.6</v>
+        <v>2296</v>
       </c>
       <c r="G24" t="n">
-        <v>2.34</v>
+        <v>3.08</v>
       </c>
       <c r="H24" t="n">
-        <v>0.93</v>
+        <v>-58.48</v>
       </c>
       <c r="I24" t="n">
-        <v>5.59</v>
+        <v>-56.36</v>
       </c>
     </row>
     <row r="25">
@@ -11835,31 +11899,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SBER/ROSN</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>441</v>
+        <v>620.4</v>
       </c>
       <c r="E25" t="n">
-        <v>372.65</v>
+        <v>623.4</v>
       </c>
       <c r="F25" t="n">
-        <v>441</v>
+        <v>620.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.34</v>
+        <v>3.06</v>
       </c>
       <c r="H25" t="n">
-        <v>-15.5</v>
+        <v>0.48</v>
       </c>
       <c r="I25" t="n">
-        <v>-18.57</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="26">
@@ -11870,31 +11934,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>SBER/ROSN</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>629.3</v>
+        <v>435.55</v>
       </c>
       <c r="E26" t="n">
-        <v>632.2</v>
+        <v>356.65</v>
       </c>
       <c r="F26" t="n">
-        <v>629.3</v>
+        <v>435.55</v>
       </c>
       <c r="G26" t="n">
-        <v>2.34</v>
+        <v>3.06</v>
       </c>
       <c r="H26" t="n">
-        <v>0.46</v>
+        <v>-18.12</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.68</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="27">
@@ -11905,31 +11969,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SBERP/TATNP</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>600.6</v>
+        <v>22.14</v>
       </c>
       <c r="E27" t="n">
-        <v>606.2</v>
+        <v>16.1</v>
       </c>
       <c r="F27" t="n">
-        <v>600.6</v>
+        <v>22.14</v>
       </c>
       <c r="G27" t="n">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="H27" t="n">
-        <v>0.93</v>
+        <v>-27.3</v>
       </c>
       <c r="I27" t="n">
-        <v>5.57</v>
+        <v>-25.37</v>
       </c>
     </row>
     <row r="28">
@@ -11940,31 +12004,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TATN/MOEX</t>
+          <t>TATN/PLZL</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>170.92</v>
+        <v>2296</v>
       </c>
       <c r="E28" t="n">
-        <v>152.19</v>
+        <v>953.2</v>
       </c>
       <c r="F28" t="n">
-        <v>170.92</v>
+        <v>2296</v>
       </c>
       <c r="G28" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>-10.96</v>
+        <v>-58.48</v>
       </c>
       <c r="I28" t="n">
-        <v>-10.76</v>
+        <v>-59.85</v>
       </c>
     </row>
     <row r="29">
@@ -11975,31 +12039,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TATN/PLZL</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2309.6</v>
+        <v>170.85</v>
       </c>
       <c r="E29" t="n">
-        <v>990.2</v>
+        <v>150.67</v>
       </c>
       <c r="F29" t="n">
-        <v>2309.6</v>
+        <v>170.85</v>
       </c>
       <c r="G29" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="H29" t="n">
-        <v>-57.13</v>
+        <v>-11.81</v>
       </c>
       <c r="I29" t="n">
-        <v>-56.13</v>
+        <v>-14.72</v>
       </c>
     </row>
     <row r="30">
@@ -12010,31 +12074,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>170.92</v>
+        <v>301.36</v>
       </c>
       <c r="E30" t="n">
-        <v>152.19</v>
+        <v>280.52</v>
       </c>
       <c r="F30" t="n">
-        <v>170.92</v>
+        <v>301.36</v>
       </c>
       <c r="G30" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="H30" t="n">
-        <v>-10.96</v>
+        <v>-6.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-12.38</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -12045,31 +12109,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>SBER/PLZL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>SBER/PLZL</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>304.5</v>
+        <v>2296</v>
       </c>
       <c r="E31" t="n">
-        <v>284.91</v>
+        <v>953.2</v>
       </c>
       <c r="F31" t="n">
-        <v>304.5</v>
+        <v>2296</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="H31" t="n">
-        <v>-6.43</v>
+        <v>-58.48</v>
       </c>
       <c r="I31" t="n">
-        <v>-6.43</v>
+        <v>-60.43</v>
       </c>
     </row>
     <row r="32">
@@ -12080,31 +12144,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6380</v>
+        <v>301.68</v>
       </c>
       <c r="E32" t="n">
-        <v>5484.5</v>
+        <v>279.94</v>
       </c>
       <c r="F32" t="n">
-        <v>6380</v>
+        <v>301.68</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-14.04</v>
+        <v>-7.21</v>
       </c>
       <c r="I32" t="n">
-        <v>-14.04</v>
+        <v>-7.21</v>
       </c>
     </row>
     <row r="33">
@@ -12115,31 +12179,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>22.84</v>
+        <v>6325.5</v>
       </c>
       <c r="E33" t="n">
-        <v>16.58</v>
+        <v>5337</v>
       </c>
       <c r="F33" t="n">
-        <v>22.84</v>
+        <v>6325.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-27.39</v>
+        <v>-15.63</v>
       </c>
       <c r="I33" t="n">
-        <v>-27.39</v>
+        <v>-15.63</v>
       </c>
     </row>
   </sheetData>

--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,12 +425,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Прошла фильтр</t>
         </is>
@@ -1399,92 +1387,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Довнесений</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, руб.</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, руб.</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, руб.</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, руб.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), руб.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -2373,92 +2361,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Довнесений</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, руб.</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, руб.</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, руб.</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, руб.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), руб.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -3471,92 +3459,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Довнесений</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, руб.</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, руб.</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, руб.</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, руб.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), руб.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -4693,92 +4681,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Довнесений</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Старт X, акций</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Финал X, акций</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Старт Y, акций</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Финал Y, акций</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Внесено, руб.</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Деньги в конце, руб.</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Налог, руб.</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Комиссия, руб.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Заработано (после), руб.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Доходность (после), %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Где деньги в конце</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
@@ -5357,42 +5345,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -7356,26 +7344,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SNGS/MOEX</t>
+          <t>ROSN/PLZL</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>46.45</v>
+        <v>462.8</v>
       </c>
       <c r="D67" t="n">
-        <v>15.83</v>
+        <v>357.7</v>
       </c>
       <c r="E67" t="n">
-        <v>46.45</v>
+        <v>462.8</v>
       </c>
       <c r="F67" t="n">
         <v>-0.04</v>
       </c>
       <c r="G67" t="n">
-        <v>-65.92</v>
+        <v>-22.71</v>
       </c>
       <c r="H67" t="n">
-        <v>-65.89</v>
+        <v>-22.7</v>
       </c>
     </row>
     <row r="68">
@@ -7386,26 +7374,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ROSN/PLZL</t>
+          <t>SNGS/MOEX</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>462.8</v>
+        <v>46.45</v>
       </c>
       <c r="D68" t="n">
-        <v>357.7</v>
+        <v>15.83</v>
       </c>
       <c r="E68" t="n">
-        <v>462.8</v>
+        <v>46.45</v>
       </c>
       <c r="F68" t="n">
         <v>-0.04</v>
       </c>
       <c r="G68" t="n">
-        <v>-22.71</v>
+        <v>-65.92</v>
       </c>
       <c r="H68" t="n">
-        <v>-22.7</v>
+        <v>-65.89</v>
       </c>
     </row>
     <row r="69">
@@ -7446,7 +7434,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SBER/SBERP</t>
+          <t>SBER/MOEX</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -7476,7 +7464,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SBER/MOEX</t>
+          <t>SBER/SBERP</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -7566,7 +7554,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TATN/SBERP</t>
+          <t>TATN/TATNP</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7596,7 +7584,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TATN/TATNP</t>
+          <t>TATN/SBERP</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7753,42 +7741,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -9602,26 +9590,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>GAZP/ROSN</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>28.99</v>
+        <v>325.7</v>
       </c>
       <c r="D62" t="n">
-        <v>15.83</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>28.99</v>
+        <v>325.7</v>
       </c>
       <c r="F62" t="n">
         <v>-0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>-45.39</v>
+        <v>-71.45999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>-45.39</v>
+        <v>-71.45</v>
       </c>
     </row>
     <row r="63">
@@ -9662,26 +9650,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GAZP/ROSN</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>325.7</v>
+        <v>28.99</v>
       </c>
       <c r="D64" t="n">
-        <v>92.95999999999999</v>
+        <v>15.83</v>
       </c>
       <c r="E64" t="n">
-        <v>325.7</v>
+        <v>28.99</v>
       </c>
       <c r="F64" t="n">
         <v>-0.01</v>
       </c>
       <c r="G64" t="n">
-        <v>-71.45999999999999</v>
+        <v>-45.39</v>
       </c>
       <c r="H64" t="n">
-        <v>-71.45</v>
+        <v>-45.39</v>
       </c>
     </row>
     <row r="65">
@@ -9722,26 +9710,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MOEX/TATNP</t>
+          <t>MOEX/VTBR</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>180.77</v>
+        <v>235.77</v>
       </c>
       <c r="D66" t="n">
         <v>146.7</v>
       </c>
       <c r="E66" t="n">
-        <v>180.77</v>
+        <v>235.77</v>
       </c>
       <c r="F66" t="n">
         <v>-0.03</v>
       </c>
       <c r="G66" t="n">
-        <v>-18.85</v>
+        <v>-37.78</v>
       </c>
       <c r="H66" t="n">
-        <v>-18.84</v>
+        <v>-37.77</v>
       </c>
     </row>
     <row r="67">
@@ -9752,26 +9740,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MOEX/VTBR</t>
+          <t>MOEX/TATNP</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>235.77</v>
+        <v>180.77</v>
       </c>
       <c r="D67" t="n">
         <v>146.7</v>
       </c>
       <c r="E67" t="n">
-        <v>235.77</v>
+        <v>180.77</v>
       </c>
       <c r="F67" t="n">
         <v>-0.03</v>
       </c>
       <c r="G67" t="n">
-        <v>-37.78</v>
+        <v>-18.85</v>
       </c>
       <c r="H67" t="n">
-        <v>-37.77</v>
+        <v>-18.84</v>
       </c>
     </row>
     <row r="68">
@@ -9932,7 +9920,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NVTK/TATNP</t>
+          <t>NVTK/SBERP</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9962,7 +9950,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NVTK/ROSN</t>
+          <t>NVTK/TATN</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9992,7 +9980,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NVTK/TATN</t>
+          <t>NVTK/ROSN</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -10022,7 +10010,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NVTK/SBERP</t>
+          <t>NVTK/TATNP</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -10149,42 +10137,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -11938,26 +11926,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SNGS/VTBR</t>
+          <t>SNGS/PLZL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>28.99</v>
+        <v>24.7</v>
       </c>
       <c r="D60" t="n">
         <v>15.83</v>
       </c>
       <c r="E60" t="n">
-        <v>28.99</v>
+        <v>24.7</v>
       </c>
       <c r="F60" t="n">
         <v>-0.01</v>
       </c>
       <c r="G60" t="n">
-        <v>-45.39</v>
+        <v>-35.9</v>
       </c>
       <c r="H60" t="n">
-        <v>-45.39</v>
+        <v>-35.89</v>
       </c>
     </row>
     <row r="61">
@@ -11968,26 +11956,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SNGS/PLZL</t>
+          <t>SBER/PLZL</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>24.7</v>
+        <v>302.09</v>
       </c>
       <c r="D61" t="n">
-        <v>15.83</v>
+        <v>275.89</v>
       </c>
       <c r="E61" t="n">
-        <v>24.7</v>
+        <v>302.09</v>
       </c>
       <c r="F61" t="n">
         <v>-0.01</v>
       </c>
       <c r="G61" t="n">
-        <v>-35.9</v>
+        <v>-8.67</v>
       </c>
       <c r="H61" t="n">
-        <v>-35.89</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="62">
@@ -11998,26 +11986,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SBER/PLZL</t>
+          <t>SNGS/VTBR</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>302.09</v>
+        <v>28.99</v>
       </c>
       <c r="D62" t="n">
-        <v>275.89</v>
+        <v>15.83</v>
       </c>
       <c r="E62" t="n">
-        <v>302.09</v>
+        <v>28.99</v>
       </c>
       <c r="F62" t="n">
         <v>-0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>-8.67</v>
+        <v>-45.39</v>
       </c>
       <c r="H62" t="n">
-        <v>-8.67</v>
+        <v>-45.39</v>
       </c>
     </row>
     <row r="63">
@@ -12118,7 +12106,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GAZP/SBERP</t>
+          <t>GAZP/TATN</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -12148,7 +12136,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GAZP/SNGS</t>
+          <t>GAZP/MOEX</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -12178,7 +12166,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GAZP/ROSN</t>
+          <t>GAZP/SBER</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -12208,7 +12196,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GAZP/TATN</t>
+          <t>GAZP/LKOH</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -12238,7 +12226,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GAZP/MOEX</t>
+          <t>GAZP/SNGS</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -12268,7 +12256,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GAZP/LKOH</t>
+          <t>GAZP/ROSN</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -12298,7 +12286,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GAZP/TATNP</t>
+          <t>GAZP/SBERP</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -12328,7 +12316,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GAZP/SBER</t>
+          <t>GAZP/TATNP</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -12545,42 +12533,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Цена акции начало</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Цена акции конец</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Теория</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Доходность (теория), %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Расхождение %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Доходность (как в прошлых), %</t>
         </is>
@@ -14574,7 +14562,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LKOH/NVTK</t>
+          <t>LKOH/SNGS</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -14604,7 +14592,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LKOH/TATNP</t>
+          <t>LKOH/SBER</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -14634,7 +14622,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LKOH/SBERP</t>
+          <t>LKOH/MOEX</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -14664,7 +14652,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LKOH/SBER</t>
+          <t>LKOH/SBERP</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -14694,7 +14682,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LKOH/MOEX</t>
+          <t>LKOH/NVTK</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -14724,7 +14712,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LKOH/SNGS</t>
+          <t>LKOH/TATNP</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -14754,7 +14742,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LKOH/TATN</t>
+          <t>LKOH/ROSN</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -14784,7 +14772,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LKOH/ROSN</t>
+          <t>LKOH/TATN</t>
         </is>
       </c>
       <c r="C75" t="n">

--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -1514,7 +1514,7 @@
         <v>102799.08</v>
       </c>
       <c r="K2" t="n">
-        <v>182227.5</v>
+        <v>183680</v>
       </c>
       <c r="L2" t="n">
         <v>4260.3</v>
@@ -1523,10 +1523,10 @@
         <v>1398.87</v>
       </c>
       <c r="N2" t="n">
-        <v>79428.42</v>
+        <v>80880.92</v>
       </c>
       <c r="O2" t="n">
-        <v>77.27</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>6161</v>
       </c>
       <c r="R2" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="3">
@@ -1555,7 +1555,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -1576,7 +1576,7 @@
         <v>100668.62</v>
       </c>
       <c r="K3" t="n">
-        <v>120544.9</v>
+        <v>121437.95</v>
       </c>
       <c r="L3" t="n">
         <v>10465.59</v>
@@ -1585,10 +1585,10 @@
         <v>2121.37</v>
       </c>
       <c r="N3" t="n">
-        <v>19876.28</v>
+        <v>20769.33</v>
       </c>
       <c r="O3" t="n">
-        <v>19.74</v>
+        <v>20.63</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>458</v>
       </c>
       <c r="R3" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="4">
@@ -1617,7 +1617,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -1638,7 +1638,7 @@
         <v>101183.44</v>
       </c>
       <c r="K4" t="n">
-        <v>111564</v>
+        <v>111672</v>
       </c>
       <c r="L4" t="n">
         <v>2236.44</v>
@@ -1647,10 +1647,10 @@
         <v>682.12</v>
       </c>
       <c r="N4" t="n">
-        <v>10380.56</v>
+        <v>10488.56</v>
       </c>
       <c r="O4" t="n">
-        <v>10.26</v>
+        <v>10.37</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>649.4</v>
       </c>
       <c r="R4" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
     </row>
     <row r="5">
@@ -1700,7 +1700,7 @@
         <v>100281.66</v>
       </c>
       <c r="K5" t="n">
-        <v>102659.9</v>
+        <v>103420.45</v>
       </c>
       <c r="L5" t="n">
         <v>5453.6</v>
@@ -1709,10 +1709,10 @@
         <v>738.6900000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>2378.24</v>
+        <v>3138.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>531.85</v>
       </c>
       <c r="R5" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="6">
@@ -1762,7 +1762,7 @@
         <v>106564.65</v>
       </c>
       <c r="K6" t="n">
-        <v>105173.3</v>
+        <v>108840.1</v>
       </c>
       <c r="L6" t="n">
         <v>5778.53</v>
@@ -1771,10 +1771,10 @@
         <v>1071.32</v>
       </c>
       <c r="N6" t="n">
-        <v>-1391.35</v>
+        <v>2275.45</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.31</v>
+        <v>2.14</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>1334.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="7">
@@ -1796,58 +1796,58 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLZL/VTBR</t>
+          <t>SBER/NVTK</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>159</v>
+        <v>1079</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1413</v>
+        <v>81</v>
       </c>
       <c r="I7" t="n">
-        <v>1930</v>
+        <v>94</v>
       </c>
       <c r="J7" t="n">
-        <v>101635.01</v>
+        <v>101451.86</v>
       </c>
       <c r="K7" t="n">
-        <v>96654.39999999999</v>
+        <v>99329.8</v>
       </c>
       <c r="L7" t="n">
-        <v>7280.72</v>
+        <v>10337.76</v>
       </c>
       <c r="M7" t="n">
-        <v>1179.68</v>
+        <v>1299.54</v>
       </c>
       <c r="N7" t="n">
-        <v>-4980.61</v>
+        <v>-2122.06</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.9</v>
+        <v>-2.09</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1930 VTBR + cash 0.00</t>
+          <t>94 NVTK + cash 0.00</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>77.86</v>
+        <v>1334.4</v>
       </c>
       <c r="R7" t="n">
-        <v>50.08</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="8">
@@ -1858,58 +1858,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SBER/NVTK</t>
+          <t>PLZL/VTBR</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1078</v>
+        <v>159</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>416</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>81</v>
+        <v>1413</v>
       </c>
       <c r="I8" t="n">
-        <v>94</v>
+        <v>1930</v>
       </c>
       <c r="J8" t="n">
-        <v>101451.86</v>
+        <v>101635.01</v>
       </c>
       <c r="K8" t="n">
-        <v>95983.39999999999</v>
+        <v>96808.8</v>
       </c>
       <c r="L8" t="n">
-        <v>10337.76</v>
+        <v>7280.72</v>
       </c>
       <c r="M8" t="n">
-        <v>1299.54</v>
+        <v>1179.68</v>
       </c>
       <c r="N8" t="n">
-        <v>-5468.46</v>
+        <v>-4826.21</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.39</v>
+        <v>-4.75</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>94 NVTK + cash 0.00</t>
+          <t>1930 VTBR + cash 0.00</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1334.4</v>
+        <v>77.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1021.1</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="9">
@@ -1927,7 +1927,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -1948,7 +1948,7 @@
         <v>106142.2</v>
       </c>
       <c r="K9" t="n">
-        <v>98923.5</v>
+        <v>99712</v>
       </c>
       <c r="L9" t="n">
         <v>3104.26</v>
@@ -1957,10 +1957,10 @@
         <v>673.53</v>
       </c>
       <c r="N9" t="n">
-        <v>-7218.7</v>
+        <v>-6430.2</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.8</v>
+        <v>-6.06</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>7008</v>
       </c>
       <c r="R9" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="10">
@@ -1989,7 +1989,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2010,7 +2010,7 @@
         <v>100383.62</v>
       </c>
       <c r="K10" t="n">
-        <v>91846.72</v>
+        <v>91993.44</v>
       </c>
       <c r="L10" t="n">
         <v>6899.45</v>
@@ -2019,10 +2019,10 @@
         <v>1152.36</v>
       </c>
       <c r="N10" t="n">
-        <v>-8536.9</v>
+        <v>-8390.18</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.5</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>99.75</v>
       </c>
       <c r="R10" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="11">
@@ -2051,7 +2051,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2072,7 +2072,7 @@
         <v>100065.6</v>
       </c>
       <c r="K11" t="n">
-        <v>90344.32000000001</v>
+        <v>90488.64</v>
       </c>
       <c r="L11" t="n">
         <v>6828.02</v>
@@ -2081,10 +2081,10 @@
         <v>1156.53</v>
       </c>
       <c r="N11" t="n">
-        <v>-9721.280000000001</v>
+        <v>-9576.959999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.57</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>99.75</v>
       </c>
       <c r="R11" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="12">
@@ -2113,7 +2113,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         <v>100831.41</v>
       </c>
       <c r="K12" t="n">
-        <v>86793.5</v>
+        <v>89819.5</v>
       </c>
       <c r="L12" t="n">
         <v>2714.42</v>
@@ -2143,10 +2143,10 @@
         <v>670.89</v>
       </c>
       <c r="N12" t="n">
-        <v>-14037.91</v>
+        <v>-11011.91</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.92</v>
+        <v>-10.92</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>1334.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="13">
@@ -2196,7 +2196,7 @@
         <v>100800.96</v>
       </c>
       <c r="K13" t="n">
-        <v>82709.10000000001</v>
+        <v>85592.7</v>
       </c>
       <c r="L13" t="n">
         <v>4623.84</v>
@@ -2205,10 +2205,10 @@
         <v>771.2</v>
       </c>
       <c r="N13" t="n">
-        <v>-18091.86</v>
+        <v>-15208.26</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.95</v>
+        <v>-15.09</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>1334.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="14">
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -2258,7 +2258,7 @@
         <v>100188.46</v>
       </c>
       <c r="K14" t="n">
-        <v>80410.39999999999</v>
+        <v>82970.8</v>
       </c>
       <c r="L14" t="n">
         <v>1788.01</v>
@@ -2267,10 +2267,10 @@
         <v>667.01</v>
       </c>
       <c r="N14" t="n">
-        <v>-19778.06</v>
+        <v>-17217.66</v>
       </c>
       <c r="O14" t="n">
-        <v>-19.74</v>
+        <v>-17.19</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>163.33</v>
       </c>
       <c r="R14" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
     </row>
     <row r="15">
@@ -2320,7 +2320,7 @@
         <v>100288.24</v>
       </c>
       <c r="K15" t="n">
-        <v>53220.46</v>
+        <v>53405.37</v>
       </c>
       <c r="L15" t="n">
         <v>3469.89</v>
@@ -2329,10 +2329,10 @@
         <v>1043.3</v>
       </c>
       <c r="N15" t="n">
-        <v>-47067.78</v>
+        <v>-46882.87</v>
       </c>
       <c r="O15" t="n">
-        <v>-46.93</v>
+        <v>-46.75</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>46.45</v>
       </c>
       <c r="R15" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
     </row>
   </sheetData>
@@ -2488,7 +2488,7 @@
         <v>100502.3</v>
       </c>
       <c r="K2" t="n">
-        <v>129668.3</v>
+        <v>130067.8</v>
       </c>
       <c r="L2" t="n">
         <v>2344.61</v>
@@ -2497,10 +2497,10 @@
         <v>686.8200000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>29166</v>
+        <v>29565.5</v>
       </c>
       <c r="O2" t="n">
-        <v>29.02</v>
+        <v>29.42</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>326.92</v>
       </c>
       <c r="R2" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="3">
@@ -2550,7 +2550,7 @@
         <v>100344.02</v>
       </c>
       <c r="K3" t="n">
-        <v>128362.5</v>
+        <v>129403.75</v>
       </c>
       <c r="L3" t="n">
         <v>3205.09</v>
@@ -2559,10 +2559,10 @@
         <v>1006.58</v>
       </c>
       <c r="N3" t="n">
-        <v>28018.48</v>
+        <v>29059.73</v>
       </c>
       <c r="O3" t="n">
-        <v>27.92</v>
+        <v>28.96</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>180.77</v>
       </c>
       <c r="R3" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -2612,7 +2612,7 @@
         <v>101183.44</v>
       </c>
       <c r="K4" t="n">
-        <v>111564</v>
+        <v>111672</v>
       </c>
       <c r="L4" t="n">
         <v>2236.44</v>
@@ -2621,10 +2621,10 @@
         <v>682.12</v>
       </c>
       <c r="N4" t="n">
-        <v>10380.56</v>
+        <v>10488.56</v>
       </c>
       <c r="O4" t="n">
-        <v>10.26</v>
+        <v>10.37</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>649.4</v>
       </c>
       <c r="R4" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
     </row>
     <row r="5">
@@ -2674,7 +2674,7 @@
         <v>100281.66</v>
       </c>
       <c r="K5" t="n">
-        <v>102659.9</v>
+        <v>103420.45</v>
       </c>
       <c r="L5" t="n">
         <v>5453.6</v>
@@ -2683,10 +2683,10 @@
         <v>738.6900000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>2378.24</v>
+        <v>3138.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>531.85</v>
       </c>
       <c r="R5" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="6">
@@ -2715,7 +2715,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -2736,7 +2736,7 @@
         <v>100243.77</v>
       </c>
       <c r="K6" t="n">
-        <v>99044.50999999999</v>
+        <v>99349.66</v>
       </c>
       <c r="L6" t="n">
         <v>4254.86</v>
@@ -2745,10 +2745,10 @@
         <v>731.4299999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1199.26</v>
+        <v>-894.11</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2</v>
+        <v>-0.89</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>326.92</v>
       </c>
       <c r="R6" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="7">
@@ -2798,7 +2798,7 @@
         <v>101635.01</v>
       </c>
       <c r="K7" t="n">
-        <v>96654.39999999999</v>
+        <v>96808.8</v>
       </c>
       <c r="L7" t="n">
         <v>7280.72</v>
@@ -2807,10 +2807,10 @@
         <v>1179.68</v>
       </c>
       <c r="N7" t="n">
-        <v>-4980.61</v>
+        <v>-4826.21</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.9</v>
+        <v>-4.75</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>77.86</v>
       </c>
       <c r="R7" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="8">
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -2860,7 +2860,7 @@
         <v>106142.2</v>
       </c>
       <c r="K8" t="n">
-        <v>98923.5</v>
+        <v>99712</v>
       </c>
       <c r="L8" t="n">
         <v>3104.26</v>
@@ -2869,10 +2869,10 @@
         <v>673.53</v>
       </c>
       <c r="N8" t="n">
-        <v>-7218.7</v>
+        <v>-6430.2</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.8</v>
+        <v>-6.06</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>7008</v>
       </c>
       <c r="R8" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="9">
@@ -2922,7 +2922,7 @@
         <v>102356.72</v>
       </c>
       <c r="K9" t="n">
-        <v>93717</v>
+        <v>94464</v>
       </c>
       <c r="L9" t="n">
         <v>2145.67</v>
@@ -2931,10 +2931,10 @@
         <v>660.5599999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-8639.719999999999</v>
+        <v>-7892.72</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.44</v>
+        <v>-7.71</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>6551</v>
       </c>
       <c r="R9" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="10">
@@ -2963,7 +2963,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2984,7 +2984,7 @@
         <v>100383.62</v>
       </c>
       <c r="K10" t="n">
-        <v>91846.72</v>
+        <v>91993.44</v>
       </c>
       <c r="L10" t="n">
         <v>6899.45</v>
@@ -2993,10 +2993,10 @@
         <v>1152.36</v>
       </c>
       <c r="N10" t="n">
-        <v>-8536.9</v>
+        <v>-8390.18</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.5</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>99.75</v>
       </c>
       <c r="R10" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="11">
@@ -3025,7 +3025,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -3046,7 +3046,7 @@
         <v>100065.6</v>
       </c>
       <c r="K11" t="n">
-        <v>90344.32000000001</v>
+        <v>90488.64</v>
       </c>
       <c r="L11" t="n">
         <v>6828.02</v>
@@ -3055,10 +3055,10 @@
         <v>1156.53</v>
       </c>
       <c r="N11" t="n">
-        <v>-9721.280000000001</v>
+        <v>-9576.959999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.57</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>99.75</v>
       </c>
       <c r="R11" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="12">
@@ -3087,7 +3087,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -3108,7 +3108,7 @@
         <v>100188.46</v>
       </c>
       <c r="K12" t="n">
-        <v>80410.39999999999</v>
+        <v>82970.8</v>
       </c>
       <c r="L12" t="n">
         <v>1788.01</v>
@@ -3117,10 +3117,10 @@
         <v>667.01</v>
       </c>
       <c r="N12" t="n">
-        <v>-19778.06</v>
+        <v>-17217.66</v>
       </c>
       <c r="O12" t="n">
-        <v>-19.74</v>
+        <v>-17.19</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>163.33</v>
       </c>
       <c r="R12" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
     </row>
     <row r="13">
@@ -3149,7 +3149,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -3170,7 +3170,7 @@
         <v>104736.56</v>
       </c>
       <c r="K13" t="n">
-        <v>79767.10000000001</v>
+        <v>80358.05</v>
       </c>
       <c r="L13" t="n">
         <v>3408.15</v>
@@ -3179,10 +3179,10 @@
         <v>1027.6</v>
       </c>
       <c r="N13" t="n">
-        <v>-24969.46</v>
+        <v>-24378.51</v>
       </c>
       <c r="O13" t="n">
-        <v>-23.84</v>
+        <v>-23.28</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>552.5</v>
       </c>
       <c r="R13" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="14">
@@ -3211,7 +3211,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -3232,7 +3232,7 @@
         <v>100420.73</v>
       </c>
       <c r="K14" t="n">
-        <v>72255.39999999999</v>
+        <v>72790.7</v>
       </c>
       <c r="L14" t="n">
         <v>2659.45</v>
@@ -3241,10 +3241,10 @@
         <v>674.95</v>
       </c>
       <c r="N14" t="n">
-        <v>-28165.33</v>
+        <v>-27630.03</v>
       </c>
       <c r="O14" t="n">
-        <v>-28.05</v>
+        <v>-27.51</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>552.5</v>
       </c>
       <c r="R14" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="15">
@@ -3273,7 +3273,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -3294,7 +3294,7 @@
         <v>100388.1</v>
       </c>
       <c r="K15" t="n">
-        <v>68413.7</v>
+        <v>70798.89999999999</v>
       </c>
       <c r="L15" t="n">
         <v>1212.48</v>
@@ -3303,10 +3303,10 @@
         <v>636.74</v>
       </c>
       <c r="N15" t="n">
-        <v>-31974.4</v>
+        <v>-29589.2</v>
       </c>
       <c r="O15" t="n">
-        <v>-31.85</v>
+        <v>-29.47</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>1840</v>
       </c>
       <c r="R15" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="16">
@@ -3335,7 +3335,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -3356,7 +3356,7 @@
         <v>105547.82</v>
       </c>
       <c r="K16" t="n">
-        <v>64111.5</v>
+        <v>64334.25</v>
       </c>
       <c r="L16" t="n">
         <v>4930.04</v>
@@ -3365,10 +3365,10 @@
         <v>1119.03</v>
       </c>
       <c r="N16" t="n">
-        <v>-41436.32</v>
+        <v>-41213.57</v>
       </c>
       <c r="O16" t="n">
-        <v>-39.26</v>
+        <v>-39.05</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>32.35</v>
       </c>
       <c r="R16" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="17">
@@ -3397,7 +3397,7 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -3418,7 +3418,7 @@
         <v>100177.45</v>
       </c>
       <c r="K17" t="n">
-        <v>33744.48</v>
+        <v>34818.96</v>
       </c>
       <c r="L17" t="n">
         <v>3979.45</v>
@@ -3427,10 +3427,10 @@
         <v>714.54</v>
       </c>
       <c r="N17" t="n">
-        <v>-66432.97</v>
+        <v>-65358.49</v>
       </c>
       <c r="O17" t="n">
-        <v>-66.31999999999999</v>
+        <v>-65.23999999999999</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>325.7</v>
       </c>
       <c r="R17" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
     </row>
   </sheetData>
@@ -3586,7 +3586,7 @@
         <v>100693.29</v>
       </c>
       <c r="K2" t="n">
-        <v>152684.4</v>
+        <v>153019.8</v>
       </c>
       <c r="L2" t="n">
         <v>6437.73</v>
@@ -3595,10 +3595,10 @@
         <v>1257.12</v>
       </c>
       <c r="N2" t="n">
-        <v>51991.11</v>
+        <v>52326.51</v>
       </c>
       <c r="O2" t="n">
-        <v>51.63</v>
+        <v>51.97</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>470.3</v>
       </c>
       <c r="R2" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
     </row>
     <row r="3">
@@ -3648,7 +3648,7 @@
         <v>100824.62</v>
       </c>
       <c r="K3" t="n">
-        <v>152092.6</v>
+        <v>152426.7</v>
       </c>
       <c r="L3" t="n">
         <v>6374.03</v>
@@ -3657,10 +3657,10 @@
         <v>1244.44</v>
       </c>
       <c r="N3" t="n">
-        <v>51267.98</v>
+        <v>51602.08</v>
       </c>
       <c r="O3" t="n">
-        <v>50.85</v>
+        <v>51.18</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>470.3</v>
       </c>
       <c r="R3" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
     </row>
     <row r="4">
@@ -3710,7 +3710,7 @@
         <v>100315.95</v>
       </c>
       <c r="K4" t="n">
-        <v>144413.4</v>
+        <v>144553.2</v>
       </c>
       <c r="L4" t="n">
         <v>5530.27</v>
@@ -3719,10 +3719,10 @@
         <v>750.5599999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>44097.45</v>
+        <v>44237.25</v>
       </c>
       <c r="O4" t="n">
-        <v>43.96</v>
+        <v>44.1</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>470.7</v>
       </c>
       <c r="R4" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
     </row>
     <row r="5">
@@ -3772,7 +3772,7 @@
         <v>100310.23</v>
       </c>
       <c r="K5" t="n">
-        <v>128840.63</v>
+        <v>129237.58</v>
       </c>
       <c r="L5" t="n">
         <v>3365.14</v>
@@ -3781,10 +3781,10 @@
         <v>726.87</v>
       </c>
       <c r="N5" t="n">
-        <v>28530.4</v>
+        <v>28927.35</v>
       </c>
       <c r="O5" t="n">
-        <v>28.44</v>
+        <v>28.84</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>241.25</v>
       </c>
       <c r="R5" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="6">
@@ -3813,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -3834,7 +3834,7 @@
         <v>100772.35</v>
       </c>
       <c r="K6" t="n">
-        <v>122219.27</v>
+        <v>122595.82</v>
       </c>
       <c r="L6" t="n">
         <v>6160.89</v>
@@ -3843,10 +3843,10 @@
         <v>786.2</v>
       </c>
       <c r="N6" t="n">
-        <v>21446.92</v>
+        <v>21823.47</v>
       </c>
       <c r="O6" t="n">
-        <v>21.28</v>
+        <v>21.66</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>241.25</v>
       </c>
       <c r="R6" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="7">
@@ -3875,7 +3875,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3896,7 +3896,7 @@
         <v>101183.44</v>
       </c>
       <c r="K7" t="n">
-        <v>111564</v>
+        <v>111672</v>
       </c>
       <c r="L7" t="n">
         <v>2236.44</v>
@@ -3905,10 +3905,10 @@
         <v>682.12</v>
       </c>
       <c r="N7" t="n">
-        <v>10380.56</v>
+        <v>10488.56</v>
       </c>
       <c r="O7" t="n">
-        <v>10.26</v>
+        <v>10.37</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>649.4</v>
       </c>
       <c r="R7" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
     </row>
     <row r="8">
@@ -3937,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -3958,7 +3958,7 @@
         <v>106337.98</v>
       </c>
       <c r="K8" t="n">
-        <v>109336.5</v>
+        <v>110208</v>
       </c>
       <c r="L8" t="n">
         <v>6020.47</v>
@@ -3967,10 +3967,10 @@
         <v>745.62</v>
       </c>
       <c r="N8" t="n">
-        <v>2998.52</v>
+        <v>3870.02</v>
       </c>
       <c r="O8" t="n">
-        <v>2.82</v>
+        <v>3.64</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>5101</v>
       </c>
       <c r="R8" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="9">
@@ -4020,7 +4020,7 @@
         <v>100281.66</v>
       </c>
       <c r="K9" t="n">
-        <v>102659.9</v>
+        <v>103420.45</v>
       </c>
       <c r="L9" t="n">
         <v>5453.6</v>
@@ -4029,10 +4029,10 @@
         <v>738.6900000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>2378.24</v>
+        <v>3138.79</v>
       </c>
       <c r="O9" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>531.85</v>
       </c>
       <c r="R9" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="10">
@@ -4061,7 +4061,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -4082,7 +4082,7 @@
         <v>100736.25</v>
       </c>
       <c r="K10" t="n">
-        <v>99082.89999999999</v>
+        <v>99816.95</v>
       </c>
       <c r="L10" t="n">
         <v>7502.45</v>
@@ -4091,10 +4091,10 @@
         <v>1249.07</v>
       </c>
       <c r="N10" t="n">
-        <v>-1653.35</v>
+        <v>-919.3</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.64</v>
+        <v>-0.91</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>459.85</v>
       </c>
       <c r="R10" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="11">
@@ -4144,7 +4144,7 @@
         <v>101635.01</v>
       </c>
       <c r="K11" t="n">
-        <v>96654.39999999999</v>
+        <v>96808.8</v>
       </c>
       <c r="L11" t="n">
         <v>7280.72</v>
@@ -4153,10 +4153,10 @@
         <v>1179.68</v>
       </c>
       <c r="N11" t="n">
-        <v>-4980.61</v>
+        <v>-4826.21</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.9</v>
+        <v>-4.75</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>77.86</v>
       </c>
       <c r="R11" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="12">
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -4206,7 +4206,7 @@
         <v>106142.2</v>
       </c>
       <c r="K12" t="n">
-        <v>98923.5</v>
+        <v>99712</v>
       </c>
       <c r="L12" t="n">
         <v>3104.26</v>
@@ -4215,10 +4215,10 @@
         <v>673.53</v>
       </c>
       <c r="N12" t="n">
-        <v>-7218.7</v>
+        <v>-6430.2</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.8</v>
+        <v>-6.06</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>7008</v>
       </c>
       <c r="R12" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="13">
@@ -4247,7 +4247,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -4268,7 +4268,7 @@
         <v>100383.62</v>
       </c>
       <c r="K13" t="n">
-        <v>91846.72</v>
+        <v>91993.44</v>
       </c>
       <c r="L13" t="n">
         <v>6899.45</v>
@@ -4277,10 +4277,10 @@
         <v>1152.36</v>
       </c>
       <c r="N13" t="n">
-        <v>-8536.9</v>
+        <v>-8390.18</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.5</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>99.75</v>
       </c>
       <c r="R13" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="14">
@@ -4309,7 +4309,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -4330,7 +4330,7 @@
         <v>100065.6</v>
       </c>
       <c r="K14" t="n">
-        <v>90344.32000000001</v>
+        <v>90488.64</v>
       </c>
       <c r="L14" t="n">
         <v>6828.02</v>
@@ -4339,10 +4339,10 @@
         <v>1156.53</v>
       </c>
       <c r="N14" t="n">
-        <v>-9721.280000000001</v>
+        <v>-9576.959999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.57</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>99.75</v>
       </c>
       <c r="R14" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="15">
@@ -4371,7 +4371,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -4392,7 +4392,7 @@
         <v>100638.87</v>
       </c>
       <c r="K15" t="n">
-        <v>84751.3</v>
+        <v>87706.10000000001</v>
       </c>
       <c r="L15" t="n">
         <v>5936.98</v>
@@ -4401,10 +4401,10 @@
         <v>753.76</v>
       </c>
       <c r="N15" t="n">
-        <v>-15887.57</v>
+        <v>-12932.77</v>
       </c>
       <c r="O15" t="n">
-        <v>-15.79</v>
+        <v>-12.85</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>1334.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="16">
@@ -4426,58 +4426,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ROSN/MOEX</t>
+          <t>NVTK/ROSN</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>767</v>
+        <v>385</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>217</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="H16" t="n">
-        <v>847</v>
+        <v>228</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>100345.56</v>
+        <v>101461.13</v>
       </c>
       <c r="K16" t="n">
-        <v>83344.10000000001</v>
+        <v>86649.39999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>4202.89</v>
+        <v>4900.32</v>
       </c>
       <c r="M16" t="n">
-        <v>730.62</v>
+        <v>734.25</v>
       </c>
       <c r="N16" t="n">
-        <v>-17001.46</v>
+        <v>-14811.73</v>
       </c>
       <c r="O16" t="n">
-        <v>-16.94</v>
+        <v>-14.6</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>233 ROSN + cash 0.00</t>
+          <t>82 NVTK + cash 0.00</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459.85</v>
+        <v>1334.2</v>
       </c>
       <c r="R16" t="n">
-        <v>357.7</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="17">
@@ -4488,58 +4488,58 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NVTK/ROSN</t>
+          <t>ROSN/MOEX</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>385</v>
+        <v>768</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="G17" t="n">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="H17" t="n">
-        <v>228</v>
+        <v>847</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>101461.13</v>
+        <v>100345.56</v>
       </c>
       <c r="K17" t="n">
-        <v>83730.2</v>
+        <v>83961.55</v>
       </c>
       <c r="L17" t="n">
-        <v>4900.32</v>
+        <v>4202.89</v>
       </c>
       <c r="M17" t="n">
-        <v>734.25</v>
+        <v>730.62</v>
       </c>
       <c r="N17" t="n">
-        <v>-17730.93</v>
+        <v>-16384.01</v>
       </c>
       <c r="O17" t="n">
-        <v>-17.48</v>
+        <v>-16.33</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>82 NVTK + cash 0.00</t>
+          <t>233 ROSN + cash 0.00</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>1334.2</v>
+        <v>459.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1021.1</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="18">
@@ -4557,7 +4557,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -4578,7 +4578,7 @@
         <v>100188.46</v>
       </c>
       <c r="K18" t="n">
-        <v>80410.39999999999</v>
+        <v>82970.8</v>
       </c>
       <c r="L18" t="n">
         <v>1788.01</v>
@@ -4587,10 +4587,10 @@
         <v>667.01</v>
       </c>
       <c r="N18" t="n">
-        <v>-19778.06</v>
+        <v>-17217.66</v>
       </c>
       <c r="O18" t="n">
-        <v>-19.74</v>
+        <v>-17.19</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>163.33</v>
       </c>
       <c r="R18" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
     </row>
     <row r="19">
@@ -4619,7 +4619,7 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -4640,7 +4640,7 @@
         <v>100067.35</v>
       </c>
       <c r="K19" t="n">
-        <v>75509.10000000001</v>
+        <v>75771.45</v>
       </c>
       <c r="L19" t="n">
         <v>6209.02</v>
@@ -4649,10 +4649,10 @@
         <v>1151.15</v>
       </c>
       <c r="N19" t="n">
-        <v>-24558.25</v>
+        <v>-24295.9</v>
       </c>
       <c r="O19" t="n">
-        <v>-24.54</v>
+        <v>-24.28</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>25.14</v>
       </c>
       <c r="R19" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
     </row>
   </sheetData>
@@ -4808,7 +4808,7 @@
         <v>100693</v>
       </c>
       <c r="K2" t="n">
-        <v>133497</v>
+        <v>134579.9</v>
       </c>
       <c r="L2" t="n">
         <v>5127.95</v>
@@ -4817,10 +4817,10 @@
         <v>1788.31</v>
       </c>
       <c r="N2" t="n">
-        <v>32804</v>
+        <v>33886.9</v>
       </c>
       <c r="O2" t="n">
-        <v>32.58</v>
+        <v>33.65</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>169.72</v>
       </c>
       <c r="R2" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
     </row>
     <row r="3">
@@ -4870,7 +4870,7 @@
         <v>101051.96</v>
       </c>
       <c r="K3" t="n">
-        <v>114363.2</v>
+        <v>118350.4</v>
       </c>
       <c r="L3" t="n">
         <v>3785.18</v>
@@ -4879,10 +4879,10 @@
         <v>1058.55</v>
       </c>
       <c r="N3" t="n">
-        <v>13311.24</v>
+        <v>17298.44</v>
       </c>
       <c r="O3" t="n">
-        <v>13.17</v>
+        <v>17.12</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>1167.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="4">
@@ -4932,7 +4932,7 @@
         <v>100246.13</v>
       </c>
       <c r="K4" t="n">
-        <v>113114.9</v>
+        <v>113463.4</v>
       </c>
       <c r="L4" t="n">
         <v>1938.58</v>
@@ -4941,10 +4941,10 @@
         <v>671.62</v>
       </c>
       <c r="N4" t="n">
-        <v>12868.77</v>
+        <v>13217.27</v>
       </c>
       <c r="O4" t="n">
-        <v>12.84</v>
+        <v>13.18</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>289.9</v>
       </c>
       <c r="R4" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="5">
@@ -4994,7 +4994,7 @@
         <v>100414.33</v>
       </c>
       <c r="K5" t="n">
-        <v>110664</v>
+        <v>110900</v>
       </c>
       <c r="L5" t="n">
         <v>1811.8</v>
@@ -5003,10 +5003,10 @@
         <v>649.86</v>
       </c>
       <c r="N5" t="n">
-        <v>10249.67</v>
+        <v>10485.67</v>
       </c>
       <c r="O5" t="n">
-        <v>10.21</v>
+        <v>10.44</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>295.52</v>
       </c>
       <c r="R5" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
     </row>
     <row r="6">
@@ -5028,58 +5028,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SBER/TATNP</t>
+          <t>NVTK/VTBR</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>339</v>
+        <v>89</v>
       </c>
       <c r="G6" t="n">
-        <v>382</v>
+        <v>103</v>
       </c>
       <c r="H6" t="n">
-        <v>182</v>
+        <v>1492</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>100706.76</v>
+        <v>100671.58</v>
       </c>
       <c r="K6" t="n">
-        <v>105389.98</v>
+        <v>108840.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1068.53</v>
+        <v>3134.85</v>
       </c>
       <c r="M6" t="n">
-        <v>631.85</v>
+        <v>692.8200000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>4683.22</v>
+        <v>8168.52</v>
       </c>
       <c r="O6" t="n">
-        <v>4.65</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>382 SBER + cash 0.00</t>
+          <t>103 NVTK + cash 0.00</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>294.84</v>
+        <v>1119.4</v>
       </c>
       <c r="R6" t="n">
-        <v>275.89</v>
+        <v>1056.7</v>
       </c>
     </row>
     <row r="7">
@@ -5090,14 +5090,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SBER/TATN</t>
+          <t>SBER/TATNP</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -5106,42 +5106,42 @@
         <v>339</v>
       </c>
       <c r="G7" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H7" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>100535.12</v>
+        <v>100706.76</v>
       </c>
       <c r="K7" t="n">
-        <v>105114.09</v>
+        <v>105714.68</v>
       </c>
       <c r="L7" t="n">
-        <v>872.75</v>
+        <v>1068.53</v>
       </c>
       <c r="M7" t="n">
-        <v>628.72</v>
+        <v>631.85</v>
       </c>
       <c r="N7" t="n">
-        <v>4578.97</v>
+        <v>5007.92</v>
       </c>
       <c r="O7" t="n">
-        <v>4.55</v>
+        <v>4.97</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>381 SBER + cash 0.00</t>
+          <t>382 SBER + cash 0.00</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>294.84</v>
       </c>
       <c r="R7" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="8">
@@ -5152,58 +5152,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVTK/VTBR</t>
+          <t>SBER/TATN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>89</v>
+        <v>339</v>
       </c>
       <c r="G8" t="n">
-        <v>103</v>
+        <v>381</v>
       </c>
       <c r="H8" t="n">
-        <v>1492</v>
+        <v>172</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>100671.58</v>
+        <v>100535.12</v>
       </c>
       <c r="K8" t="n">
-        <v>105173.3</v>
+        <v>105437.94</v>
       </c>
       <c r="L8" t="n">
-        <v>3134.85</v>
+        <v>872.75</v>
       </c>
       <c r="M8" t="n">
-        <v>692.8200000000001</v>
+        <v>628.72</v>
       </c>
       <c r="N8" t="n">
-        <v>4501.72</v>
+        <v>4902.82</v>
       </c>
       <c r="O8" t="n">
-        <v>4.47</v>
+        <v>4.88</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>103 NVTK + cash 0.00</t>
+          <t>381 SBER + cash 0.00</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1119.4</v>
+        <v>294.84</v>
       </c>
       <c r="R8" t="n">
-        <v>1021.1</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="9">
@@ -5242,7 +5242,7 @@
         <v>100165.78</v>
       </c>
       <c r="K9" t="n">
-        <v>103017.6</v>
+        <v>103780.8</v>
       </c>
       <c r="L9" t="n">
         <v>3008.67</v>
@@ -5251,10 +5251,10 @@
         <v>1025.94</v>
       </c>
       <c r="N9" t="n">
-        <v>2851.82</v>
+        <v>3615.02</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>3.61</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>428.9</v>
       </c>
       <c r="R9" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
     </row>
     <row r="10">
@@ -5283,7 +5283,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -5304,7 +5304,7 @@
         <v>102108.92</v>
       </c>
       <c r="K10" t="n">
-        <v>56640</v>
+        <v>56356.8</v>
       </c>
       <c r="L10" t="n">
         <v>7201.32</v>
@@ -5313,10 +5313,10 @@
         <v>1460.37</v>
       </c>
       <c r="N10" t="n">
-        <v>-45468.92</v>
+        <v>-45752.12</v>
       </c>
       <c r="O10" t="n">
-        <v>-44.53</v>
+        <v>-44.81</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>2313</v>
       </c>
       <c r="R10" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
     </row>
   </sheetData>
@@ -5401,7 +5401,7 @@
         <v>1806.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E2" t="n">
         <v>1806.8</v>
@@ -5410,10 +5410,10 @@
         <v>55.94</v>
       </c>
       <c r="G2" t="n">
-        <v>-43.49</v>
+        <v>-41.52</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.39</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="3">
@@ -5431,7 +5431,7 @@
         <v>502.4</v>
       </c>
       <c r="D3" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E3" t="n">
         <v>502.4</v>
@@ -5440,10 +5440,10 @@
         <v>55.68</v>
       </c>
       <c r="G3" t="n">
-        <v>-28.8</v>
+        <v>-28.27</v>
       </c>
       <c r="H3" t="n">
-        <v>19.74</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="4">
@@ -5461,7 +5461,7 @@
         <v>6344.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E4" t="n">
         <v>6344.5</v>
@@ -5470,10 +5470,10 @@
         <v>52.71</v>
       </c>
       <c r="G4" t="n">
-        <v>-17.94</v>
+        <v>-17.28</v>
       </c>
       <c r="H4" t="n">
-        <v>35.08</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="5">
@@ -5491,7 +5491,7 @@
         <v>162.99</v>
       </c>
       <c r="D5" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E5" t="n">
         <v>162.99</v>
@@ -5500,10 +5500,10 @@
         <v>40.12</v>
       </c>
       <c r="G5" t="n">
-        <v>-42.97</v>
+        <v>-41.15</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.89</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="6">
@@ -5521,7 +5521,7 @@
         <v>169.62</v>
       </c>
       <c r="D6" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E6" t="n">
         <v>169.62</v>
@@ -5530,10 +5530,10 @@
         <v>37.72</v>
       </c>
       <c r="G6" t="n">
-        <v>-45.2</v>
+        <v>-43.45</v>
       </c>
       <c r="H6" t="n">
-        <v>-19.72</v>
+        <v>-17.17</v>
       </c>
     </row>
     <row r="7">
@@ -5551,7 +5551,7 @@
         <v>79.52</v>
       </c>
       <c r="D7" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E7" t="n">
         <v>79.52</v>
@@ -5560,10 +5560,10 @@
         <v>37.26</v>
       </c>
       <c r="G7" t="n">
-        <v>-37.02</v>
+        <v>-36.92</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.5</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5581,7 +5581,7 @@
         <v>80.53</v>
       </c>
       <c r="D8" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E8" t="n">
         <v>80.53</v>
@@ -5590,10 +5590,10 @@
         <v>37.2</v>
       </c>
       <c r="G8" t="n">
-        <v>-37.81</v>
+        <v>-37.71</v>
       </c>
       <c r="H8" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="9">
@@ -5611,7 +5611,7 @@
         <v>76.62</v>
       </c>
       <c r="D9" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E9" t="n">
         <v>76.62</v>
@@ -5620,10 +5620,10 @@
         <v>37.17</v>
       </c>
       <c r="G9" t="n">
-        <v>-34.64</v>
+        <v>-34.53</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.9</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="10">
@@ -5641,7 +5641,7 @@
         <v>1348</v>
       </c>
       <c r="D10" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E10" t="n">
         <v>1348</v>
@@ -5650,10 +5650,10 @@
         <v>33.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-24.25</v>
+        <v>-21.61</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="11">
@@ -5671,7 +5671,7 @@
         <v>174.94</v>
       </c>
       <c r="D11" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E11" t="n">
         <v>174.94</v>
@@ -5680,10 +5680,10 @@
         <v>30.92</v>
       </c>
       <c r="G11" t="n">
-        <v>-46.86</v>
+        <v>-45.17</v>
       </c>
       <c r="H11" t="n">
-        <v>-26.54</v>
+        <v>-24.2</v>
       </c>
     </row>
     <row r="12">
@@ -5701,7 +5701,7 @@
         <v>1222.8</v>
       </c>
       <c r="D12" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E12" t="n">
         <v>1222.8</v>
@@ -5710,10 +5710,10 @@
         <v>29.61</v>
       </c>
       <c r="G12" t="n">
-        <v>-16.49</v>
+        <v>-13.58</v>
       </c>
       <c r="H12" t="n">
-        <v>13.18</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="13">
@@ -5731,7 +5731,7 @@
         <v>473.95</v>
       </c>
       <c r="D13" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E13" t="n">
         <v>473.95</v>
@@ -5740,10 +5740,10 @@
         <v>29.47</v>
       </c>
       <c r="G13" t="n">
-        <v>-24.53</v>
+        <v>-23.97</v>
       </c>
       <c r="H13" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="14">
@@ -5761,7 +5761,7 @@
         <v>562.35</v>
       </c>
       <c r="D14" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E14" t="n">
         <v>562.35</v>
@@ -5770,10 +5770,10 @@
         <v>29.05</v>
       </c>
       <c r="G14" t="n">
-        <v>-36.39</v>
+        <v>-35.92</v>
       </c>
       <c r="H14" t="n">
-        <v>-14</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="15">
@@ -5791,7 +5791,7 @@
         <v>420.7</v>
       </c>
       <c r="D15" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E15" t="n">
         <v>420.7</v>
@@ -5800,10 +5800,10 @@
         <v>27.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.98</v>
+        <v>-14.35</v>
       </c>
       <c r="H15" t="n">
-        <v>12.93</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="16">
@@ -5821,7 +5821,7 @@
         <v>1525.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E16" t="n">
         <v>1525.8</v>
@@ -5830,10 +5830,10 @@
         <v>26.89</v>
       </c>
       <c r="G16" t="n">
-        <v>-33.08</v>
+        <v>-30.74</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.15</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -5851,7 +5851,7 @@
         <v>1624</v>
       </c>
       <c r="D17" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E17" t="n">
         <v>1624</v>
@@ -5860,10 +5860,10 @@
         <v>25.15</v>
       </c>
       <c r="G17" t="n">
-        <v>-37.12</v>
+        <v>-34.93</v>
       </c>
       <c r="H17" t="n">
-        <v>-17.95</v>
+        <v>-15.09</v>
       </c>
     </row>
     <row r="18">
@@ -5881,7 +5881,7 @@
         <v>162.94</v>
       </c>
       <c r="D18" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E18" t="n">
         <v>162.94</v>
@@ -5890,10 +5890,10 @@
         <v>25.13</v>
       </c>
       <c r="G18" t="n">
-        <v>-42.95</v>
+        <v>-41.13</v>
       </c>
       <c r="H18" t="n">
-        <v>-25.05</v>
+        <v>-22.67</v>
       </c>
     </row>
     <row r="19">
@@ -5911,7 +5911,7 @@
         <v>3828</v>
       </c>
       <c r="D19" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E19" t="n">
         <v>3828</v>
@@ -5920,10 +5920,10 @@
         <v>24.83</v>
       </c>
       <c r="G19" t="n">
-        <v>36.01</v>
+        <v>37.1</v>
       </c>
       <c r="H19" t="n">
-        <v>77.27</v>
+        <v>78.68000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -5941,7 +5941,7 @@
         <v>1351.6</v>
       </c>
       <c r="D20" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E20" t="n">
         <v>1351.6</v>
@@ -5950,10 +5950,10 @@
         <v>24.21</v>
       </c>
       <c r="G20" t="n">
-        <v>-24.45</v>
+        <v>-21.82</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.31</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="21">
@@ -5971,7 +5971,7 @@
         <v>58.46</v>
       </c>
       <c r="D21" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E21" t="n">
         <v>58.46</v>
@@ -5980,10 +5980,10 @@
         <v>23.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-14.33</v>
+        <v>-14.2</v>
       </c>
       <c r="H21" t="n">
-        <v>11.03</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="22">
@@ -6001,7 +6001,7 @@
         <v>6725</v>
       </c>
       <c r="D22" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E22" t="n">
         <v>6725</v>
@@ -6010,10 +6010,10 @@
         <v>22.36</v>
       </c>
       <c r="G22" t="n">
-        <v>-22.58</v>
+        <v>-21.96</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.14</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="23">
@@ -6031,7 +6031,7 @@
         <v>301.77</v>
       </c>
       <c r="D23" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E23" t="n">
         <v>301.77</v>
@@ -6040,10 +6040,10 @@
         <v>20.49</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.32</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>14.88</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="24">
@@ -6061,7 +6061,7 @@
         <v>36.35</v>
       </c>
       <c r="D24" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E24" t="n">
         <v>36.35</v>
@@ -6070,10 +6070,10 @@
         <v>17.37</v>
       </c>
       <c r="G24" t="n">
-        <v>-56.46</v>
+        <v>-56.31</v>
       </c>
       <c r="H24" t="n">
-        <v>-46.93</v>
+        <v>-46.75</v>
       </c>
     </row>
     <row r="25">
@@ -6091,7 +6091,7 @@
         <v>169.85</v>
       </c>
       <c r="D25" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E25" t="n">
         <v>169.85</v>
@@ -6100,10 +6100,10 @@
         <v>15.29</v>
       </c>
       <c r="G25" t="n">
-        <v>-45.27</v>
+        <v>-43.53</v>
       </c>
       <c r="H25" t="n">
-        <v>-34.47</v>
+        <v>-32.39</v>
       </c>
     </row>
     <row r="26">
@@ -6121,7 +6121,7 @@
         <v>600.8</v>
       </c>
       <c r="D26" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E26" t="n">
         <v>600.8</v>
@@ -6130,10 +6130,10 @@
         <v>15.08</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.5</v>
+        <v>-1.28</v>
       </c>
       <c r="H26" t="n">
-        <v>17.15</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="27">
@@ -6151,7 +6151,7 @@
         <v>140.2</v>
       </c>
       <c r="D27" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E27" t="n">
         <v>140.2</v>
@@ -6160,10 +6160,10 @@
         <v>14.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.69</v>
+        <v>-7.19</v>
       </c>
       <c r="H27" t="n">
-        <v>8.960000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6181,7 +6181,7 @@
         <v>79.59</v>
       </c>
       <c r="D28" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E28" t="n">
         <v>79.59</v>
@@ -6190,10 +6190,10 @@
         <v>14.56</v>
       </c>
       <c r="G28" t="n">
-        <v>-37.08</v>
+        <v>-36.98</v>
       </c>
       <c r="H28" t="n">
-        <v>-25.45</v>
+        <v>-25.33</v>
       </c>
     </row>
     <row r="29">
@@ -6211,7 +6211,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E29" t="n">
         <v>79.59999999999999</v>
@@ -6220,10 +6220,10 @@
         <v>13.96</v>
       </c>
       <c r="G29" t="n">
-        <v>-37.09</v>
+        <v>-36.98</v>
       </c>
       <c r="H29" t="n">
-        <v>-25.88</v>
+        <v>-25.76</v>
       </c>
     </row>
     <row r="30">
@@ -6241,7 +6241,7 @@
         <v>1390</v>
       </c>
       <c r="D30" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E30" t="n">
         <v>1390</v>
@@ -6250,10 +6250,10 @@
         <v>13.82</v>
       </c>
       <c r="G30" t="n">
-        <v>-26.54</v>
+        <v>-23.98</v>
       </c>
       <c r="H30" t="n">
-        <v>-13.92</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="31">
@@ -6271,7 +6271,7 @@
         <v>127.83</v>
       </c>
       <c r="D31" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E31" t="n">
         <v>127.83</v>
@@ -6280,10 +6280,10 @@
         <v>12.78</v>
       </c>
       <c r="G31" t="n">
-        <v>-27.28</v>
+        <v>-24.96</v>
       </c>
       <c r="H31" t="n">
-        <v>-15.65</v>
+        <v>-12.97</v>
       </c>
     </row>
     <row r="32">
@@ -6301,7 +6301,7 @@
         <v>642</v>
       </c>
       <c r="D32" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E32" t="n">
         <v>642</v>
@@ -6310,10 +6310,10 @@
         <v>11.32</v>
       </c>
       <c r="G32" t="n">
-        <v>-3.46</v>
+        <v>-3.36</v>
       </c>
       <c r="H32" t="n">
-        <v>10.26</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="33">
@@ -6331,7 +6331,7 @@
         <v>159.3</v>
       </c>
       <c r="D33" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E33" t="n">
         <v>159.3</v>
@@ -6340,10 +6340,10 @@
         <v>10.49</v>
       </c>
       <c r="G33" t="n">
-        <v>-18.76</v>
+        <v>-18.32</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.85</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="34">
@@ -6361,7 +6361,7 @@
         <v>46.12</v>
       </c>
       <c r="D34" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E34" t="n">
         <v>46.12</v>
@@ -6370,10 +6370,10 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>-65.68000000000001</v>
+        <v>-65.56</v>
       </c>
       <c r="H34" t="n">
-        <v>-61.36</v>
+        <v>-61.22</v>
       </c>
     </row>
     <row r="35">
@@ -6391,7 +6391,7 @@
         <v>171.86</v>
       </c>
       <c r="D35" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E35" t="n">
         <v>171.86</v>
@@ -6400,10 +6400,10 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>-45.91</v>
+        <v>-44.19</v>
       </c>
       <c r="H35" t="n">
-        <v>-39.13</v>
+        <v>-37.19</v>
       </c>
     </row>
     <row r="36">
@@ -6421,7 +6421,7 @@
         <v>6335.5</v>
       </c>
       <c r="D36" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E36" t="n">
         <v>6335.5</v>
@@ -6430,10 +6430,10 @@
         <v>9.85</v>
       </c>
       <c r="G36" t="n">
-        <v>-17.82</v>
+        <v>-17.17</v>
       </c>
       <c r="H36" t="n">
-        <v>-6.8</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="37">
@@ -6451,7 +6451,7 @@
         <v>720</v>
       </c>
       <c r="D37" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E37" t="n">
         <v>720</v>
@@ -6460,10 +6460,10 @@
         <v>9.26</v>
       </c>
       <c r="G37" t="n">
-        <v>-17.81</v>
+        <v>-17.62</v>
       </c>
       <c r="H37" t="n">
-        <v>-8.51</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="38">
@@ -6481,7 +6481,7 @@
         <v>128.76</v>
       </c>
       <c r="D38" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E38" t="n">
         <v>128.76</v>
@@ -6490,10 +6490,10 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>-27.8</v>
+        <v>-25.5</v>
       </c>
       <c r="H38" t="n">
-        <v>-19.74</v>
+        <v>-17.19</v>
       </c>
     </row>
     <row r="39">
@@ -6511,7 +6511,7 @@
         <v>788.9</v>
       </c>
       <c r="D39" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E39" t="n">
         <v>788.9</v>
@@ -6520,10 +6520,10 @@
         <v>7.28</v>
       </c>
       <c r="G39" t="n">
-        <v>-21.43</v>
+        <v>-21.36</v>
       </c>
       <c r="H39" t="n">
-        <v>-14.31</v>
+        <v>-14.23</v>
       </c>
     </row>
     <row r="40">
@@ -6541,7 +6541,7 @@
         <v>47.8</v>
       </c>
       <c r="D40" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E40" t="n">
         <v>47.8</v>
@@ -6550,10 +6550,10 @@
         <v>6.61</v>
       </c>
       <c r="G40" t="n">
-        <v>-66.88</v>
+        <v>-66.77</v>
       </c>
       <c r="H40" t="n">
-        <v>-64.16</v>
+        <v>-64.03</v>
       </c>
     </row>
     <row r="41">
@@ -6571,7 +6571,7 @@
         <v>46.05</v>
       </c>
       <c r="D41" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E41" t="n">
         <v>46.05</v>
@@ -6580,10 +6580,10 @@
         <v>6.27</v>
       </c>
       <c r="G41" t="n">
-        <v>-65.62</v>
+        <v>-65.5</v>
       </c>
       <c r="H41" t="n">
-        <v>-62.77</v>
+        <v>-62.64</v>
       </c>
     </row>
     <row r="42">
@@ -6601,7 +6601,7 @@
         <v>22.05</v>
       </c>
       <c r="D42" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E42" t="n">
         <v>22.05</v>
@@ -6610,10 +6610,10 @@
         <v>5.4</v>
       </c>
       <c r="G42" t="n">
-        <v>-28.21</v>
+        <v>-27.96</v>
       </c>
       <c r="H42" t="n">
-        <v>-23.04</v>
+        <v>-22.77</v>
       </c>
     </row>
     <row r="43">
@@ -6631,7 +6631,7 @@
         <v>176.65</v>
       </c>
       <c r="D43" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E43" t="n">
         <v>176.65</v>
@@ -6640,10 +6640,10 @@
         <v>4.92</v>
       </c>
       <c r="G43" t="n">
-        <v>-47.38</v>
+        <v>-45.7</v>
       </c>
       <c r="H43" t="n">
-        <v>-43.67</v>
+        <v>-41.87</v>
       </c>
     </row>
     <row r="44">
@@ -6661,7 +6661,7 @@
         <v>779</v>
       </c>
       <c r="D44" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E44" t="n">
         <v>779</v>
@@ -6670,10 +6670,10 @@
         <v>4.82</v>
       </c>
       <c r="G44" t="n">
-        <v>-20.44</v>
+        <v>-20.36</v>
       </c>
       <c r="H44" t="n">
-        <v>-15.55</v>
+        <v>-15.46</v>
       </c>
     </row>
     <row r="45">
@@ -6691,7 +6691,7 @@
         <v>157.59</v>
       </c>
       <c r="D45" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E45" t="n">
         <v>157.59</v>
@@ -6700,10 +6700,10 @@
         <v>4.44</v>
       </c>
       <c r="G45" t="n">
-        <v>-41.01</v>
+        <v>-39.13</v>
       </c>
       <c r="H45" t="n">
-        <v>-37.43</v>
+        <v>-35.43</v>
       </c>
     </row>
     <row r="46">
@@ -6721,7 +6721,7 @@
         <v>759.7</v>
       </c>
       <c r="D46" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E46" t="n">
         <v>759.7</v>
@@ -6730,10 +6730,10 @@
         <v>4.29</v>
       </c>
       <c r="G46" t="n">
-        <v>-18.42</v>
+        <v>-18.34</v>
       </c>
       <c r="H46" t="n">
-        <v>-14</v>
+        <v>-13.92</v>
       </c>
     </row>
     <row r="47">
@@ -6751,7 +6751,7 @@
         <v>88.14</v>
       </c>
       <c r="D47" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E47" t="n">
         <v>88.14</v>
@@ -6760,10 +6760,10 @@
         <v>4.2</v>
       </c>
       <c r="G47" t="n">
-        <v>-43.18</v>
+        <v>-43.09</v>
       </c>
       <c r="H47" t="n">
-        <v>-40.13</v>
+        <v>-40.03</v>
       </c>
     </row>
     <row r="48">
@@ -6781,7 +6781,7 @@
         <v>46.5</v>
       </c>
       <c r="D48" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E48" t="n">
         <v>46.5</v>
@@ -6790,10 +6790,10 @@
         <v>3.9</v>
       </c>
       <c r="G48" t="n">
-        <v>-65.95999999999999</v>
+        <v>-65.84</v>
       </c>
       <c r="H48" t="n">
-        <v>-64.25</v>
+        <v>-64.13</v>
       </c>
     </row>
     <row r="49">
@@ -6811,7 +6811,7 @@
         <v>155.08</v>
       </c>
       <c r="D49" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E49" t="n">
         <v>155.08</v>
@@ -6820,10 +6820,10 @@
         <v>3.82</v>
       </c>
       <c r="G49" t="n">
-        <v>-16.55</v>
+        <v>-16.09</v>
       </c>
       <c r="H49" t="n">
-        <v>-12.08</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="50">
@@ -6841,7 +6841,7 @@
         <v>216.16</v>
       </c>
       <c r="D50" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E50" t="n">
         <v>216.16</v>
@@ -6850,10 +6850,10 @@
         <v>3.1</v>
       </c>
       <c r="G50" t="n">
-        <v>27.99</v>
+        <v>28.26</v>
       </c>
       <c r="H50" t="n">
-        <v>33.2</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="51">
@@ -6871,7 +6871,7 @@
         <v>36.74</v>
       </c>
       <c r="D51" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E51" t="n">
         <v>36.74</v>
@@ -6880,10 +6880,10 @@
         <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>-56.92</v>
+        <v>-56.77</v>
       </c>
       <c r="H51" t="n">
-        <v>-54.95</v>
+        <v>-54.79</v>
       </c>
     </row>
     <row r="52">
@@ -6901,7 +6901,7 @@
         <v>761</v>
       </c>
       <c r="D52" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E52" t="n">
         <v>761</v>
@@ -6910,10 +6910,10 @@
         <v>2.84</v>
       </c>
       <c r="G52" t="n">
-        <v>-18.55</v>
+        <v>-18.48</v>
       </c>
       <c r="H52" t="n">
-        <v>-15.47</v>
+        <v>-15.39</v>
       </c>
     </row>
     <row r="53">
@@ -6931,7 +6931,7 @@
         <v>195.3</v>
       </c>
       <c r="D53" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E53" t="n">
         <v>195.3</v>
@@ -6940,10 +6940,10 @@
         <v>2.43</v>
       </c>
       <c r="G53" t="n">
-        <v>-24.88</v>
+        <v>-24.28</v>
       </c>
       <c r="H53" t="n">
-        <v>-22.4</v>
+        <v>-21.77</v>
       </c>
     </row>
     <row r="54">
@@ -6961,7 +6961,7 @@
         <v>404.75</v>
       </c>
       <c r="D54" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E54" t="n">
         <v>404.75</v>
@@ -6970,10 +6970,10 @@
         <v>2.35</v>
       </c>
       <c r="G54" t="n">
-        <v>-11.62</v>
+        <v>-10.97</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.85</v>
+        <v>-8.18</v>
       </c>
     </row>
     <row r="55">
@@ -6991,7 +6991,7 @@
         <v>183.56</v>
       </c>
       <c r="D55" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E55" t="n">
         <v>183.56</v>
@@ -7000,10 +7000,10 @@
         <v>2.1</v>
       </c>
       <c r="G55" t="n">
-        <v>-20.08</v>
+        <v>-19.43</v>
       </c>
       <c r="H55" t="n">
-        <v>-17.77</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="56">
@@ -7021,7 +7021,7 @@
         <v>485.2</v>
       </c>
       <c r="D56" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E56" t="n">
         <v>485.2</v>
@@ -7030,10 +7030,10 @@
         <v>1.91</v>
       </c>
       <c r="G56" t="n">
-        <v>21.97</v>
+        <v>22.24</v>
       </c>
       <c r="H56" t="n">
-        <v>25.2</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="57">
@@ -7051,7 +7051,7 @@
         <v>152.48</v>
       </c>
       <c r="D57" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E57" t="n">
         <v>152.48</v>
@@ -7060,10 +7060,10 @@
         <v>1.8</v>
       </c>
       <c r="G57" t="n">
-        <v>-15.12</v>
+        <v>-14.66</v>
       </c>
       <c r="H57" t="n">
-        <v>-12.97</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="58">
@@ -7081,7 +7081,7 @@
         <v>541.8</v>
       </c>
       <c r="D58" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E58" t="n">
         <v>541.8</v>
@@ -7090,10 +7090,10 @@
         <v>1.67</v>
       </c>
       <c r="G58" t="n">
-        <v>9.23</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>11.91</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="59">
@@ -7111,7 +7111,7 @@
         <v>570.4</v>
       </c>
       <c r="D59" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E59" t="n">
         <v>570.4</v>
@@ -7120,10 +7120,10 @@
         <v>1.65</v>
       </c>
       <c r="G59" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="H59" t="n">
-        <v>6.2</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="60">
@@ -7141,7 +7141,7 @@
         <v>485.2</v>
       </c>
       <c r="D60" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E60" t="n">
         <v>485.2</v>
@@ -7150,10 +7150,10 @@
         <v>1.62</v>
       </c>
       <c r="G60" t="n">
-        <v>21.97</v>
+        <v>22.24</v>
       </c>
       <c r="H60" t="n">
-        <v>24.89</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="61">
@@ -7171,7 +7171,7 @@
         <v>1286</v>
       </c>
       <c r="D61" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E61" t="n">
         <v>1286</v>
@@ -7180,10 +7180,10 @@
         <v>1.41</v>
       </c>
       <c r="G61" t="n">
-        <v>-25.35</v>
+        <v>-25.72</v>
       </c>
       <c r="H61" t="n">
-        <v>-23.78</v>
+        <v>-24.16</v>
       </c>
     </row>
     <row r="62">
@@ -7201,7 +7201,7 @@
         <v>24.7</v>
       </c>
       <c r="D62" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E62" t="n">
         <v>24.7</v>
@@ -7210,10 +7210,10 @@
         <v>-0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>-35.9</v>
+        <v>-35.68</v>
       </c>
       <c r="H62" t="n">
-        <v>-35.89</v>
+        <v>-35.67</v>
       </c>
     </row>
     <row r="63">
@@ -7231,7 +7231,7 @@
         <v>302.09</v>
       </c>
       <c r="D63" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E63" t="n">
         <v>302.09</v>
@@ -7240,10 +7240,10 @@
         <v>-0.01</v>
       </c>
       <c r="G63" t="n">
-        <v>-8.67</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>-8.67</v>
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -7261,7 +7261,7 @@
         <v>28.99</v>
       </c>
       <c r="D64" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E64" t="n">
         <v>28.99</v>
@@ -7270,10 +7270,10 @@
         <v>-0.01</v>
       </c>
       <c r="G64" t="n">
-        <v>-45.39</v>
+        <v>-45.21</v>
       </c>
       <c r="H64" t="n">
-        <v>-45.39</v>
+        <v>-45.2</v>
       </c>
     </row>
     <row r="65">
@@ -7291,7 +7291,7 @@
         <v>235.77</v>
       </c>
       <c r="D65" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E65" t="n">
         <v>235.77</v>
@@ -7300,10 +7300,10 @@
         <v>-0.03</v>
       </c>
       <c r="G65" t="n">
-        <v>-37.78</v>
+        <v>-37.27</v>
       </c>
       <c r="H65" t="n">
-        <v>-37.77</v>
+        <v>-37.26</v>
       </c>
     </row>
     <row r="66">
@@ -7321,7 +7321,7 @@
         <v>46.45</v>
       </c>
       <c r="D66" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E66" t="n">
         <v>46.45</v>
@@ -7330,10 +7330,10 @@
         <v>-0.04</v>
       </c>
       <c r="G66" t="n">
-        <v>-65.92</v>
+        <v>-65.8</v>
       </c>
       <c r="H66" t="n">
-        <v>-65.89</v>
+        <v>-65.78</v>
       </c>
     </row>
     <row r="67">
@@ -7351,7 +7351,7 @@
         <v>462.8</v>
       </c>
       <c r="D67" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E67" t="n">
         <v>462.8</v>
@@ -7360,10 +7360,10 @@
         <v>-0.04</v>
       </c>
       <c r="G67" t="n">
-        <v>-22.71</v>
+        <v>-22.14</v>
       </c>
       <c r="H67" t="n">
-        <v>-22.7</v>
+        <v>-22.13</v>
       </c>
     </row>
     <row r="68">
@@ -7381,7 +7381,7 @@
         <v>46.45</v>
       </c>
       <c r="D68" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E68" t="n">
         <v>46.45</v>
@@ -7390,10 +7390,10 @@
         <v>-0.04</v>
       </c>
       <c r="G68" t="n">
-        <v>-65.92</v>
+        <v>-65.8</v>
       </c>
       <c r="H68" t="n">
-        <v>-65.89</v>
+        <v>-65.78</v>
       </c>
     </row>
     <row r="69">
@@ -7411,7 +7411,7 @@
         <v>99.75</v>
       </c>
       <c r="D69" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E69" t="n">
         <v>99.75</v>
@@ -7420,10 +7420,10 @@
         <v>-0.05</v>
       </c>
       <c r="G69" t="n">
-        <v>-49.79</v>
+        <v>-49.71</v>
       </c>
       <c r="H69" t="n">
-        <v>-49.77</v>
+        <v>-49.69</v>
       </c>
     </row>
     <row r="70">
@@ -7441,7 +7441,7 @@
         <v>240</v>
       </c>
       <c r="D70" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E70" t="n">
         <v>240</v>
@@ -7450,10 +7450,10 @@
         <v>-0.16</v>
       </c>
       <c r="G70" t="n">
-        <v>14.95</v>
+        <v>15.31</v>
       </c>
       <c r="H70" t="n">
-        <v>14.93</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="71">
@@ -7471,7 +7471,7 @@
         <v>240</v>
       </c>
       <c r="D71" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E71" t="n">
         <v>240</v>
@@ -7480,10 +7480,10 @@
         <v>-0.16</v>
       </c>
       <c r="G71" t="n">
-        <v>14.95</v>
+        <v>15.31</v>
       </c>
       <c r="H71" t="n">
-        <v>14.93</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="72">
@@ -7501,7 +7501,7 @@
         <v>458</v>
       </c>
       <c r="D72" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E72" t="n">
         <v>458</v>
@@ -7510,10 +7510,10 @@
         <v>-0.16</v>
       </c>
       <c r="G72" t="n">
-        <v>-21.9</v>
+        <v>-21.32</v>
       </c>
       <c r="H72" t="n">
-        <v>-21.87</v>
+        <v>-21.29</v>
       </c>
     </row>
     <row r="73">
@@ -7531,7 +7531,7 @@
         <v>764</v>
       </c>
       <c r="D73" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E73" t="n">
         <v>764</v>
@@ -7540,10 +7540,10 @@
         <v>-0.68</v>
       </c>
       <c r="G73" t="n">
-        <v>-18.87</v>
+        <v>-18.8</v>
       </c>
       <c r="H73" t="n">
-        <v>-18.75</v>
+        <v>-18.67</v>
       </c>
     </row>
     <row r="74">
@@ -7561,7 +7561,7 @@
         <v>764</v>
       </c>
       <c r="D74" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E74" t="n">
         <v>764</v>
@@ -7570,10 +7570,10 @@
         <v>-0.68</v>
       </c>
       <c r="G74" t="n">
-        <v>-18.87</v>
+        <v>-18.8</v>
       </c>
       <c r="H74" t="n">
-        <v>-18.75</v>
+        <v>-18.67</v>
       </c>
     </row>
     <row r="75">
@@ -7591,7 +7591,7 @@
         <v>764</v>
       </c>
       <c r="D75" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E75" t="n">
         <v>764</v>
@@ -7600,10 +7600,10 @@
         <v>-0.68</v>
       </c>
       <c r="G75" t="n">
-        <v>-18.87</v>
+        <v>-18.8</v>
       </c>
       <c r="H75" t="n">
-        <v>-18.75</v>
+        <v>-18.67</v>
       </c>
     </row>
     <row r="76">
@@ -7621,7 +7621,7 @@
         <v>1223.8</v>
       </c>
       <c r="D76" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E76" t="n">
         <v>1223.8</v>
@@ -7630,10 +7630,10 @@
         <v>-0.87</v>
       </c>
       <c r="G76" t="n">
-        <v>-16.56</v>
+        <v>-13.65</v>
       </c>
       <c r="H76" t="n">
-        <v>-16.42</v>
+        <v>-13.54</v>
       </c>
     </row>
     <row r="77">
@@ -7651,7 +7651,7 @@
         <v>6161</v>
       </c>
       <c r="D77" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E77" t="n">
         <v>6161</v>
@@ -7660,10 +7660,10 @@
         <v>-1.42</v>
       </c>
       <c r="G77" t="n">
-        <v>-15.49</v>
+        <v>-14.82</v>
       </c>
       <c r="H77" t="n">
-        <v>-15.27</v>
+        <v>-14.61</v>
       </c>
     </row>
     <row r="78">
@@ -7681,7 +7681,7 @@
         <v>6802</v>
       </c>
       <c r="D78" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E78" t="n">
         <v>6802</v>
@@ -7690,10 +7690,10 @@
         <v>-4.77</v>
       </c>
       <c r="G78" t="n">
-        <v>-23.46</v>
+        <v>-22.85</v>
       </c>
       <c r="H78" t="n">
-        <v>-22.34</v>
+        <v>-21.76</v>
       </c>
     </row>
     <row r="79">
@@ -7711,7 +7711,7 @@
         <v>7920.5</v>
       </c>
       <c r="D79" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E79" t="n">
         <v>7920.5</v>
@@ -7720,10 +7720,10 @@
         <v>-4.95</v>
       </c>
       <c r="G79" t="n">
-        <v>-34.27</v>
+        <v>-33.74</v>
       </c>
       <c r="H79" t="n">
-        <v>-32.57</v>
+        <v>-32.07</v>
       </c>
     </row>
   </sheetData>
@@ -7797,7 +7797,7 @@
         <v>79.52</v>
       </c>
       <c r="D2" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E2" t="n">
         <v>79.52</v>
@@ -7806,10 +7806,10 @@
         <v>37.26</v>
       </c>
       <c r="G2" t="n">
-        <v>-37.02</v>
+        <v>-36.92</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.5</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -7827,7 +7827,7 @@
         <v>80.53</v>
       </c>
       <c r="D3" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E3" t="n">
         <v>80.53</v>
@@ -7836,10 +7836,10 @@
         <v>37.2</v>
       </c>
       <c r="G3" t="n">
-        <v>-37.81</v>
+        <v>-37.71</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="4">
@@ -7857,7 +7857,7 @@
         <v>76.62</v>
       </c>
       <c r="D4" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E4" t="n">
         <v>76.62</v>
@@ -7866,10 +7866,10 @@
         <v>37.17</v>
       </c>
       <c r="G4" t="n">
-        <v>-34.64</v>
+        <v>-34.53</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.9</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="5">
@@ -7887,7 +7887,7 @@
         <v>5140.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E5" t="n">
         <v>5140.5</v>
@@ -7896,10 +7896,10 @@
         <v>29.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.28</v>
+        <v>2.09</v>
       </c>
       <c r="H5" t="n">
-        <v>38.3</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="6">
@@ -7917,7 +7917,7 @@
         <v>473.95</v>
       </c>
       <c r="D6" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E6" t="n">
         <v>473.95</v>
@@ -7926,10 +7926,10 @@
         <v>29.47</v>
       </c>
       <c r="G6" t="n">
-        <v>-24.53</v>
+        <v>-23.97</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7">
@@ -7947,7 +7947,7 @@
         <v>58.46</v>
       </c>
       <c r="D7" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E7" t="n">
         <v>58.46</v>
@@ -7956,10 +7956,10 @@
         <v>23.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-14.33</v>
+        <v>-14.2</v>
       </c>
       <c r="H7" t="n">
-        <v>11.03</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="8">
@@ -7977,7 +7977,7 @@
         <v>356.24</v>
       </c>
       <c r="D8" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E8" t="n">
         <v>356.24</v>
@@ -7986,10 +7986,10 @@
         <v>22.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-22.56</v>
+        <v>-22.32</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9">
@@ -8007,7 +8007,7 @@
         <v>347.44</v>
       </c>
       <c r="D9" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E9" t="n">
         <v>347.44</v>
@@ -8016,10 +8016,10 @@
         <v>21.21</v>
       </c>
       <c r="G9" t="n">
-        <v>-73.23999999999999</v>
+        <v>-72.39</v>
       </c>
       <c r="H9" t="n">
-        <v>-66.31999999999999</v>
+        <v>-65.23999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -8037,7 +8037,7 @@
         <v>32.96</v>
       </c>
       <c r="D10" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E10" t="n">
         <v>32.96</v>
@@ -8046,10 +8046,10 @@
         <v>20.74</v>
       </c>
       <c r="G10" t="n">
-        <v>-51.97</v>
+        <v>-51.81</v>
       </c>
       <c r="H10" t="n">
-        <v>-39.26</v>
+        <v>-39.05</v>
       </c>
     </row>
     <row r="11">
@@ -8067,7 +8067,7 @@
         <v>30.79</v>
       </c>
       <c r="D11" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E11" t="n">
         <v>30.79</v>
@@ -8076,10 +8076,10 @@
         <v>20.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-48.59</v>
+        <v>-48.41</v>
       </c>
       <c r="H11" t="n">
-        <v>-35.68</v>
+        <v>-35.46</v>
       </c>
     </row>
     <row r="12">
@@ -8097,7 +8097,7 @@
         <v>301.77</v>
       </c>
       <c r="D12" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E12" t="n">
         <v>301.77</v>
@@ -8106,10 +8106,10 @@
         <v>20.49</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.32</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>14.88</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="13">
@@ -8127,7 +8127,7 @@
         <v>634.5</v>
       </c>
       <c r="D13" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E13" t="n">
         <v>634.5</v>
@@ -8136,10 +8136,10 @@
         <v>17.25</v>
       </c>
       <c r="G13" t="n">
-        <v>-43.62</v>
+        <v>-43.21</v>
       </c>
       <c r="H13" t="n">
-        <v>-31.9</v>
+        <v>-31.4</v>
       </c>
     </row>
     <row r="14">
@@ -8157,7 +8157,7 @@
         <v>137.9</v>
       </c>
       <c r="D14" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E14" t="n">
         <v>137.9</v>
@@ -8166,10 +8166,10 @@
         <v>16.05</v>
       </c>
       <c r="G14" t="n">
-        <v>6.38</v>
+        <v>7.24</v>
       </c>
       <c r="H14" t="n">
-        <v>27.92</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="15">
@@ -8187,7 +8187,7 @@
         <v>600.8</v>
       </c>
       <c r="D15" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E15" t="n">
         <v>600.8</v>
@@ -8196,10 +8196,10 @@
         <v>15.08</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5</v>
+        <v>-1.28</v>
       </c>
       <c r="H15" t="n">
-        <v>17.15</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="16">
@@ -8217,7 +8217,7 @@
         <v>560.3</v>
       </c>
       <c r="D16" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E16" t="n">
         <v>560.3</v>
@@ -8226,10 +8226,10 @@
         <v>15.06</v>
       </c>
       <c r="G16" t="n">
-        <v>-36.16</v>
+        <v>-35.69</v>
       </c>
       <c r="H16" t="n">
-        <v>-23.84</v>
+        <v>-23.28</v>
       </c>
     </row>
     <row r="17">
@@ -8247,7 +8247,7 @@
         <v>172.73</v>
       </c>
       <c r="D17" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E17" t="n">
         <v>172.73</v>
@@ -8256,10 +8256,10 @@
         <v>15.03</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.07</v>
+        <v>-14.38</v>
       </c>
       <c r="H17" t="n">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18">
@@ -8277,7 +8277,7 @@
         <v>140.2</v>
       </c>
       <c r="D18" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E18" t="n">
         <v>140.2</v>
@@ -8286,10 +8286,10 @@
         <v>14.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-7.69</v>
+        <v>-7.19</v>
       </c>
       <c r="H18" t="n">
-        <v>8.960000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -8307,7 +8307,7 @@
         <v>79.59</v>
       </c>
       <c r="D19" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E19" t="n">
         <v>79.59</v>
@@ -8316,10 +8316,10 @@
         <v>14.56</v>
       </c>
       <c r="G19" t="n">
-        <v>-37.08</v>
+        <v>-36.98</v>
       </c>
       <c r="H19" t="n">
-        <v>-25.45</v>
+        <v>-25.33</v>
       </c>
     </row>
     <row r="20">
@@ -8337,7 +8337,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E20" t="n">
         <v>79.59999999999999</v>
@@ -8346,10 +8346,10 @@
         <v>13.96</v>
       </c>
       <c r="G20" t="n">
-        <v>-37.09</v>
+        <v>-36.98</v>
       </c>
       <c r="H20" t="n">
-        <v>-25.88</v>
+        <v>-25.76</v>
       </c>
     </row>
     <row r="21">
@@ -8367,7 +8367,7 @@
         <v>581.5</v>
       </c>
       <c r="D21" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E21" t="n">
         <v>581.5</v>
@@ -8376,10 +8376,10 @@
         <v>13.65</v>
       </c>
       <c r="G21" t="n">
-        <v>-38.49</v>
+        <v>-38.03</v>
       </c>
       <c r="H21" t="n">
-        <v>-28.05</v>
+        <v>-27.51</v>
       </c>
     </row>
     <row r="22">
@@ -8397,7 +8397,7 @@
         <v>26.76</v>
       </c>
       <c r="D22" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E22" t="n">
         <v>26.76</v>
@@ -8406,10 +8406,10 @@
         <v>13.1</v>
       </c>
       <c r="G22" t="n">
-        <v>-40.84</v>
+        <v>-40.64</v>
       </c>
       <c r="H22" t="n">
-        <v>-31.2</v>
+        <v>-30.96</v>
       </c>
     </row>
     <row r="23">
@@ -8427,7 +8427,7 @@
         <v>127.83</v>
       </c>
       <c r="D23" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E23" t="n">
         <v>127.83</v>
@@ -8436,10 +8436,10 @@
         <v>12.78</v>
       </c>
       <c r="G23" t="n">
-        <v>-27.28</v>
+        <v>-24.96</v>
       </c>
       <c r="H23" t="n">
-        <v>-15.65</v>
+        <v>-12.97</v>
       </c>
     </row>
     <row r="24">
@@ -8457,7 +8457,7 @@
         <v>6560</v>
       </c>
       <c r="D24" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E24" t="n">
         <v>6560</v>
@@ -8466,10 +8466,10 @@
         <v>12.62</v>
       </c>
       <c r="G24" t="n">
-        <v>-20.63</v>
+        <v>-20</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.44</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="25">
@@ -8487,7 +8487,7 @@
         <v>245.18</v>
       </c>
       <c r="D25" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E25" t="n">
         <v>245.18</v>
@@ -8496,10 +8496,10 @@
         <v>11.64</v>
       </c>
       <c r="G25" t="n">
-        <v>12.53</v>
+        <v>12.87</v>
       </c>
       <c r="H25" t="n">
-        <v>29.02</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="26">
@@ -8517,7 +8517,7 @@
         <v>642</v>
       </c>
       <c r="D26" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E26" t="n">
         <v>642</v>
@@ -8526,10 +8526,10 @@
         <v>11.32</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.46</v>
+        <v>-3.36</v>
       </c>
       <c r="H26" t="n">
-        <v>10.26</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="27">
@@ -8547,7 +8547,7 @@
         <v>171.86</v>
       </c>
       <c r="D27" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E27" t="n">
         <v>171.86</v>
@@ -8556,10 +8556,10 @@
         <v>11.01</v>
       </c>
       <c r="G27" t="n">
-        <v>-45.91</v>
+        <v>-44.19</v>
       </c>
       <c r="H27" t="n">
-        <v>-38.38</v>
+        <v>-36.42</v>
       </c>
     </row>
     <row r="28">
@@ -8577,7 +8577,7 @@
         <v>478.4</v>
       </c>
       <c r="D28" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E28" t="n">
         <v>478.4</v>
@@ -8586,10 +8586,10 @@
         <v>10.78</v>
       </c>
       <c r="G28" t="n">
-        <v>-25.23</v>
+        <v>-24.68</v>
       </c>
       <c r="H28" t="n">
-        <v>-15.12</v>
+        <v>-14.49</v>
       </c>
     </row>
     <row r="29">
@@ -8607,7 +8607,7 @@
         <v>159.3</v>
       </c>
       <c r="D29" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E29" t="n">
         <v>159.3</v>
@@ -8616,10 +8616,10 @@
         <v>10.49</v>
       </c>
       <c r="G29" t="n">
-        <v>-18.76</v>
+        <v>-18.32</v>
       </c>
       <c r="H29" t="n">
-        <v>-7.85</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="30">
@@ -8637,7 +8637,7 @@
         <v>6335.5</v>
       </c>
       <c r="D30" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E30" t="n">
         <v>6335.5</v>
@@ -8646,10 +8646,10 @@
         <v>9.85</v>
       </c>
       <c r="G30" t="n">
-        <v>-17.82</v>
+        <v>-17.17</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.8</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="31">
@@ -8667,7 +8667,7 @@
         <v>508.75</v>
       </c>
       <c r="D31" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E31" t="n">
         <v>508.75</v>
@@ -8676,10 +8676,10 @@
         <v>9.43</v>
       </c>
       <c r="G31" t="n">
-        <v>-29.69</v>
+        <v>-29.17</v>
       </c>
       <c r="H31" t="n">
-        <v>-21.19</v>
+        <v>-20.61</v>
       </c>
     </row>
     <row r="32">
@@ -8697,7 +8697,7 @@
         <v>332.99</v>
       </c>
       <c r="D32" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E32" t="n">
         <v>332.99</v>
@@ -8706,10 +8706,10 @@
         <v>9.33</v>
       </c>
       <c r="G32" t="n">
-        <v>-16.92</v>
+        <v>-16.74</v>
       </c>
       <c r="H32" t="n">
-        <v>-7.44</v>
+        <v>-7.24</v>
       </c>
     </row>
     <row r="33">
@@ -8727,7 +8727,7 @@
         <v>128.76</v>
       </c>
       <c r="D33" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E33" t="n">
         <v>128.76</v>
@@ -8736,10 +8736,10 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>-27.8</v>
+        <v>-25.5</v>
       </c>
       <c r="H33" t="n">
-        <v>-19.74</v>
+        <v>-17.19</v>
       </c>
     </row>
     <row r="34">
@@ -8757,7 +8757,7 @@
         <v>5925.5</v>
       </c>
       <c r="D34" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E34" t="n">
         <v>5925.5</v>
@@ -8766,10 +8766,10 @@
         <v>7.58</v>
       </c>
       <c r="G34" t="n">
-        <v>-12.13</v>
+        <v>-11.43</v>
       </c>
       <c r="H34" t="n">
-        <v>-3.68</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="35">
@@ -8787,7 +8787,7 @@
         <v>539.55</v>
       </c>
       <c r="D35" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E35" t="n">
         <v>539.55</v>
@@ -8796,10 +8796,10 @@
         <v>6.69</v>
       </c>
       <c r="G35" t="n">
-        <v>-33.7</v>
+        <v>-33.21</v>
       </c>
       <c r="H35" t="n">
-        <v>-27.95</v>
+        <v>-27.42</v>
       </c>
     </row>
     <row r="36">
@@ -8817,7 +8817,7 @@
         <v>1930.4</v>
       </c>
       <c r="D36" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E36" t="n">
         <v>1930.4</v>
@@ -8826,10 +8826,10 @@
         <v>6.64</v>
       </c>
       <c r="G36" t="n">
-        <v>-47.1</v>
+        <v>-45.26</v>
       </c>
       <c r="H36" t="n">
-        <v>-42.64</v>
+        <v>-40.65</v>
       </c>
     </row>
     <row r="37">
@@ -8847,7 +8847,7 @@
         <v>1625.2</v>
       </c>
       <c r="D37" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E37" t="n">
         <v>1625.2</v>
@@ -8856,10 +8856,10 @@
         <v>6.63</v>
       </c>
       <c r="G37" t="n">
-        <v>-37.17</v>
+        <v>-34.98</v>
       </c>
       <c r="H37" t="n">
-        <v>-31.85</v>
+        <v>-29.47</v>
       </c>
     </row>
     <row r="38">
@@ -8877,7 +8877,7 @@
         <v>31.74</v>
       </c>
       <c r="D38" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E38" t="n">
         <v>31.74</v>
@@ -8886,10 +8886,10 @@
         <v>6.11</v>
       </c>
       <c r="G38" t="n">
-        <v>-50.13</v>
+        <v>-49.95</v>
       </c>
       <c r="H38" t="n">
-        <v>-46.12</v>
+        <v>-45.93</v>
       </c>
     </row>
     <row r="39">
@@ -8907,7 +8907,7 @@
         <v>177.77</v>
       </c>
       <c r="D39" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E39" t="n">
         <v>177.77</v>
@@ -8916,10 +8916,10 @@
         <v>5.9</v>
       </c>
       <c r="G39" t="n">
-        <v>-17.48</v>
+        <v>-16.81</v>
       </c>
       <c r="H39" t="n">
-        <v>-11.38</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="40">
@@ -8937,7 +8937,7 @@
         <v>313.5</v>
       </c>
       <c r="D40" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E40" t="n">
         <v>313.5</v>
@@ -8946,10 +8946,10 @@
         <v>5.71</v>
       </c>
       <c r="G40" t="n">
-        <v>-11.75</v>
+        <v>-11.56</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.39</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="41">
@@ -8967,7 +8967,7 @@
         <v>1867</v>
       </c>
       <c r="D41" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E41" t="n">
         <v>1867</v>
@@ -8976,10 +8976,10 @@
         <v>5.59</v>
       </c>
       <c r="G41" t="n">
-        <v>-45.31</v>
+        <v>-43.4</v>
       </c>
       <c r="H41" t="n">
-        <v>-41.44</v>
+        <v>-39.4</v>
       </c>
     </row>
     <row r="42">
@@ -8997,7 +8997,7 @@
         <v>169.5</v>
       </c>
       <c r="D42" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E42" t="n">
         <v>169.5</v>
@@ -9006,10 +9006,10 @@
         <v>5.47</v>
       </c>
       <c r="G42" t="n">
-        <v>-45.16</v>
+        <v>-43.41</v>
       </c>
       <c r="H42" t="n">
-        <v>-41.18</v>
+        <v>-39.31</v>
       </c>
     </row>
     <row r="43">
@@ -9027,7 +9027,7 @@
         <v>22.05</v>
       </c>
       <c r="D43" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E43" t="n">
         <v>22.05</v>
@@ -9036,10 +9036,10 @@
         <v>5.4</v>
       </c>
       <c r="G43" t="n">
-        <v>-28.21</v>
+        <v>-27.96</v>
       </c>
       <c r="H43" t="n">
-        <v>-23.04</v>
+        <v>-22.77</v>
       </c>
     </row>
     <row r="44">
@@ -9057,7 +9057,7 @@
         <v>5302.5</v>
       </c>
       <c r="D44" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E44" t="n">
         <v>5302.5</v>
@@ -9066,10 +9066,10 @@
         <v>5.33</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.81</v>
+        <v>-1.03</v>
       </c>
       <c r="H44" t="n">
-        <v>5.44</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="45">
@@ -9087,7 +9087,7 @@
         <v>169.5</v>
       </c>
       <c r="D45" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E45" t="n">
         <v>169.5</v>
@@ -9096,10 +9096,10 @@
         <v>4.87</v>
       </c>
       <c r="G45" t="n">
-        <v>-45.16</v>
+        <v>-43.41</v>
       </c>
       <c r="H45" t="n">
-        <v>-41.17</v>
+        <v>-39.3</v>
       </c>
     </row>
     <row r="46">
@@ -9117,7 +9117,7 @@
         <v>156.16</v>
       </c>
       <c r="D46" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E46" t="n">
         <v>156.16</v>
@@ -9126,10 +9126,10 @@
         <v>4.87</v>
       </c>
       <c r="G46" t="n">
-        <v>-40.47</v>
+        <v>-38.58</v>
       </c>
       <c r="H46" t="n">
-        <v>-36.51</v>
+        <v>-34.49</v>
       </c>
     </row>
     <row r="47">
@@ -9147,7 +9147,7 @@
         <v>167.88</v>
       </c>
       <c r="D47" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E47" t="n">
         <v>167.88</v>
@@ -9156,10 +9156,10 @@
         <v>4.56</v>
       </c>
       <c r="G47" t="n">
-        <v>-44.63</v>
+        <v>-42.86</v>
       </c>
       <c r="H47" t="n">
-        <v>-41.18</v>
+        <v>-39.31</v>
       </c>
     </row>
     <row r="48">
@@ -9177,7 +9177,7 @@
         <v>1867</v>
       </c>
       <c r="D48" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E48" t="n">
         <v>1867</v>
@@ -9186,10 +9186,10 @@
         <v>4.41</v>
       </c>
       <c r="G48" t="n">
-        <v>-45.31</v>
+        <v>-43.4</v>
       </c>
       <c r="H48" t="n">
-        <v>-42.27</v>
+        <v>-40.25</v>
       </c>
     </row>
     <row r="49">
@@ -9207,7 +9207,7 @@
         <v>88.14</v>
       </c>
       <c r="D49" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E49" t="n">
         <v>88.14</v>
@@ -9216,10 +9216,10 @@
         <v>4.2</v>
       </c>
       <c r="G49" t="n">
-        <v>-43.18</v>
+        <v>-43.09</v>
       </c>
       <c r="H49" t="n">
-        <v>-40.13</v>
+        <v>-40.03</v>
       </c>
     </row>
     <row r="50">
@@ -9237,7 +9237,7 @@
         <v>463.7</v>
       </c>
       <c r="D50" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E50" t="n">
         <v>463.7</v>
@@ -9246,10 +9246,10 @@
         <v>4.08</v>
       </c>
       <c r="G50" t="n">
-        <v>33.66</v>
+        <v>33.79</v>
       </c>
       <c r="H50" t="n">
-        <v>41.07</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="51">
@@ -9267,7 +9267,7 @@
         <v>155.08</v>
       </c>
       <c r="D51" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E51" t="n">
         <v>155.08</v>
@@ -9276,10 +9276,10 @@
         <v>3.82</v>
       </c>
       <c r="G51" t="n">
-        <v>-16.55</v>
+        <v>-16.09</v>
       </c>
       <c r="H51" t="n">
-        <v>-12.08</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="52">
@@ -9297,7 +9297,7 @@
         <v>29.07</v>
       </c>
       <c r="D52" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E52" t="n">
         <v>29.07</v>
@@ -9306,10 +9306,10 @@
         <v>3.72</v>
       </c>
       <c r="G52" t="n">
-        <v>-45.54</v>
+        <v>-45.35</v>
       </c>
       <c r="H52" t="n">
-        <v>-42.68</v>
+        <v>-42.48</v>
       </c>
     </row>
     <row r="53">
@@ -9327,7 +9327,7 @@
         <v>1854.2</v>
       </c>
       <c r="D53" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E53" t="n">
         <v>1854.2</v>
@@ -9336,10 +9336,10 @@
         <v>3.62</v>
       </c>
       <c r="G53" t="n">
-        <v>-44.93</v>
+        <v>-43.01</v>
       </c>
       <c r="H53" t="n">
-        <v>-42.35</v>
+        <v>-40.34</v>
       </c>
     </row>
     <row r="54">
@@ -9357,7 +9357,7 @@
         <v>327.02</v>
       </c>
       <c r="D54" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E54" t="n">
         <v>327.02</v>
@@ -9366,10 +9366,10 @@
         <v>3.51</v>
       </c>
       <c r="G54" t="n">
-        <v>-15.64</v>
+        <v>-15.38</v>
       </c>
       <c r="H54" t="n">
-        <v>-11.81</v>
+        <v>-11.54</v>
       </c>
     </row>
     <row r="55">
@@ -9387,7 +9387,7 @@
         <v>195.3</v>
       </c>
       <c r="D55" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E55" t="n">
         <v>195.3</v>
@@ -9396,10 +9396,10 @@
         <v>2.43</v>
       </c>
       <c r="G55" t="n">
-        <v>-24.88</v>
+        <v>-24.28</v>
       </c>
       <c r="H55" t="n">
-        <v>-22.4</v>
+        <v>-21.77</v>
       </c>
     </row>
     <row r="56">
@@ -9417,7 +9417,7 @@
         <v>404.75</v>
       </c>
       <c r="D56" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E56" t="n">
         <v>404.75</v>
@@ -9426,10 +9426,10 @@
         <v>2.35</v>
       </c>
       <c r="G56" t="n">
-        <v>-11.62</v>
+        <v>-10.97</v>
       </c>
       <c r="H56" t="n">
-        <v>-8.85</v>
+        <v>-8.18</v>
       </c>
     </row>
     <row r="57">
@@ -9447,7 +9447,7 @@
         <v>183.56</v>
       </c>
       <c r="D57" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E57" t="n">
         <v>183.56</v>
@@ -9456,10 +9456,10 @@
         <v>2.1</v>
       </c>
       <c r="G57" t="n">
-        <v>-20.08</v>
+        <v>-19.43</v>
       </c>
       <c r="H57" t="n">
-        <v>-17.77</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="58">
@@ -9477,7 +9477,7 @@
         <v>152.48</v>
       </c>
       <c r="D58" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E58" t="n">
         <v>152.48</v>
@@ -9486,10 +9486,10 @@
         <v>1.8</v>
       </c>
       <c r="G58" t="n">
-        <v>-15.12</v>
+        <v>-14.66</v>
       </c>
       <c r="H58" t="n">
-        <v>-12.97</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="59">
@@ -9507,7 +9507,7 @@
         <v>541.8</v>
       </c>
       <c r="D59" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E59" t="n">
         <v>541.8</v>
@@ -9516,10 +9516,10 @@
         <v>1.67</v>
       </c>
       <c r="G59" t="n">
-        <v>9.23</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>11.91</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="60">
@@ -9537,7 +9537,7 @@
         <v>5684</v>
       </c>
       <c r="D60" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E60" t="n">
         <v>5684</v>
@@ -9546,10 +9546,10 @@
         <v>1.57</v>
       </c>
       <c r="G60" t="n">
-        <v>-8.4</v>
+        <v>-7.67</v>
       </c>
       <c r="H60" t="n">
-        <v>-5.48</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="61">
@@ -9567,7 +9567,7 @@
         <v>1286</v>
       </c>
       <c r="D61" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E61" t="n">
         <v>1286</v>
@@ -9576,10 +9576,10 @@
         <v>1.41</v>
       </c>
       <c r="G61" t="n">
-        <v>-25.35</v>
+        <v>-25.72</v>
       </c>
       <c r="H61" t="n">
-        <v>-23.78</v>
+        <v>-24.16</v>
       </c>
     </row>
     <row r="62">
@@ -9597,7 +9597,7 @@
         <v>325.7</v>
       </c>
       <c r="D62" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E62" t="n">
         <v>325.7</v>
@@ -9606,10 +9606,10 @@
         <v>-0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>-71.45999999999999</v>
+        <v>-70.55</v>
       </c>
       <c r="H62" t="n">
-        <v>-71.45</v>
+        <v>-70.54000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -9627,7 +9627,7 @@
         <v>302.09</v>
       </c>
       <c r="D63" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E63" t="n">
         <v>302.09</v>
@@ -9636,10 +9636,10 @@
         <v>-0.01</v>
       </c>
       <c r="G63" t="n">
-        <v>-8.67</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>-8.67</v>
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -9657,7 +9657,7 @@
         <v>28.99</v>
       </c>
       <c r="D64" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E64" t="n">
         <v>28.99</v>
@@ -9666,10 +9666,10 @@
         <v>-0.01</v>
       </c>
       <c r="G64" t="n">
-        <v>-45.39</v>
+        <v>-45.21</v>
       </c>
       <c r="H64" t="n">
-        <v>-45.39</v>
+        <v>-45.2</v>
       </c>
     </row>
     <row r="65">
@@ -9687,7 +9687,7 @@
         <v>24.7</v>
       </c>
       <c r="D65" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E65" t="n">
         <v>24.7</v>
@@ -9696,10 +9696,10 @@
         <v>-0.01</v>
       </c>
       <c r="G65" t="n">
-        <v>-35.9</v>
+        <v>-35.68</v>
       </c>
       <c r="H65" t="n">
-        <v>-35.89</v>
+        <v>-35.67</v>
       </c>
     </row>
     <row r="66">
@@ -9717,7 +9717,7 @@
         <v>235.77</v>
       </c>
       <c r="D66" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E66" t="n">
         <v>235.77</v>
@@ -9726,10 +9726,10 @@
         <v>-0.03</v>
       </c>
       <c r="G66" t="n">
-        <v>-37.78</v>
+        <v>-37.27</v>
       </c>
       <c r="H66" t="n">
-        <v>-37.77</v>
+        <v>-37.26</v>
       </c>
     </row>
     <row r="67">
@@ -9747,7 +9747,7 @@
         <v>180.77</v>
       </c>
       <c r="D67" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E67" t="n">
         <v>180.77</v>
@@ -9756,10 +9756,10 @@
         <v>-0.03</v>
       </c>
       <c r="G67" t="n">
-        <v>-18.85</v>
+        <v>-18.19</v>
       </c>
       <c r="H67" t="n">
-        <v>-18.84</v>
+        <v>-18.18</v>
       </c>
     </row>
     <row r="68">
@@ -9777,7 +9777,7 @@
         <v>462.8</v>
       </c>
       <c r="D68" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E68" t="n">
         <v>462.8</v>
@@ -9786,10 +9786,10 @@
         <v>-0.04</v>
       </c>
       <c r="G68" t="n">
-        <v>-22.71</v>
+        <v>-22.14</v>
       </c>
       <c r="H68" t="n">
-        <v>-22.7</v>
+        <v>-22.13</v>
       </c>
     </row>
     <row r="69">
@@ -9807,7 +9807,7 @@
         <v>99.75</v>
       </c>
       <c r="D69" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E69" t="n">
         <v>99.75</v>
@@ -9816,10 +9816,10 @@
         <v>-0.05</v>
       </c>
       <c r="G69" t="n">
-        <v>-49.79</v>
+        <v>-49.71</v>
       </c>
       <c r="H69" t="n">
-        <v>-49.77</v>
+        <v>-49.69</v>
       </c>
     </row>
     <row r="70">
@@ -9837,7 +9837,7 @@
         <v>308.3</v>
       </c>
       <c r="D70" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E70" t="n">
         <v>308.3</v>
@@ -9846,10 +9846,10 @@
         <v>-0.11</v>
       </c>
       <c r="G70" t="n">
-        <v>-10.26</v>
+        <v>-10.07</v>
       </c>
       <c r="H70" t="n">
-        <v>-10.25</v>
+        <v>-10.06</v>
       </c>
     </row>
     <row r="71">
@@ -9867,7 +9867,7 @@
         <v>326.92</v>
       </c>
       <c r="D71" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E71" t="n">
         <v>326.92</v>
@@ -9876,10 +9876,10 @@
         <v>-0.29</v>
       </c>
       <c r="G71" t="n">
-        <v>-15.61</v>
+        <v>-15.35</v>
       </c>
       <c r="H71" t="n">
-        <v>-15.56</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="72">
@@ -9897,7 +9897,7 @@
         <v>326.92</v>
       </c>
       <c r="D72" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E72" t="n">
         <v>326.92</v>
@@ -9906,10 +9906,10 @@
         <v>-0.29</v>
       </c>
       <c r="G72" t="n">
-        <v>-15.61</v>
+        <v>-15.35</v>
       </c>
       <c r="H72" t="n">
-        <v>-15.56</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="73">
@@ -9927,7 +9927,7 @@
         <v>1840</v>
       </c>
       <c r="D73" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E73" t="n">
         <v>1840</v>
@@ -9936,10 +9936,10 @@
         <v>-0.64</v>
       </c>
       <c r="G73" t="n">
-        <v>-44.51</v>
+        <v>-42.57</v>
       </c>
       <c r="H73" t="n">
-        <v>-44.22</v>
+        <v>-42.3</v>
       </c>
     </row>
     <row r="74">
@@ -9957,7 +9957,7 @@
         <v>1840</v>
       </c>
       <c r="D74" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E74" t="n">
         <v>1840</v>
@@ -9966,10 +9966,10 @@
         <v>-0.64</v>
       </c>
       <c r="G74" t="n">
-        <v>-44.51</v>
+        <v>-42.57</v>
       </c>
       <c r="H74" t="n">
-        <v>-44.22</v>
+        <v>-42.3</v>
       </c>
     </row>
     <row r="75">
@@ -9987,7 +9987,7 @@
         <v>1840</v>
       </c>
       <c r="D75" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E75" t="n">
         <v>1840</v>
@@ -9996,10 +9996,10 @@
         <v>-0.64</v>
       </c>
       <c r="G75" t="n">
-        <v>-44.51</v>
+        <v>-42.57</v>
       </c>
       <c r="H75" t="n">
-        <v>-44.22</v>
+        <v>-42.3</v>
       </c>
     </row>
     <row r="76">
@@ -10017,7 +10017,7 @@
         <v>1840</v>
       </c>
       <c r="D76" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E76" t="n">
         <v>1840</v>
@@ -10026,10 +10026,10 @@
         <v>-0.64</v>
       </c>
       <c r="G76" t="n">
-        <v>-44.51</v>
+        <v>-42.57</v>
       </c>
       <c r="H76" t="n">
-        <v>-44.22</v>
+        <v>-42.3</v>
       </c>
     </row>
     <row r="77">
@@ -10047,7 +10047,7 @@
         <v>1223.8</v>
       </c>
       <c r="D77" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E77" t="n">
         <v>1223.8</v>
@@ -10056,10 +10056,10 @@
         <v>-0.87</v>
       </c>
       <c r="G77" t="n">
-        <v>-16.56</v>
+        <v>-13.65</v>
       </c>
       <c r="H77" t="n">
-        <v>-16.42</v>
+        <v>-13.54</v>
       </c>
     </row>
     <row r="78">
@@ -10077,7 +10077,7 @@
         <v>6802</v>
       </c>
       <c r="D78" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E78" t="n">
         <v>6802</v>
@@ -10086,10 +10086,10 @@
         <v>-4.77</v>
       </c>
       <c r="G78" t="n">
-        <v>-23.46</v>
+        <v>-22.85</v>
       </c>
       <c r="H78" t="n">
-        <v>-22.34</v>
+        <v>-21.76</v>
       </c>
     </row>
     <row r="79">
@@ -10107,7 +10107,7 @@
         <v>7920.5</v>
       </c>
       <c r="D79" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E79" t="n">
         <v>7920.5</v>
@@ -10116,10 +10116,10 @@
         <v>-4.95</v>
       </c>
       <c r="G79" t="n">
-        <v>-34.27</v>
+        <v>-33.74</v>
       </c>
       <c r="H79" t="n">
-        <v>-32.57</v>
+        <v>-32.07</v>
       </c>
     </row>
   </sheetData>
@@ -10193,7 +10193,7 @@
         <v>24.98</v>
       </c>
       <c r="D2" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E2" t="n">
         <v>24.98</v>
@@ -10202,10 +10202,10 @@
         <v>46.38</v>
       </c>
       <c r="G2" t="n">
-        <v>-36.63</v>
+        <v>-36.41</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.68</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="3">
@@ -10223,7 +10223,7 @@
         <v>714</v>
       </c>
       <c r="D3" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E3" t="n">
         <v>714</v>
@@ -10232,10 +10232,10 @@
         <v>43.56</v>
       </c>
       <c r="G3" t="n">
-        <v>-17.11</v>
+        <v>-16.93</v>
       </c>
       <c r="H3" t="n">
-        <v>25.82</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="4">
@@ -10253,7 +10253,7 @@
         <v>540.1</v>
       </c>
       <c r="D4" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E4" t="n">
         <v>540.1</v>
@@ -10262,10 +10262,10 @@
         <v>39.83</v>
       </c>
       <c r="G4" t="n">
-        <v>-33.77</v>
+        <v>-33.28</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.64</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="5">
@@ -10283,7 +10283,7 @@
         <v>6375.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E5" t="n">
         <v>6375.5</v>
@@ -10292,10 +10292,10 @@
         <v>39.29</v>
       </c>
       <c r="G5" t="n">
-        <v>-18.34</v>
+        <v>-17.68</v>
       </c>
       <c r="H5" t="n">
-        <v>22.07</v>
+        <v>23.05</v>
       </c>
     </row>
     <row r="6">
@@ -10313,7 +10313,7 @@
         <v>79.52</v>
       </c>
       <c r="D6" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E6" t="n">
         <v>79.52</v>
@@ -10322,10 +10322,10 @@
         <v>37.26</v>
       </c>
       <c r="G6" t="n">
-        <v>-37.02</v>
+        <v>-36.92</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.5</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -10343,7 +10343,7 @@
         <v>80.53</v>
       </c>
       <c r="D7" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E7" t="n">
         <v>80.53</v>
@@ -10352,10 +10352,10 @@
         <v>37.2</v>
       </c>
       <c r="G7" t="n">
-        <v>-37.81</v>
+        <v>-37.71</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="8">
@@ -10373,7 +10373,7 @@
         <v>76.62</v>
       </c>
       <c r="D8" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E8" t="n">
         <v>76.62</v>
@@ -10382,10 +10382,10 @@
         <v>37.17</v>
       </c>
       <c r="G8" t="n">
-        <v>-34.64</v>
+        <v>-34.53</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.9</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="9">
@@ -10403,7 +10403,7 @@
         <v>277.07</v>
       </c>
       <c r="D9" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E9" t="n">
         <v>277.07</v>
@@ -10412,10 +10412,10 @@
         <v>34.66</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.15</v>
+        <v>0.06</v>
       </c>
       <c r="H9" t="n">
-        <v>42.06</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="10">
@@ -10433,7 +10433,7 @@
         <v>552.7</v>
       </c>
       <c r="D10" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E10" t="n">
         <v>552.7</v>
@@ -10442,10 +10442,10 @@
         <v>33.97</v>
       </c>
       <c r="G10" t="n">
-        <v>7.07</v>
+        <v>7.31</v>
       </c>
       <c r="H10" t="n">
-        <v>51.63</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="11">
@@ -10463,7 +10463,7 @@
         <v>552.7</v>
       </c>
       <c r="D11" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E11" t="n">
         <v>552.7</v>
@@ -10472,10 +10472,10 @@
         <v>33.33</v>
       </c>
       <c r="G11" t="n">
-        <v>7.07</v>
+        <v>7.31</v>
       </c>
       <c r="H11" t="n">
-        <v>50.85</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="12">
@@ -10493,7 +10493,7 @@
         <v>29.49</v>
       </c>
       <c r="D12" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E12" t="n">
         <v>29.49</v>
@@ -10502,10 +10502,10 @@
         <v>33.22</v>
       </c>
       <c r="G12" t="n">
-        <v>-46.32</v>
+        <v>-46.13</v>
       </c>
       <c r="H12" t="n">
-        <v>-24.54</v>
+        <v>-24.28</v>
       </c>
     </row>
     <row r="13">
@@ -10523,7 +10523,7 @@
         <v>1688.6</v>
       </c>
       <c r="D13" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E13" t="n">
         <v>1688.6</v>
@@ -10532,10 +10532,10 @@
         <v>32.62</v>
       </c>
       <c r="G13" t="n">
-        <v>-39.53</v>
+        <v>-37.42</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.79</v>
+        <v>-12.85</v>
       </c>
     </row>
     <row r="14">
@@ -10553,7 +10553,7 @@
         <v>317.17</v>
       </c>
       <c r="D14" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E14" t="n">
         <v>317.17</v>
@@ -10562,10 +10562,10 @@
         <v>32.54</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.02</v>
+        <v>-12.75</v>
       </c>
       <c r="H14" t="n">
-        <v>21.28</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="15">
@@ -10583,7 +10583,7 @@
         <v>1514</v>
       </c>
       <c r="D15" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E15" t="n">
         <v>1514</v>
@@ -10592,10 +10592,10 @@
         <v>31.82</v>
       </c>
       <c r="G15" t="n">
-        <v>-32.56</v>
+        <v>-30.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.52</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="16">
@@ -10613,7 +10613,7 @@
         <v>6114.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E16" t="n">
         <v>6114.5</v>
@@ -10622,10 +10622,10 @@
         <v>31.74</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.85</v>
+        <v>-14.17</v>
       </c>
       <c r="H16" t="n">
-        <v>20.17</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="17">
@@ -10643,7 +10643,7 @@
         <v>591.95</v>
       </c>
       <c r="D17" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E17" t="n">
         <v>591.95</v>
@@ -10652,10 +10652,10 @@
         <v>30.14</v>
       </c>
       <c r="G17" t="n">
-        <v>-39.57</v>
+        <v>-39.12</v>
       </c>
       <c r="H17" t="n">
-        <v>-17.59</v>
+        <v>-16.98</v>
       </c>
     </row>
     <row r="18">
@@ -10673,7 +10673,7 @@
         <v>586.5</v>
       </c>
       <c r="D18" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E18" t="n">
         <v>586.5</v>
@@ -10682,10 +10682,10 @@
         <v>29.96</v>
       </c>
       <c r="G18" t="n">
-        <v>5.68</v>
+        <v>5.78</v>
       </c>
       <c r="H18" t="n">
-        <v>43.96</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="19">
@@ -10703,7 +10703,7 @@
         <v>473.95</v>
       </c>
       <c r="D19" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E19" t="n">
         <v>473.95</v>
@@ -10712,10 +10712,10 @@
         <v>29.47</v>
       </c>
       <c r="G19" t="n">
-        <v>-24.53</v>
+        <v>-23.97</v>
       </c>
       <c r="H19" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="20">
@@ -10733,7 +10733,7 @@
         <v>270.39</v>
       </c>
       <c r="D20" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E20" t="n">
         <v>270.39</v>
@@ -10742,10 +10742,10 @@
         <v>29.35</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>39.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="21">
@@ -10763,7 +10763,7 @@
         <v>30.92</v>
       </c>
       <c r="D21" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E21" t="n">
         <v>30.92</v>
@@ -10772,10 +10772,10 @@
         <v>28.33</v>
       </c>
       <c r="G21" t="n">
-        <v>-48.8</v>
+        <v>-48.63</v>
       </c>
       <c r="H21" t="n">
-        <v>-31.22</v>
+        <v>-30.99</v>
       </c>
     </row>
     <row r="22">
@@ -10793,7 +10793,7 @@
         <v>1636.2</v>
       </c>
       <c r="D22" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E22" t="n">
         <v>1636.2</v>
@@ -10802,10 +10802,10 @@
         <v>26.37</v>
       </c>
       <c r="G22" t="n">
-        <v>-37.59</v>
+        <v>-35.42</v>
       </c>
       <c r="H22" t="n">
-        <v>-17.53</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="23">
@@ -10823,7 +10823,7 @@
         <v>6666.5</v>
       </c>
       <c r="D23" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E23" t="n">
         <v>6666.5</v>
@@ -10832,10 +10832,10 @@
         <v>25.29</v>
       </c>
       <c r="G23" t="n">
-        <v>-21.9</v>
+        <v>-21.28</v>
       </c>
       <c r="H23" t="n">
-        <v>2.82</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="24">
@@ -10853,7 +10853,7 @@
         <v>1618.2</v>
       </c>
       <c r="D24" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E24" t="n">
         <v>1618.2</v>
@@ -10862,10 +10862,10 @@
         <v>25.23</v>
       </c>
       <c r="G24" t="n">
-        <v>-36.9</v>
+        <v>-34.7</v>
       </c>
       <c r="H24" t="n">
-        <v>-17.48</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="25">
@@ -10883,7 +10883,7 @@
         <v>30.43</v>
       </c>
       <c r="D25" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E25" t="n">
         <v>30.43</v>
@@ -10892,10 +10892,10 @@
         <v>24.26</v>
       </c>
       <c r="G25" t="n">
-        <v>-47.97</v>
+        <v>-47.79</v>
       </c>
       <c r="H25" t="n">
-        <v>-32.61</v>
+        <v>-32.38</v>
       </c>
     </row>
     <row r="26">
@@ -10913,7 +10913,7 @@
         <v>30.36</v>
       </c>
       <c r="D26" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E26" t="n">
         <v>30.36</v>
@@ -10922,10 +10922,10 @@
         <v>23.91</v>
       </c>
       <c r="G26" t="n">
-        <v>-47.85</v>
+        <v>-47.67</v>
       </c>
       <c r="H26" t="n">
-        <v>-32.66</v>
+        <v>-32.42</v>
       </c>
     </row>
     <row r="27">
@@ -10943,7 +10943,7 @@
         <v>58.46</v>
       </c>
       <c r="D27" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E27" t="n">
         <v>58.46</v>
@@ -10952,10 +10952,10 @@
         <v>23.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-14.33</v>
+        <v>-14.2</v>
       </c>
       <c r="H27" t="n">
-        <v>11.03</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="28">
@@ -10973,7 +10973,7 @@
         <v>1599.6</v>
       </c>
       <c r="D28" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E28" t="n">
         <v>1599.6</v>
@@ -10982,10 +10982,10 @@
         <v>23.24</v>
       </c>
       <c r="G28" t="n">
-        <v>-36.17</v>
+        <v>-33.94</v>
       </c>
       <c r="H28" t="n">
-        <v>-18.11</v>
+        <v>-15.26</v>
       </c>
     </row>
     <row r="29">
@@ -11003,7 +11003,7 @@
         <v>548.2</v>
       </c>
       <c r="D29" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E29" t="n">
         <v>548.2</v>
@@ -11012,10 +11012,10 @@
         <v>22.37</v>
       </c>
       <c r="G29" t="n">
-        <v>-34.75</v>
+        <v>-34.27</v>
       </c>
       <c r="H29" t="n">
-        <v>-16.94</v>
+        <v>-16.33</v>
       </c>
     </row>
     <row r="30">
@@ -11033,7 +11033,7 @@
         <v>582.3</v>
       </c>
       <c r="D30" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E30" t="n">
         <v>582.3</v>
@@ -11042,10 +11042,10 @@
         <v>22.05</v>
       </c>
       <c r="G30" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="H30" t="n">
-        <v>28.54</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="31">
@@ -11063,7 +11063,7 @@
         <v>1682.8</v>
       </c>
       <c r="D31" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E31" t="n">
         <v>1682.8</v>
@@ -11072,10 +11072,10 @@
         <v>21.96</v>
       </c>
       <c r="G31" t="n">
-        <v>-39.32</v>
+        <v>-37.21</v>
       </c>
       <c r="H31" t="n">
-        <v>-23.28</v>
+        <v>-20.6</v>
       </c>
     </row>
     <row r="32">
@@ -11093,7 +11093,7 @@
         <v>301.77</v>
       </c>
       <c r="D32" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E32" t="n">
         <v>301.77</v>
@@ -11102,10 +11102,10 @@
         <v>20.49</v>
       </c>
       <c r="G32" t="n">
-        <v>-8.32</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>14.88</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="33">
@@ -11123,7 +11123,7 @@
         <v>30.75</v>
       </c>
       <c r="D33" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E33" t="n">
         <v>30.75</v>
@@ -11132,10 +11132,10 @@
         <v>20.44</v>
       </c>
       <c r="G33" t="n">
-        <v>-48.52</v>
+        <v>-48.34</v>
       </c>
       <c r="H33" t="n">
-        <v>-35.89</v>
+        <v>-35.67</v>
       </c>
     </row>
     <row r="34">
@@ -11153,7 +11153,7 @@
         <v>6249</v>
       </c>
       <c r="D34" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E34" t="n">
         <v>6249</v>
@@ -11162,10 +11162,10 @@
         <v>19.23</v>
       </c>
       <c r="G34" t="n">
-        <v>-16.68</v>
+        <v>-16.02</v>
       </c>
       <c r="H34" t="n">
-        <v>3.57</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="35">
@@ -11183,7 +11183,7 @@
         <v>6249</v>
       </c>
       <c r="D35" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E35" t="n">
         <v>6249</v>
@@ -11192,10 +11192,10 @@
         <v>18.41</v>
       </c>
       <c r="G35" t="n">
-        <v>-16.68</v>
+        <v>-16.02</v>
       </c>
       <c r="H35" t="n">
-        <v>2.93</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="36">
@@ -11213,7 +11213,7 @@
         <v>260.99</v>
       </c>
       <c r="D36" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E36" t="n">
         <v>260.99</v>
@@ -11222,10 +11222,10 @@
         <v>17.43</v>
       </c>
       <c r="G36" t="n">
-        <v>5.71</v>
+        <v>6.03</v>
       </c>
       <c r="H36" t="n">
-        <v>28.44</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="37">
@@ -11243,7 +11243,7 @@
         <v>1511.2</v>
       </c>
       <c r="D37" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E37" t="n">
         <v>1511.2</v>
@@ -11252,10 +11252,10 @@
         <v>17.29</v>
       </c>
       <c r="G37" t="n">
-        <v>-32.43</v>
+        <v>-30.08</v>
       </c>
       <c r="H37" t="n">
-        <v>-18.06</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="38">
@@ -11273,7 +11273,7 @@
         <v>600.8</v>
       </c>
       <c r="D38" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E38" t="n">
         <v>600.8</v>
@@ -11282,10 +11282,10 @@
         <v>15.08</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.5</v>
+        <v>-1.28</v>
       </c>
       <c r="H38" t="n">
-        <v>17.15</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="39">
@@ -11303,7 +11303,7 @@
         <v>27</v>
       </c>
       <c r="D39" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E39" t="n">
         <v>27</v>
@@ -11312,10 +11312,10 @@
         <v>15</v>
       </c>
       <c r="G39" t="n">
-        <v>-41.36</v>
+        <v>-41.16</v>
       </c>
       <c r="H39" t="n">
-        <v>-30.46</v>
+        <v>-30.22</v>
       </c>
     </row>
     <row r="40">
@@ -11333,7 +11333,7 @@
         <v>140.2</v>
       </c>
       <c r="D40" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E40" t="n">
         <v>140.2</v>
@@ -11342,10 +11342,10 @@
         <v>14.6</v>
       </c>
       <c r="G40" t="n">
-        <v>-7.69</v>
+        <v>-7.19</v>
       </c>
       <c r="H40" t="n">
-        <v>8.960000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -11363,7 +11363,7 @@
         <v>79.59</v>
       </c>
       <c r="D41" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E41" t="n">
         <v>79.59</v>
@@ -11372,10 +11372,10 @@
         <v>14.56</v>
       </c>
       <c r="G41" t="n">
-        <v>-37.08</v>
+        <v>-36.98</v>
       </c>
       <c r="H41" t="n">
-        <v>-25.45</v>
+        <v>-25.33</v>
       </c>
     </row>
     <row r="42">
@@ -11393,7 +11393,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E42" t="n">
         <v>79.59999999999999</v>
@@ -11402,10 +11402,10 @@
         <v>13.96</v>
       </c>
       <c r="G42" t="n">
-        <v>-37.09</v>
+        <v>-36.98</v>
       </c>
       <c r="H42" t="n">
-        <v>-25.88</v>
+        <v>-25.76</v>
       </c>
     </row>
     <row r="43">
@@ -11423,7 +11423,7 @@
         <v>127.83</v>
       </c>
       <c r="D43" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E43" t="n">
         <v>127.83</v>
@@ -11432,10 +11432,10 @@
         <v>12.78</v>
       </c>
       <c r="G43" t="n">
-        <v>-27.28</v>
+        <v>-24.96</v>
       </c>
       <c r="H43" t="n">
-        <v>-15.65</v>
+        <v>-12.97</v>
       </c>
     </row>
     <row r="44">
@@ -11453,7 +11453,7 @@
         <v>642</v>
       </c>
       <c r="D44" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E44" t="n">
         <v>642</v>
@@ -11462,10 +11462,10 @@
         <v>11.32</v>
       </c>
       <c r="G44" t="n">
-        <v>-3.46</v>
+        <v>-3.36</v>
       </c>
       <c r="H44" t="n">
-        <v>10.26</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="45">
@@ -11483,7 +11483,7 @@
         <v>500.65</v>
       </c>
       <c r="D45" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E45" t="n">
         <v>500.65</v>
@@ -11492,10 +11492,10 @@
         <v>10.67</v>
       </c>
       <c r="G45" t="n">
-        <v>-28.55</v>
+        <v>-28.02</v>
       </c>
       <c r="H45" t="n">
-        <v>-19.29</v>
+        <v>-18.69</v>
       </c>
     </row>
     <row r="46">
@@ -11513,7 +11513,7 @@
         <v>159.3</v>
       </c>
       <c r="D46" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E46" t="n">
         <v>159.3</v>
@@ -11522,10 +11522,10 @@
         <v>10.49</v>
       </c>
       <c r="G46" t="n">
-        <v>-18.76</v>
+        <v>-18.32</v>
       </c>
       <c r="H46" t="n">
-        <v>-7.85</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="47">
@@ -11543,7 +11543,7 @@
         <v>1444.6</v>
       </c>
       <c r="D47" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E47" t="n">
         <v>1444.6</v>
@@ -11552,10 +11552,10 @@
         <v>9.91</v>
       </c>
       <c r="G47" t="n">
-        <v>-29.32</v>
+        <v>-26.85</v>
       </c>
       <c r="H47" t="n">
-        <v>-20.79</v>
+        <v>-18.03</v>
       </c>
     </row>
     <row r="48">
@@ -11573,7 +11573,7 @@
         <v>6335.5</v>
       </c>
       <c r="D48" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E48" t="n">
         <v>6335.5</v>
@@ -11582,10 +11582,10 @@
         <v>9.85</v>
       </c>
       <c r="G48" t="n">
-        <v>-17.82</v>
+        <v>-17.17</v>
       </c>
       <c r="H48" t="n">
-        <v>-6.8</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="49">
@@ -11603,7 +11603,7 @@
         <v>132.17</v>
       </c>
       <c r="D49" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E49" t="n">
         <v>132.17</v>
@@ -11612,10 +11612,10 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>-29.67</v>
+        <v>-27.43</v>
       </c>
       <c r="H49" t="n">
-        <v>-21.66</v>
+        <v>-19.17</v>
       </c>
     </row>
     <row r="50">
@@ -11633,7 +11633,7 @@
         <v>128.76</v>
       </c>
       <c r="D50" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E50" t="n">
         <v>128.76</v>
@@ -11642,10 +11642,10 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>-27.8</v>
+        <v>-25.5</v>
       </c>
       <c r="H50" t="n">
-        <v>-19.74</v>
+        <v>-17.19</v>
       </c>
     </row>
     <row r="51">
@@ -11663,7 +11663,7 @@
         <v>22.05</v>
       </c>
       <c r="D51" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E51" t="n">
         <v>22.05</v>
@@ -11672,10 +11672,10 @@
         <v>5.4</v>
       </c>
       <c r="G51" t="n">
-        <v>-28.21</v>
+        <v>-27.96</v>
       </c>
       <c r="H51" t="n">
-        <v>-23.04</v>
+        <v>-22.77</v>
       </c>
     </row>
     <row r="52">
@@ -11693,7 +11693,7 @@
         <v>88.14</v>
       </c>
       <c r="D52" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E52" t="n">
         <v>88.14</v>
@@ -11702,10 +11702,10 @@
         <v>4.2</v>
       </c>
       <c r="G52" t="n">
-        <v>-43.18</v>
+        <v>-43.09</v>
       </c>
       <c r="H52" t="n">
-        <v>-40.13</v>
+        <v>-40.03</v>
       </c>
     </row>
     <row r="53">
@@ -11723,7 +11723,7 @@
         <v>155.08</v>
       </c>
       <c r="D53" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E53" t="n">
         <v>155.08</v>
@@ -11732,10 +11732,10 @@
         <v>3.82</v>
       </c>
       <c r="G53" t="n">
-        <v>-16.55</v>
+        <v>-16.09</v>
       </c>
       <c r="H53" t="n">
-        <v>-12.08</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="54">
@@ -11753,7 +11753,7 @@
         <v>195.3</v>
       </c>
       <c r="D54" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E54" t="n">
         <v>195.3</v>
@@ -11762,10 +11762,10 @@
         <v>2.43</v>
       </c>
       <c r="G54" t="n">
-        <v>-24.88</v>
+        <v>-24.28</v>
       </c>
       <c r="H54" t="n">
-        <v>-22.4</v>
+        <v>-21.77</v>
       </c>
     </row>
     <row r="55">
@@ -11783,7 +11783,7 @@
         <v>404.75</v>
       </c>
       <c r="D55" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E55" t="n">
         <v>404.75</v>
@@ -11792,10 +11792,10 @@
         <v>2.35</v>
       </c>
       <c r="G55" t="n">
-        <v>-11.62</v>
+        <v>-10.97</v>
       </c>
       <c r="H55" t="n">
-        <v>-8.85</v>
+        <v>-8.18</v>
       </c>
     </row>
     <row r="56">
@@ -11813,7 +11813,7 @@
         <v>183.56</v>
       </c>
       <c r="D56" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E56" t="n">
         <v>183.56</v>
@@ -11822,10 +11822,10 @@
         <v>2.1</v>
       </c>
       <c r="G56" t="n">
-        <v>-20.08</v>
+        <v>-19.43</v>
       </c>
       <c r="H56" t="n">
-        <v>-17.77</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="57">
@@ -11843,7 +11843,7 @@
         <v>152.48</v>
       </c>
       <c r="D57" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E57" t="n">
         <v>152.48</v>
@@ -11852,10 +11852,10 @@
         <v>1.8</v>
       </c>
       <c r="G57" t="n">
-        <v>-15.12</v>
+        <v>-14.66</v>
       </c>
       <c r="H57" t="n">
-        <v>-12.97</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="58">
@@ -11873,7 +11873,7 @@
         <v>541.8</v>
       </c>
       <c r="D58" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E58" t="n">
         <v>541.8</v>
@@ -11882,10 +11882,10 @@
         <v>1.67</v>
       </c>
       <c r="G58" t="n">
-        <v>9.23</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>11.91</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="59">
@@ -11903,7 +11903,7 @@
         <v>1286</v>
       </c>
       <c r="D59" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E59" t="n">
         <v>1286</v>
@@ -11912,10 +11912,10 @@
         <v>1.41</v>
       </c>
       <c r="G59" t="n">
-        <v>-25.35</v>
+        <v>-25.72</v>
       </c>
       <c r="H59" t="n">
-        <v>-23.78</v>
+        <v>-24.16</v>
       </c>
     </row>
     <row r="60">
@@ -11933,7 +11933,7 @@
         <v>24.7</v>
       </c>
       <c r="D60" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E60" t="n">
         <v>24.7</v>
@@ -11942,10 +11942,10 @@
         <v>-0.01</v>
       </c>
       <c r="G60" t="n">
-        <v>-35.9</v>
+        <v>-35.68</v>
       </c>
       <c r="H60" t="n">
-        <v>-35.89</v>
+        <v>-35.67</v>
       </c>
     </row>
     <row r="61">
@@ -11963,7 +11963,7 @@
         <v>302.09</v>
       </c>
       <c r="D61" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E61" t="n">
         <v>302.09</v>
@@ -11972,10 +11972,10 @@
         <v>-0.01</v>
       </c>
       <c r="G61" t="n">
-        <v>-8.67</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>-8.67</v>
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -11993,7 +11993,7 @@
         <v>28.99</v>
       </c>
       <c r="D62" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E62" t="n">
         <v>28.99</v>
@@ -12002,10 +12002,10 @@
         <v>-0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>-45.39</v>
+        <v>-45.21</v>
       </c>
       <c r="H62" t="n">
-        <v>-45.39</v>
+        <v>-45.2</v>
       </c>
     </row>
     <row r="63">
@@ -12023,7 +12023,7 @@
         <v>235.77</v>
       </c>
       <c r="D63" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E63" t="n">
         <v>235.77</v>
@@ -12032,10 +12032,10 @@
         <v>-0.03</v>
       </c>
       <c r="G63" t="n">
-        <v>-37.78</v>
+        <v>-37.27</v>
       </c>
       <c r="H63" t="n">
-        <v>-37.77</v>
+        <v>-37.26</v>
       </c>
     </row>
     <row r="64">
@@ -12053,7 +12053,7 @@
         <v>462.8</v>
       </c>
       <c r="D64" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E64" t="n">
         <v>462.8</v>
@@ -12062,10 +12062,10 @@
         <v>-0.04</v>
       </c>
       <c r="G64" t="n">
-        <v>-22.71</v>
+        <v>-22.14</v>
       </c>
       <c r="H64" t="n">
-        <v>-22.7</v>
+        <v>-22.13</v>
       </c>
     </row>
     <row r="65">
@@ -12083,7 +12083,7 @@
         <v>99.75</v>
       </c>
       <c r="D65" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E65" t="n">
         <v>99.75</v>
@@ -12092,10 +12092,10 @@
         <v>-0.05</v>
       </c>
       <c r="G65" t="n">
-        <v>-49.79</v>
+        <v>-49.71</v>
       </c>
       <c r="H65" t="n">
-        <v>-49.77</v>
+        <v>-49.69</v>
       </c>
     </row>
     <row r="66">
@@ -12113,7 +12113,7 @@
         <v>164.65</v>
       </c>
       <c r="D66" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E66" t="n">
         <v>164.65</v>
@@ -12122,10 +12122,10 @@
         <v>-0.06</v>
       </c>
       <c r="G66" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H66" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="67">
@@ -12143,7 +12143,7 @@
         <v>164.65</v>
       </c>
       <c r="D67" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E67" t="n">
         <v>164.65</v>
@@ -12152,10 +12152,10 @@
         <v>-0.06</v>
       </c>
       <c r="G67" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H67" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="68">
@@ -12173,7 +12173,7 @@
         <v>164.65</v>
       </c>
       <c r="D68" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E68" t="n">
         <v>164.65</v>
@@ -12182,10 +12182,10 @@
         <v>-0.06</v>
       </c>
       <c r="G68" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H68" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="69">
@@ -12203,7 +12203,7 @@
         <v>164.65</v>
       </c>
       <c r="D69" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E69" t="n">
         <v>164.65</v>
@@ -12212,10 +12212,10 @@
         <v>-0.06</v>
       </c>
       <c r="G69" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H69" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="70">
@@ -12233,7 +12233,7 @@
         <v>164.65</v>
       </c>
       <c r="D70" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E70" t="n">
         <v>164.65</v>
@@ -12242,10 +12242,10 @@
         <v>-0.06</v>
       </c>
       <c r="G70" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H70" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="71">
@@ -12263,7 +12263,7 @@
         <v>164.65</v>
       </c>
       <c r="D71" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E71" t="n">
         <v>164.65</v>
@@ -12272,10 +12272,10 @@
         <v>-0.06</v>
       </c>
       <c r="G71" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H71" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="72">
@@ -12293,7 +12293,7 @@
         <v>164.65</v>
       </c>
       <c r="D72" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E72" t="n">
         <v>164.65</v>
@@ -12302,10 +12302,10 @@
         <v>-0.06</v>
       </c>
       <c r="G72" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H72" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="73">
@@ -12323,7 +12323,7 @@
         <v>164.65</v>
       </c>
       <c r="D73" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E73" t="n">
         <v>164.65</v>
@@ -12332,10 +12332,10 @@
         <v>-0.06</v>
       </c>
       <c r="G73" t="n">
-        <v>-43.54</v>
+        <v>-41.74</v>
       </c>
       <c r="H73" t="n">
-        <v>-43.52</v>
+        <v>-41.72</v>
       </c>
     </row>
     <row r="74">
@@ -12353,7 +12353,7 @@
         <v>241.25</v>
       </c>
       <c r="D74" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E74" t="n">
         <v>241.25</v>
@@ -12362,10 +12362,10 @@
         <v>-0.12</v>
       </c>
       <c r="G74" t="n">
-        <v>14.36</v>
+        <v>14.71</v>
       </c>
       <c r="H74" t="n">
-        <v>14.34</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="75">
@@ -12383,7 +12383,7 @@
         <v>459.85</v>
       </c>
       <c r="D75" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E75" t="n">
         <v>459.85</v>
@@ -12392,10 +12392,10 @@
         <v>-0.21</v>
       </c>
       <c r="G75" t="n">
-        <v>-22.21</v>
+        <v>-21.64</v>
       </c>
       <c r="H75" t="n">
-        <v>-22.17</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="76">
@@ -12413,7 +12413,7 @@
         <v>459.85</v>
       </c>
       <c r="D76" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E76" t="n">
         <v>459.85</v>
@@ -12422,10 +12422,10 @@
         <v>-0.21</v>
       </c>
       <c r="G76" t="n">
-        <v>-22.21</v>
+        <v>-21.64</v>
       </c>
       <c r="H76" t="n">
-        <v>-22.17</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="77">
@@ -12443,7 +12443,7 @@
         <v>1223.8</v>
       </c>
       <c r="D77" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E77" t="n">
         <v>1223.8</v>
@@ -12452,10 +12452,10 @@
         <v>-0.87</v>
       </c>
       <c r="G77" t="n">
-        <v>-16.56</v>
+        <v>-13.65</v>
       </c>
       <c r="H77" t="n">
-        <v>-16.42</v>
+        <v>-13.54</v>
       </c>
     </row>
     <row r="78">
@@ -12473,7 +12473,7 @@
         <v>6802</v>
       </c>
       <c r="D78" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E78" t="n">
         <v>6802</v>
@@ -12482,10 +12482,10 @@
         <v>-4.77</v>
       </c>
       <c r="G78" t="n">
-        <v>-23.46</v>
+        <v>-22.85</v>
       </c>
       <c r="H78" t="n">
-        <v>-22.34</v>
+        <v>-21.76</v>
       </c>
     </row>
     <row r="79">
@@ -12503,7 +12503,7 @@
         <v>7920.5</v>
       </c>
       <c r="D79" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E79" t="n">
         <v>7920.5</v>
@@ -12512,10 +12512,10 @@
         <v>-4.95</v>
       </c>
       <c r="G79" t="n">
-        <v>-34.27</v>
+        <v>-33.74</v>
       </c>
       <c r="H79" t="n">
-        <v>-32.57</v>
+        <v>-32.07</v>
       </c>
     </row>
   </sheetData>
@@ -12589,7 +12589,7 @@
         <v>2533.8</v>
       </c>
       <c r="D2" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E2" t="n">
         <v>2533.8</v>
@@ -12598,10 +12598,10 @@
         <v>37.92</v>
       </c>
       <c r="G2" t="n">
-        <v>-62.11</v>
+        <v>-62.3</v>
       </c>
       <c r="H2" t="n">
-        <v>-44.53</v>
+        <v>-44.81</v>
       </c>
     </row>
     <row r="3">
@@ -12619,7 +12619,7 @@
         <v>2431.6</v>
       </c>
       <c r="D3" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E3" t="n">
         <v>2431.6</v>
@@ -12628,10 +12628,10 @@
         <v>27.77</v>
       </c>
       <c r="G3" t="n">
-        <v>-60.52</v>
+        <v>-60.72</v>
       </c>
       <c r="H3" t="n">
-        <v>-47.01</v>
+        <v>-47.28</v>
       </c>
     </row>
     <row r="4">
@@ -12649,7 +12649,7 @@
         <v>146.7</v>
       </c>
       <c r="D4" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E4" t="n">
         <v>146.7</v>
@@ -12658,10 +12658,10 @@
         <v>25.71</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>32.58</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="5">
@@ -12679,7 +12679,7 @@
         <v>139.9</v>
       </c>
       <c r="D5" t="n">
-        <v>129.42</v>
+        <v>130.12</v>
       </c>
       <c r="E5" t="n">
         <v>139.9</v>
@@ -12688,10 +12688,10 @@
         <v>21.97</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.49</v>
+        <v>-6.99</v>
       </c>
       <c r="H5" t="n">
-        <v>17.28</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="6">
@@ -12709,7 +12709,7 @@
         <v>2251.4</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E6" t="n">
         <v>2251.4</v>
@@ -12718,10 +12718,10 @@
         <v>21.93</v>
       </c>
       <c r="G6" t="n">
-        <v>-57.36</v>
+        <v>-57.57</v>
       </c>
       <c r="H6" t="n">
-        <v>-45.52</v>
+        <v>-45.79</v>
       </c>
     </row>
     <row r="7">
@@ -12739,7 +12739,7 @@
         <v>2121</v>
       </c>
       <c r="D7" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E7" t="n">
         <v>2121</v>
@@ -12748,10 +12748,10 @@
         <v>21.58</v>
       </c>
       <c r="G7" t="n">
-        <v>-54.74</v>
+        <v>-54.96</v>
       </c>
       <c r="H7" t="n">
-        <v>-42.35</v>
+        <v>-42.64</v>
       </c>
     </row>
     <row r="8">
@@ -12769,7 +12769,7 @@
         <v>1123</v>
       </c>
       <c r="D8" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E8" t="n">
         <v>1123</v>
@@ -12778,10 +12778,10 @@
         <v>19.67</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.07</v>
+        <v>-5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>13.17</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="9">
@@ -12799,7 +12799,7 @@
         <v>130.14</v>
       </c>
       <c r="D9" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E9" t="n">
         <v>130.14</v>
@@ -12808,10 +12808,10 @@
         <v>16.99</v>
       </c>
       <c r="G9" t="n">
-        <v>-28.57</v>
+        <v>-26.29</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.66</v>
+        <v>-10.91</v>
       </c>
     </row>
     <row r="10">
@@ -12829,7 +12829,7 @@
         <v>182.42</v>
       </c>
       <c r="D10" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E10" t="n">
         <v>182.42</v>
@@ -12838,10 +12838,10 @@
         <v>16.55</v>
       </c>
       <c r="G10" t="n">
-        <v>-19.58</v>
+        <v>-18.93</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.2</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="11">
@@ -12859,7 +12859,7 @@
         <v>1173.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E11" t="n">
         <v>1173.4</v>
@@ -12868,10 +12868,10 @@
         <v>16.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.98</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>4.47</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -12889,7 +12889,7 @@
         <v>127.84</v>
       </c>
       <c r="D12" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E12" t="n">
         <v>127.84</v>
@@ -12898,10 +12898,10 @@
         <v>16.16</v>
       </c>
       <c r="G12" t="n">
-        <v>-27.28</v>
+        <v>-24.97</v>
       </c>
       <c r="H12" t="n">
-        <v>-12.8</v>
+        <v>-10.02</v>
       </c>
     </row>
     <row r="13">
@@ -12919,7 +12919,7 @@
         <v>417</v>
       </c>
       <c r="D13" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E13" t="n">
         <v>417</v>
@@ -12928,10 +12928,10 @@
         <v>15.87</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.22</v>
+        <v>-13.59</v>
       </c>
       <c r="H13" t="n">
-        <v>2.85</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="14">
@@ -12949,7 +12949,7 @@
         <v>304.16</v>
       </c>
       <c r="D14" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E14" t="n">
         <v>304.16</v>
@@ -12958,10 +12958,10 @@
         <v>15.75</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="H14" t="n">
-        <v>8.369999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -12979,7 +12979,7 @@
         <v>2165.6</v>
       </c>
       <c r="D15" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E15" t="n">
         <v>2165.6</v>
@@ -12988,10 +12988,10 @@
         <v>15.73</v>
       </c>
       <c r="G15" t="n">
-        <v>-55.67</v>
+        <v>-55.89</v>
       </c>
       <c r="H15" t="n">
-        <v>-46.79</v>
+        <v>-47.06</v>
       </c>
     </row>
     <row r="16">
@@ -13009,7 +13009,7 @@
         <v>130.32</v>
       </c>
       <c r="D16" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E16" t="n">
         <v>130.32</v>
@@ -13018,10 +13018,10 @@
         <v>15.68</v>
       </c>
       <c r="G16" t="n">
-        <v>-28.67</v>
+        <v>-26.4</v>
       </c>
       <c r="H16" t="n">
-        <v>-14.83</v>
+        <v>-12.12</v>
       </c>
     </row>
     <row r="17">
@@ -13039,7 +13039,7 @@
         <v>21.91</v>
       </c>
       <c r="D17" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E17" t="n">
         <v>21.91</v>
@@ -13048,10 +13048,10 @@
         <v>14.41</v>
       </c>
       <c r="G17" t="n">
-        <v>-27.73</v>
+        <v>-27.48</v>
       </c>
       <c r="H17" t="n">
-        <v>-14.76</v>
+        <v>-14.47</v>
       </c>
     </row>
     <row r="18">
@@ -13069,7 +13069,7 @@
         <v>274.35</v>
       </c>
       <c r="D18" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E18" t="n">
         <v>274.35</v>
@@ -13078,10 +13078,10 @@
         <v>13.88</v>
       </c>
       <c r="G18" t="n">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="H18" t="n">
-        <v>18.59</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="19">
@@ -13099,7 +13099,7 @@
         <v>22.75</v>
       </c>
       <c r="D19" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E19" t="n">
         <v>22.75</v>
@@ -13108,10 +13108,10 @@
         <v>13.25</v>
       </c>
       <c r="G19" t="n">
-        <v>-30.4</v>
+        <v>-30.16</v>
       </c>
       <c r="H19" t="n">
-        <v>-18.9</v>
+        <v>-18.62</v>
       </c>
     </row>
     <row r="20">
@@ -13129,7 +13129,7 @@
         <v>1203</v>
       </c>
       <c r="D20" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E20" t="n">
         <v>1203</v>
@@ -13138,10 +13138,10 @@
         <v>11.29</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.12</v>
+        <v>-12.16</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.23</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="21">
@@ -13159,7 +13159,7 @@
         <v>125.17</v>
       </c>
       <c r="D21" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E21" t="n">
         <v>125.17</v>
@@ -13168,10 +13168,10 @@
         <v>10.95</v>
       </c>
       <c r="G21" t="n">
-        <v>-25.73</v>
+        <v>-23.37</v>
       </c>
       <c r="H21" t="n">
-        <v>-15.47</v>
+        <v>-12.78</v>
       </c>
     </row>
     <row r="22">
@@ -13189,7 +13189,7 @@
         <v>435.35</v>
       </c>
       <c r="D22" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E22" t="n">
         <v>435.35</v>
@@ -13198,10 +13198,10 @@
         <v>10.68</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.84</v>
+        <v>-17.23</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.73</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="23">
@@ -13219,7 +13219,7 @@
         <v>2392.6</v>
       </c>
       <c r="D23" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E23" t="n">
         <v>2392.6</v>
@@ -13228,10 +13228,10 @@
         <v>10.25</v>
       </c>
       <c r="G23" t="n">
-        <v>-59.88</v>
+        <v>-60.08</v>
       </c>
       <c r="H23" t="n">
-        <v>-54.65</v>
+        <v>-54.87</v>
       </c>
     </row>
     <row r="24">
@@ -13249,7 +13249,7 @@
         <v>124.68</v>
       </c>
       <c r="D24" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E24" t="n">
         <v>124.68</v>
@@ -13258,10 +13258,10 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-25.44</v>
+        <v>-23.07</v>
       </c>
       <c r="H24" t="n">
-        <v>-16.11</v>
+        <v>-13.44</v>
       </c>
     </row>
     <row r="25">
@@ -13279,7 +13279,7 @@
         <v>21.82</v>
       </c>
       <c r="D25" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E25" t="n">
         <v>21.82</v>
@@ -13288,10 +13288,10 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-27.45</v>
+        <v>-27.2</v>
       </c>
       <c r="H25" t="n">
-        <v>-18.69</v>
+        <v>-18.41</v>
       </c>
     </row>
     <row r="26">
@@ -13309,7 +13309,7 @@
         <v>274.28</v>
       </c>
       <c r="D26" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E26" t="n">
         <v>274.28</v>
@@ -13318,10 +13318,10 @@
         <v>9.57</v>
       </c>
       <c r="G26" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="H26" t="n">
-        <v>12.84</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="27">
@@ -13339,7 +13339,7 @@
         <v>174.08</v>
       </c>
       <c r="D27" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E27" t="n">
         <v>174.08</v>
@@ -13348,10 +13348,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-15.73</v>
+        <v>-15.04</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.49</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="28">
@@ -13369,7 +13369,7 @@
         <v>279.69</v>
       </c>
       <c r="D28" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E28" t="n">
         <v>279.69</v>
@@ -13378,10 +13378,10 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.08</v>
+        <v>-0.87</v>
       </c>
       <c r="H28" t="n">
-        <v>10.21</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="29">
@@ -13399,7 +13399,7 @@
         <v>21.3</v>
       </c>
       <c r="D29" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E29" t="n">
         <v>21.3</v>
@@ -13408,10 +13408,10 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>-25.68</v>
+        <v>-25.42</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.39</v>
+        <v>-17.11</v>
       </c>
     </row>
     <row r="30">
@@ -13429,7 +13429,7 @@
         <v>176.82</v>
       </c>
       <c r="D30" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E30" t="n">
         <v>176.82</v>
@@ -13438,10 +13438,10 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>-17.03</v>
+        <v>-16.36</v>
       </c>
       <c r="H30" t="n">
-        <v>-8.35</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="31">
@@ -13459,7 +13459,7 @@
         <v>176.7</v>
       </c>
       <c r="D31" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E31" t="n">
         <v>176.7</v>
@@ -13468,10 +13468,10 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>-16.98</v>
+        <v>-16.3</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.57</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="32">
@@ -13489,7 +13489,7 @@
         <v>646.6</v>
       </c>
       <c r="D32" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E32" t="n">
         <v>646.6</v>
@@ -13498,10 +13498,10 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>-4.14</v>
+        <v>-4.05</v>
       </c>
       <c r="H32" t="n">
-        <v>5.51</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="33">
@@ -13519,7 +13519,7 @@
         <v>304.82</v>
       </c>
       <c r="D33" t="n">
-        <v>276.66</v>
+        <v>277.25</v>
       </c>
       <c r="E33" t="n">
         <v>304.82</v>
@@ -13528,10 +13528,10 @@
         <v>7.22</v>
       </c>
       <c r="G33" t="n">
-        <v>-9.24</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.13</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="34">
@@ -13549,7 +13549,7 @@
         <v>613</v>
       </c>
       <c r="D34" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E34" t="n">
         <v>613</v>
@@ -13558,10 +13558,10 @@
         <v>6.89</v>
       </c>
       <c r="G34" t="n">
-        <v>-3.46</v>
+        <v>-3.25</v>
       </c>
       <c r="H34" t="n">
-        <v>4.85</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="35">
@@ -13579,7 +13579,7 @@
         <v>5470</v>
       </c>
       <c r="D35" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E35" t="n">
         <v>5470</v>
@@ -13588,10 +13588,10 @@
         <v>6.88</v>
       </c>
       <c r="G35" t="n">
-        <v>-4.82</v>
+        <v>-4.06</v>
       </c>
       <c r="H35" t="n">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="36">
@@ -13609,7 +13609,7 @@
         <v>116.15</v>
       </c>
       <c r="D36" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E36" t="n">
         <v>116.15</v>
@@ -13618,10 +13618,10 @@
         <v>6.67</v>
       </c>
       <c r="G36" t="n">
-        <v>-19.97</v>
+        <v>-17.42</v>
       </c>
       <c r="H36" t="n">
-        <v>-13</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="37">
@@ -13639,7 +13639,7 @@
         <v>2186</v>
       </c>
       <c r="D37" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E37" t="n">
         <v>2186</v>
@@ -13648,10 +13648,10 @@
         <v>6.6</v>
       </c>
       <c r="G37" t="n">
-        <v>-56.08</v>
+        <v>-56.3</v>
       </c>
       <c r="H37" t="n">
-        <v>-52.37</v>
+        <v>-52.6</v>
       </c>
     </row>
     <row r="38">
@@ -13669,7 +13669,7 @@
         <v>1005.7</v>
       </c>
       <c r="D38" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E38" t="n">
         <v>1005.7</v>
@@ -13678,10 +13678,10 @@
         <v>6.46</v>
       </c>
       <c r="G38" t="n">
-        <v>1.53</v>
+        <v>5.07</v>
       </c>
       <c r="H38" t="n">
-        <v>9.949999999999999</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="39">
@@ -13699,7 +13699,7 @@
         <v>52.28</v>
       </c>
       <c r="D39" t="n">
-        <v>50.08</v>
+        <v>50.16</v>
       </c>
       <c r="E39" t="n">
         <v>52.28</v>
@@ -13708,10 +13708,10 @@
         <v>6.37</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.21</v>
+        <v>-4.06</v>
       </c>
       <c r="H39" t="n">
-        <v>3.71</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="40">
@@ -13729,7 +13729,7 @@
         <v>2436.4</v>
       </c>
       <c r="D40" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E40" t="n">
         <v>2436.4</v>
@@ -13738,10 +13738,10 @@
         <v>6.04</v>
       </c>
       <c r="G40" t="n">
-        <v>-60.6</v>
+        <v>-60.79</v>
       </c>
       <c r="H40" t="n">
-        <v>-57.55</v>
+        <v>-57.76</v>
       </c>
     </row>
     <row r="41">
@@ -13759,7 +13759,7 @@
         <v>1119.4</v>
       </c>
       <c r="D41" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E41" t="n">
         <v>1119.4</v>
@@ -13768,10 +13768,10 @@
         <v>6.01</v>
       </c>
       <c r="G41" t="n">
-        <v>-8.779999999999999</v>
+        <v>-5.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.61</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="42">
@@ -13789,7 +13789,7 @@
         <v>174.99</v>
       </c>
       <c r="D42" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E42" t="n">
         <v>174.99</v>
@@ -13798,10 +13798,10 @@
         <v>5.65</v>
       </c>
       <c r="G42" t="n">
-        <v>-16.17</v>
+        <v>-15.49</v>
       </c>
       <c r="H42" t="n">
-        <v>-10.21</v>
+        <v>-9.48</v>
       </c>
     </row>
     <row r="43">
@@ -13819,7 +13819,7 @@
         <v>589.1</v>
       </c>
       <c r="D43" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E43" t="n">
         <v>589.1</v>
@@ -13828,10 +13828,10 @@
         <v>5.11</v>
       </c>
       <c r="G43" t="n">
-        <v>5.21</v>
+        <v>5.31</v>
       </c>
       <c r="H43" t="n">
-        <v>12.41</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="44">
@@ -13849,7 +13849,7 @@
         <v>90.88</v>
       </c>
       <c r="D44" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E44" t="n">
         <v>90.88</v>
@@ -13858,10 +13858,10 @@
         <v>4.97</v>
       </c>
       <c r="G44" t="n">
-        <v>2.29</v>
+        <v>5.55</v>
       </c>
       <c r="H44" t="n">
-        <v>9.039999999999999</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="45">
@@ -13879,7 +13879,7 @@
         <v>2323</v>
       </c>
       <c r="D45" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E45" t="n">
         <v>2323</v>
@@ -13888,10 +13888,10 @@
         <v>4.62</v>
       </c>
       <c r="G45" t="n">
-        <v>-58.67</v>
+        <v>-58.88</v>
       </c>
       <c r="H45" t="n">
-        <v>-56.28</v>
+        <v>-56.5</v>
       </c>
     </row>
     <row r="46">
@@ -13909,7 +13909,7 @@
         <v>152.68</v>
       </c>
       <c r="D46" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E46" t="n">
         <v>152.68</v>
@@ -13918,10 +13918,10 @@
         <v>4.48</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.92</v>
+        <v>-3.14</v>
       </c>
       <c r="H46" t="n">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="47">
@@ -13939,7 +13939,7 @@
         <v>279.2</v>
       </c>
       <c r="D47" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E47" t="n">
         <v>279.2</v>
@@ -13948,10 +13948,10 @@
         <v>4.22</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.19</v>
+        <v>-0.88</v>
       </c>
       <c r="H47" t="n">
-        <v>4.65</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="48">
@@ -13969,7 +13969,7 @@
         <v>357.7</v>
       </c>
       <c r="D48" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E48" t="n">
         <v>357.7</v>
@@ -13978,10 +13978,10 @@
         <v>3.94</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="H48" t="n">
-        <v>5.55</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="49">
@@ -13999,7 +13999,7 @@
         <v>90.61</v>
       </c>
       <c r="D49" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E49" t="n">
         <v>90.61</v>
@@ -14008,10 +14008,10 @@
         <v>3.87</v>
       </c>
       <c r="G49" t="n">
-        <v>2.59</v>
+        <v>5.86</v>
       </c>
       <c r="H49" t="n">
-        <v>8.15</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="50">
@@ -14029,7 +14029,7 @@
         <v>2283</v>
       </c>
       <c r="D50" t="n">
-        <v>960</v>
+        <v>955.2</v>
       </c>
       <c r="E50" t="n">
         <v>2283</v>
@@ -14038,10 +14038,10 @@
         <v>3.62</v>
       </c>
       <c r="G50" t="n">
-        <v>-57.95</v>
+        <v>-58.16</v>
       </c>
       <c r="H50" t="n">
-        <v>-56.08</v>
+        <v>-56.3</v>
       </c>
     </row>
     <row r="51">
@@ -14059,7 +14059,7 @@
         <v>277.04</v>
       </c>
       <c r="D51" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E51" t="n">
         <v>277.04</v>
@@ -14068,10 +14068,10 @@
         <v>3.5</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.42</v>
+        <v>-0.11</v>
       </c>
       <c r="H51" t="n">
-        <v>4.55</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="52">
@@ -14089,7 +14089,7 @@
         <v>1099.4</v>
       </c>
       <c r="D52" t="n">
-        <v>1021.1</v>
+        <v>1056.7</v>
       </c>
       <c r="E52" t="n">
         <v>1099.4</v>
@@ -14098,10 +14098,10 @@
         <v>3.3</v>
       </c>
       <c r="G52" t="n">
-        <v>-7.12</v>
+        <v>-3.88</v>
       </c>
       <c r="H52" t="n">
-        <v>-3.23</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="53">
@@ -14119,7 +14119,7 @@
         <v>411.65</v>
       </c>
       <c r="D53" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E53" t="n">
         <v>411.65</v>
@@ -14128,10 +14128,10 @@
         <v>3.14</v>
       </c>
       <c r="G53" t="n">
-        <v>-13.11</v>
+        <v>-12.46</v>
       </c>
       <c r="H53" t="n">
-        <v>-9.57</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="54">
@@ -14149,7 +14149,7 @@
         <v>598</v>
       </c>
       <c r="D54" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E54" t="n">
         <v>598</v>
@@ -14158,10 +14158,10 @@
         <v>3.03</v>
       </c>
       <c r="G54" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H54" t="n">
-        <v>7.71</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="55">
@@ -14179,7 +14179,7 @@
         <v>567.9</v>
       </c>
       <c r="D55" t="n">
-        <v>591.8</v>
+        <v>593.1</v>
       </c>
       <c r="E55" t="n">
         <v>567.9</v>
@@ -14188,10 +14188,10 @@
         <v>2.8</v>
       </c>
       <c r="G55" t="n">
-        <v>4.21</v>
+        <v>4.44</v>
       </c>
       <c r="H55" t="n">
-        <v>8.06</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -14209,7 +14209,7 @@
         <v>165.91</v>
       </c>
       <c r="D56" t="n">
-        <v>146.7</v>
+        <v>147.89</v>
       </c>
       <c r="E56" t="n">
         <v>165.91</v>
@@ -14218,10 +14218,10 @@
         <v>2.74</v>
       </c>
       <c r="G56" t="n">
-        <v>-11.58</v>
+        <v>-10.86</v>
       </c>
       <c r="H56" t="n">
-        <v>-8.359999999999999</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="57">
@@ -14239,7 +14239,7 @@
         <v>416.9</v>
       </c>
       <c r="D57" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E57" t="n">
         <v>416.9</v>
@@ -14248,10 +14248,10 @@
         <v>2.72</v>
       </c>
       <c r="G57" t="n">
-        <v>-14.2</v>
+        <v>-13.56</v>
       </c>
       <c r="H57" t="n">
-        <v>-11.1</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="58">
@@ -14269,7 +14269,7 @@
         <v>20.89</v>
       </c>
       <c r="D58" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E58" t="n">
         <v>20.89</v>
@@ -14278,10 +14278,10 @@
         <v>1.79</v>
       </c>
       <c r="G58" t="n">
-        <v>-24.24</v>
+        <v>-23.98</v>
       </c>
       <c r="H58" t="n">
-        <v>-22.33</v>
+        <v>-22.06</v>
       </c>
     </row>
     <row r="59">
@@ -14299,7 +14299,7 @@
         <v>20.84</v>
       </c>
       <c r="D59" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E59" t="n">
         <v>20.84</v>
@@ -14308,10 +14308,10 @@
         <v>1.7</v>
       </c>
       <c r="G59" t="n">
-        <v>-24.06</v>
+        <v>-23.79</v>
       </c>
       <c r="H59" t="n">
-        <v>-22.23</v>
+        <v>-21.96</v>
       </c>
     </row>
     <row r="60">
@@ -14329,7 +14329,7 @@
         <v>5697</v>
       </c>
       <c r="D60" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E60" t="n">
         <v>5697</v>
@@ -14338,10 +14338,10 @@
         <v>0.9</v>
       </c>
       <c r="G60" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.88</v>
       </c>
       <c r="H60" t="n">
-        <v>-6.38</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="61">
@@ -14359,7 +14359,7 @@
         <v>21.41</v>
       </c>
       <c r="D61" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E61" t="n">
         <v>21.41</v>
@@ -14368,10 +14368,10 @@
         <v>-0.01</v>
       </c>
       <c r="G61" t="n">
-        <v>-26.08</v>
+        <v>-25.82</v>
       </c>
       <c r="H61" t="n">
-        <v>-26.08</v>
+        <v>-25.82</v>
       </c>
     </row>
     <row r="62">
@@ -14389,7 +14389,7 @@
         <v>21.41</v>
       </c>
       <c r="D62" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E62" t="n">
         <v>21.41</v>
@@ -14398,10 +14398,10 @@
         <v>-0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>-26.08</v>
+        <v>-25.82</v>
       </c>
       <c r="H62" t="n">
-        <v>-26.08</v>
+        <v>-25.82</v>
       </c>
     </row>
     <row r="63">
@@ -14419,7 +14419,7 @@
         <v>21.66</v>
       </c>
       <c r="D63" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E63" t="n">
         <v>21.66</v>
@@ -14428,10 +14428,10 @@
         <v>-0.02</v>
       </c>
       <c r="G63" t="n">
-        <v>-26.93</v>
+        <v>-26.68</v>
       </c>
       <c r="H63" t="n">
-        <v>-26.93</v>
+        <v>-26.67</v>
       </c>
     </row>
     <row r="64">
@@ -14449,7 +14449,7 @@
         <v>21.66</v>
       </c>
       <c r="D64" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E64" t="n">
         <v>21.66</v>
@@ -14458,10 +14458,10 @@
         <v>-0.02</v>
       </c>
       <c r="G64" t="n">
-        <v>-26.93</v>
+        <v>-26.68</v>
       </c>
       <c r="H64" t="n">
-        <v>-26.93</v>
+        <v>-26.67</v>
       </c>
     </row>
     <row r="65">
@@ -14479,7 +14479,7 @@
         <v>21.66</v>
       </c>
       <c r="D65" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="E65" t="n">
         <v>21.66</v>
@@ -14488,10 +14488,10 @@
         <v>-0.02</v>
       </c>
       <c r="G65" t="n">
-        <v>-26.93</v>
+        <v>-26.68</v>
       </c>
       <c r="H65" t="n">
-        <v>-26.93</v>
+        <v>-26.67</v>
       </c>
     </row>
     <row r="66">
@@ -14509,7 +14509,7 @@
         <v>294.84</v>
       </c>
       <c r="D66" t="n">
-        <v>275.89</v>
+        <v>276.74</v>
       </c>
       <c r="E66" t="n">
         <v>294.84</v>
@@ -14518,10 +14518,10 @@
         <v>-0.05</v>
       </c>
       <c r="G66" t="n">
-        <v>-6.43</v>
+        <v>-6.14</v>
       </c>
       <c r="H66" t="n">
-        <v>-6.42</v>
+        <v>-6.14</v>
       </c>
     </row>
     <row r="67">
@@ -14539,7 +14539,7 @@
         <v>117.66</v>
       </c>
       <c r="D67" t="n">
-        <v>92.95999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="E67" t="n">
         <v>117.66</v>
@@ -14548,10 +14548,10 @@
         <v>-0.11</v>
       </c>
       <c r="G67" t="n">
-        <v>-20.99</v>
+        <v>-18.48</v>
       </c>
       <c r="H67" t="n">
-        <v>-20.97</v>
+        <v>-18.46</v>
       </c>
     </row>
     <row r="68">
@@ -14569,7 +14569,7 @@
         <v>6239</v>
       </c>
       <c r="D68" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E68" t="n">
         <v>6239</v>
@@ -14578,10 +14578,10 @@
         <v>-0.18</v>
       </c>
       <c r="G68" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H68" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="69">
@@ -14599,7 +14599,7 @@
         <v>6239</v>
       </c>
       <c r="D69" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E69" t="n">
         <v>6239</v>
@@ -14608,10 +14608,10 @@
         <v>-0.18</v>
       </c>
       <c r="G69" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H69" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="70">
@@ -14629,7 +14629,7 @@
         <v>6239</v>
       </c>
       <c r="D70" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E70" t="n">
         <v>6239</v>
@@ -14638,10 +14638,10 @@
         <v>-0.18</v>
       </c>
       <c r="G70" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H70" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="71">
@@ -14659,7 +14659,7 @@
         <v>6239</v>
       </c>
       <c r="D71" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E71" t="n">
         <v>6239</v>
@@ -14668,10 +14668,10 @@
         <v>-0.18</v>
       </c>
       <c r="G71" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H71" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="72">
@@ -14689,7 +14689,7 @@
         <v>6239</v>
       </c>
       <c r="D72" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E72" t="n">
         <v>6239</v>
@@ -14698,10 +14698,10 @@
         <v>-0.18</v>
       </c>
       <c r="G72" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H72" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="73">
@@ -14719,7 +14719,7 @@
         <v>6239</v>
       </c>
       <c r="D73" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E73" t="n">
         <v>6239</v>
@@ -14728,10 +14728,10 @@
         <v>-0.18</v>
       </c>
       <c r="G73" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H73" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="74">
@@ -14749,7 +14749,7 @@
         <v>6239</v>
       </c>
       <c r="D74" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E74" t="n">
         <v>6239</v>
@@ -14758,10 +14758,10 @@
         <v>-0.18</v>
       </c>
       <c r="G74" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H74" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="75">
@@ -14779,7 +14779,7 @@
         <v>6239</v>
       </c>
       <c r="D75" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E75" t="n">
         <v>6239</v>
@@ -14788,10 +14788,10 @@
         <v>-0.18</v>
       </c>
       <c r="G75" t="n">
-        <v>-16.55</v>
+        <v>-15.88</v>
       </c>
       <c r="H75" t="n">
-        <v>-16.52</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="76">
@@ -14809,7 +14809,7 @@
         <v>627.3</v>
       </c>
       <c r="D76" t="n">
-        <v>619.8</v>
+        <v>620.4</v>
       </c>
       <c r="E76" t="n">
         <v>627.3</v>
@@ -14818,10 +14818,10 @@
         <v>-0.26</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.19</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="77">
@@ -14839,7 +14839,7 @@
         <v>422.2</v>
       </c>
       <c r="D77" t="n">
-        <v>357.7</v>
+        <v>360.35</v>
       </c>
       <c r="E77" t="n">
         <v>422.2</v>
@@ -14848,10 +14848,10 @@
         <v>-0.36</v>
       </c>
       <c r="G77" t="n">
-        <v>-15.28</v>
+        <v>-14.65</v>
       </c>
       <c r="H77" t="n">
-        <v>-15.22</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="78">
@@ -14869,7 +14869,7 @@
         <v>6123</v>
       </c>
       <c r="D78" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E78" t="n">
         <v>6123</v>
@@ -14878,10 +14878,10 @@
         <v>-2.03</v>
       </c>
       <c r="G78" t="n">
-        <v>-14.97</v>
+        <v>-14.29</v>
       </c>
       <c r="H78" t="n">
-        <v>-14.66</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="79">
@@ -14899,7 +14899,7 @@
         <v>6123</v>
       </c>
       <c r="D79" t="n">
-        <v>5206.5</v>
+        <v>5248</v>
       </c>
       <c r="E79" t="n">
         <v>6123</v>
@@ -14908,10 +14908,10 @@
         <v>-2.03</v>
       </c>
       <c r="G79" t="n">
-        <v>-14.97</v>
+        <v>-14.29</v>
       </c>
       <c r="H79" t="n">
-        <v>-14.66</v>
+        <v>-14</v>
       </c>
     </row>
   </sheetData>
